--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835040</v>
+        <v>122832599</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>78499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529514</v>
+        <v>529625</v>
       </c>
       <c r="R2" t="n">
-        <v>7000177</v>
+        <v>7000333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122832599</v>
+        <v>122835621</v>
       </c>
       <c r="B3" t="n">
-        <v>78499</v>
+        <v>77699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -846,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529625</v>
+        <v>529556</v>
       </c>
       <c r="R3" t="n">
-        <v>7000333</v>
+        <v>7000147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835621</v>
+        <v>122835040</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +921,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529556</v>
+        <v>529514</v>
       </c>
       <c r="R4" t="n">
-        <v>7000147</v>
+        <v>7000177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1028,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122831851</v>
+        <v>122834978</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,34 +1056,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529624</v>
+        <v>529514</v>
       </c>
       <c r="R5" t="n">
-        <v>7000364</v>
+        <v>7000208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1130,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122834978</v>
+        <v>122831851</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,39 +1178,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529514</v>
+        <v>529624</v>
       </c>
       <c r="R6" t="n">
-        <v>7000208</v>
+        <v>7000364</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832733</v>
+        <v>122835055</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>77709</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,42 +1754,28 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1799,7 +1785,7 @@
         <v>529555</v>
       </c>
       <c r="R11" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,12 +1827,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1873,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835055</v>
+        <v>122832733</v>
       </c>
       <c r="B12" t="n">
-        <v>77709</v>
+        <v>98347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,28 +1871,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1916,7 +1916,7 @@
         <v>529555</v>
       </c>
       <c r="R12" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3199,10 +3199,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835079</v>
+        <v>122830095</v>
       </c>
       <c r="B23" t="n">
-        <v>78499</v>
+        <v>57428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3211,41 +3211,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529555</v>
+        <v>529529</v>
       </c>
       <c r="R23" t="n">
-        <v>7000239</v>
+        <v>7000102</v>
       </c>
       <c r="S23" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3272,24 +3281,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:59</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3304,22 +3298,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122830095</v>
+        <v>122835079</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>78499</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3328,50 +3322,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529529</v>
+        <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000102</v>
+        <v>7000239</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3398,9 +3383,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,12 +3415,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3542,6 +3542,2930 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122850162</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>529529</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7000221</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122843718</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>529568</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7000344</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122844745</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>529519</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7000310</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122849991</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>529495</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7000242</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122850306</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>529539</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7000235</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122844246</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>529543</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7000331</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122843242</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>529586</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7000356</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122845104</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>529481</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7000274</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122849927</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>529495</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7000242</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122848017</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>529485</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7000279</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122847410</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>529482</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7000271</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122842800</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>529564</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7000368</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122844041</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>529559</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7000333</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>122849488</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>529504</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7000251</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122844922</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>529490</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7000318</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>122843609</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>529564</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7000340</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>122848070</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>529485</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7000279</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>122848281</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>529501</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7000255</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>122842399</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>529556</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7000374</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>122844420</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78762</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>529532</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7000325</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122832599</v>
+        <v>122834822</v>
       </c>
       <c r="B2" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R2" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122835621</v>
+        <v>122835016</v>
       </c>
       <c r="B3" t="n">
-        <v>77699</v>
+        <v>90909</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529556</v>
+        <v>529528</v>
       </c>
       <c r="R3" t="n">
-        <v>7000147</v>
+        <v>7000177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +885,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835040</v>
+        <v>122832328</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,40 +929,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529514</v>
+        <v>529625</v>
       </c>
       <c r="R4" t="n">
-        <v>7000177</v>
+        <v>7000333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +1011,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834978</v>
+        <v>122834913</v>
       </c>
       <c r="B5" t="n">
         <v>57478</v>
@@ -1074,24 +1077,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R5" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,12 +1136,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122831851</v>
+        <v>122835055</v>
       </c>
       <c r="B6" t="n">
-        <v>78796</v>
+        <v>77709</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,21 +1184,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1202,10 +1208,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R6" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1243,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,12 +1253,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122834862</v>
+        <v>122834838</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1369,7 +1375,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834838</v>
+        <v>122835079</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,21 +1418,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,13 +1442,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R8" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1471,7 +1477,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,12 +1487,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1522,7 @@
         <v>122835651</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1625,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122835601</v>
+        <v>122831851</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,21 +1647,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529556</v>
+        <v>529624</v>
       </c>
       <c r="R10" t="n">
-        <v>7000147</v>
+        <v>7000364</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,22 +1736,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122835055</v>
+        <v>122834941</v>
       </c>
       <c r="B11" t="n">
-        <v>77709</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,35 +1760,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529555</v>
+        <v>529485</v>
       </c>
       <c r="R11" t="n">
         <v>7000239</v>
@@ -1817,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,12 +1842,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122832733</v>
+        <v>122834862</v>
       </c>
       <c r="B12" t="n">
-        <v>98347</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,52 +1881,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R12" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1948,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,12 +1954,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,10 +1986,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122834822</v>
+        <v>122835059</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2006,32 +2002,24 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -2041,7 +2029,7 @@
         <v>529555</v>
       </c>
       <c r="R13" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,7 +2061,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2083,12 +2071,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2115,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835637</v>
+        <v>122834884</v>
       </c>
       <c r="B14" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,39 +2119,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R14" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,7 +2178,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2205,12 +2188,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2225,22 +2208,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122834884</v>
+        <v>122832599</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>78503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2253,21 +2236,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2277,10 +2260,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R15" t="n">
-        <v>7000239</v>
+        <v>7000333</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2322,12 +2305,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2354,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122835016</v>
+        <v>122835065</v>
       </c>
       <c r="B16" t="n">
-        <v>90905</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2366,25 +2349,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2394,10 +2377,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529528</v>
+        <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2429,7 +2412,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2439,12 +2422,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2593,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122834941</v>
+        <v>122835040</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2636,16 +2619,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529485</v>
+        <v>529514</v>
       </c>
       <c r="R18" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2677,7 +2665,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2687,7 +2675,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2714,10 +2707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122834991</v>
+        <v>122835601</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2730,21 +2723,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2754,10 +2747,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529500</v>
+        <v>529556</v>
       </c>
       <c r="R19" t="n">
-        <v>7000177</v>
+        <v>7000147</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2789,7 +2782,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2799,12 +2792,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,22 +2812,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122834913</v>
+        <v>122834991</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2847,45 +2840,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R20" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2914,7 +2899,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2924,12 +2909,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122832328</v>
+        <v>122832733</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2968,35 +2953,40 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R21" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3040,7 +3030,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,12 +3040,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,10 +3072,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122835059</v>
+        <v>122835621</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3098,21 +3088,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3122,10 +3112,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R22" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3157,7 +3147,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3167,12 +3157,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,12 +3177,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3310,10 +3300,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835079</v>
+        <v>122835637</v>
       </c>
       <c r="B24" t="n">
-        <v>78499</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3326,37 +3316,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R24" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S24" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3390,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,22 +3410,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122835065</v>
+        <v>122834978</v>
       </c>
       <c r="B25" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3443,34 +3438,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R25" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850162</v>
+        <v>122850306</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529529</v>
+        <v>529539</v>
       </c>
       <c r="R26" t="n">
-        <v>7000221</v>
+        <v>7000235</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3668,14 +3668,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3693,7 +3688,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122843718</v>
+        <v>122844745</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3731,7 +3726,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3741,14 +3736,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529568</v>
+        <v>529519</v>
       </c>
       <c r="R27" t="n">
-        <v>7000344</v>
+        <v>7000310</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3785,7 +3780,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3804,7 +3799,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3842,7 +3837,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844745</v>
+        <v>122849927</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3894,13 +3889,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529519</v>
+        <v>529495</v>
       </c>
       <c r="R28" t="n">
-        <v>7000310</v>
+        <v>7000242</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3934,7 +3929,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3991,10 +3986,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122849991</v>
+        <v>122847410</v>
       </c>
       <c r="B29" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4007,40 +4002,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529495</v>
+        <v>529482</v>
       </c>
       <c r="R29" t="n">
-        <v>7000242</v>
+        <v>7000271</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4072,13 +4072,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4104,12 +4108,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4127,7 +4131,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850306</v>
+        <v>122843242</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4165,7 +4169,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4179,13 +4183,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529539</v>
+        <v>529586</v>
       </c>
       <c r="R30" t="n">
-        <v>7000235</v>
+        <v>7000356</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4219,7 +4223,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4238,7 +4242,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4251,9 +4255,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4271,7 +4280,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122844246</v>
+        <v>122843609</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4323,10 +4332,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529543</v>
+        <v>529564</v>
       </c>
       <c r="R31" t="n">
-        <v>7000331</v>
+        <v>7000340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4372,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4420,7 +4429,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122843242</v>
+        <v>122842800</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4458,7 +4467,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4472,10 +4481,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529586</v>
+        <v>529564</v>
       </c>
       <c r="R32" t="n">
-        <v>7000356</v>
+        <v>7000368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,7 +4521,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4569,10 +4578,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122845104</v>
+        <v>122844041</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4585,49 +4594,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529481</v>
+        <v>529559</v>
       </c>
       <c r="R33" t="n">
-        <v>7000274</v>
+        <v>7000333</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4670,6 +4670,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4680,17 +4681,27 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4708,7 +4719,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122849927</v>
+        <v>122848017</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4746,7 +4757,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4756,17 +4767,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529495</v>
+        <v>529485</v>
       </c>
       <c r="R34" t="n">
-        <v>7000242</v>
+        <v>7000279</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4800,7 +4811,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4857,10 +4868,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122848017</v>
+        <v>122848070</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4873,36 +4884,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
@@ -4949,7 +4951,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4958,6 +4960,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4983,12 +4986,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5006,7 +5009,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122847410</v>
+        <v>122842399</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5047,17 +5050,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529482</v>
+        <v>529556</v>
       </c>
       <c r="R36" t="n">
-        <v>7000271</v>
+        <v>7000374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5094,7 +5101,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5113,7 +5120,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5151,10 +5158,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842800</v>
+        <v>122844420</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5167,46 +5174,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529564</v>
+        <v>529532</v>
       </c>
       <c r="R37" t="n">
-        <v>7000368</v>
+        <v>7000325</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5243,7 +5245,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5252,6 +5254,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5262,7 +5265,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5277,12 +5280,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5300,10 +5303,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122844041</v>
+        <v>122844246</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5316,37 +5319,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529559</v>
+        <v>529543</v>
       </c>
       <c r="R38" t="n">
-        <v>7000333</v>
+        <v>7000331</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5383,7 +5395,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5392,7 +5404,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5418,12 +5429,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5441,7 +5452,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122849488</v>
+        <v>122843718</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5493,10 +5504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529504</v>
+        <v>529568</v>
       </c>
       <c r="R39" t="n">
-        <v>7000251</v>
+        <v>7000344</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5533,7 +5544,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5552,7 +5563,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5593,7 +5604,7 @@
         <v>122844922</v>
       </c>
       <c r="B40" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5735,7 +5746,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122843609</v>
+        <v>122849488</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5787,10 +5798,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529564</v>
+        <v>529504</v>
       </c>
       <c r="R41" t="n">
-        <v>7000340</v>
+        <v>7000251</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5827,7 +5838,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5846,7 +5857,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5884,10 +5895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122848070</v>
+        <v>122845104</v>
       </c>
       <c r="B42" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5900,40 +5911,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529485</v>
+        <v>529481</v>
       </c>
       <c r="R42" t="n">
-        <v>7000279</v>
+        <v>7000274</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5967,7 +5987,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5976,7 +5996,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5990,24 +6009,14 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6025,10 +6034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122848281</v>
+        <v>122849991</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6041,49 +6050,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529501</v>
+        <v>529495</v>
       </c>
       <c r="R43" t="n">
-        <v>7000255</v>
+        <v>7000242</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6115,17 +6115,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6151,12 +6147,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6174,7 +6170,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122842399</v>
+        <v>122848281</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6212,7 +6208,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6226,10 +6222,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529556</v>
+        <v>529501</v>
       </c>
       <c r="R44" t="n">
-        <v>7000374</v>
+        <v>7000255</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6266,7 +6262,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6285,7 +6281,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6300,12 +6296,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6323,10 +6319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122844420</v>
+        <v>122850162</v>
       </c>
       <c r="B45" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6339,41 +6335,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529532</v>
+        <v>529529</v>
       </c>
       <c r="R45" t="n">
-        <v>7000325</v>
+        <v>7000221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6410,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6419,7 +6420,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850306</v>
+        <v>122844745</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3582,7 +3582,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3592,17 +3592,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529539</v>
+        <v>529519</v>
       </c>
       <c r="R26" t="n">
-        <v>7000235</v>
+        <v>7000310</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3668,9 +3668,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3688,7 +3693,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122844745</v>
+        <v>122849927</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3740,13 +3745,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529519</v>
+        <v>529495</v>
       </c>
       <c r="R27" t="n">
-        <v>7000310</v>
+        <v>7000242</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3780,7 +3785,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3837,7 +3842,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122849927</v>
+        <v>122850306</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3875,7 +3880,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3885,14 +3890,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529495</v>
+        <v>529539</v>
       </c>
       <c r="R28" t="n">
-        <v>7000242</v>
+        <v>7000235</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3929,7 +3934,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3961,14 +3966,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122848017</v>
+        <v>122848070</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4735,36 +4735,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
@@ -4811,7 +4802,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4820,6 +4811,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4845,12 +4837,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4868,10 +4860,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122848070</v>
+        <v>122848017</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4884,27 +4876,36 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
@@ -4951,7 +4952,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4960,7 +4961,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122834822</v>
+        <v>122835621</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R2" t="n">
-        <v>7000270</v>
+        <v>7000147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122835016</v>
+        <v>122831851</v>
       </c>
       <c r="B3" t="n">
-        <v>90909</v>
+        <v>78800</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529528</v>
+        <v>529624</v>
       </c>
       <c r="R3" t="n">
-        <v>7000177</v>
+        <v>7000364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122832328</v>
+        <v>122835065</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,43 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834913</v>
+        <v>122835016</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>90909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,49 +1038,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529555</v>
+        <v>529528</v>
       </c>
       <c r="R5" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1168,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835055</v>
+        <v>122834822</v>
       </c>
       <c r="B6" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,24 +1159,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1211,7 +1194,7 @@
         <v>529555</v>
       </c>
       <c r="R6" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1253,12 +1236,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1268,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122834838</v>
+        <v>122832074</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,34 +1284,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529541</v>
+        <v>529610</v>
       </c>
       <c r="R7" t="n">
-        <v>7000301</v>
+        <v>7000425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,12 +1358,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122835079</v>
+        <v>122834913</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,24 +1406,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1448,7 +1444,7 @@
         <v>7000239</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,7 +1473,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1487,12 +1483,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1519,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835651</v>
+        <v>122832599</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,21 +1531,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1559,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529527</v>
+        <v>529625</v>
       </c>
       <c r="R9" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,22 +1620,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122831851</v>
+        <v>122835637</v>
       </c>
       <c r="B10" t="n">
-        <v>78800</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,34 +1648,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529624</v>
+        <v>529527</v>
       </c>
       <c r="R10" t="n">
-        <v>7000364</v>
+        <v>7000270</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,22 +1742,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834941</v>
+        <v>122835079</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,50 +1766,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529485</v>
+        <v>529555</v>
       </c>
       <c r="R11" t="n">
         <v>7000239</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1832,7 +1829,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1839,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122834862</v>
+        <v>122835055</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>77709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1885,21 +1887,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1909,10 +1911,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R12" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1944,7 +1946,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1954,12 +1956,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,10 +1988,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122835059</v>
+        <v>122834884</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,21 +2004,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2071,12 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122834884</v>
+        <v>122835040</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,38 +2117,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R14" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,7 +2194,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2188,12 +2204,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122832599</v>
+        <v>122835651</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,21 +2252,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2260,10 +2276,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529625</v>
+        <v>529527</v>
       </c>
       <c r="R15" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2311,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,12 +2321,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,22 +2336,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122835065</v>
+        <v>122834991</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,21 +2364,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2377,10 +2388,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R16" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,7 +2423,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2422,12 +2433,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2454,10 +2465,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122832074</v>
+        <v>122834862</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,39 +2481,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529610</v>
+        <v>529541</v>
       </c>
       <c r="R17" t="n">
-        <v>7000425</v>
+        <v>7000301</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2540,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,12 +2550,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,7 +2582,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122835040</v>
+        <v>122834941</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2619,21 +2625,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529514</v>
+        <v>529485</v>
       </c>
       <c r="R18" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,7 +2666,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2675,12 +2676,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På marken i gammal skog</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2824,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122834991</v>
+        <v>122832328</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,34 +2836,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529500</v>
+        <v>529625</v>
       </c>
       <c r="R20" t="n">
-        <v>7000177</v>
+        <v>7000333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,7 +2904,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2909,12 +2914,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2941,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122832733</v>
+        <v>122835059</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,42 +2958,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -2998,7 +2989,7 @@
         <v>529555</v>
       </c>
       <c r="R21" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3030,7 +3021,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3040,12 +3031,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,10 +3063,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122835621</v>
+        <v>122834838</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3088,21 +3079,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3112,10 +3103,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529556</v>
+        <v>529541</v>
       </c>
       <c r="R22" t="n">
-        <v>7000147</v>
+        <v>7000301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3147,7 +3138,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3157,7 +3148,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3177,22 +3168,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122830095</v>
+        <v>122834978</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3201,20 +3192,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3222,14 +3213,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3238,10 +3225,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529529</v>
+        <v>529514</v>
       </c>
       <c r="R23" t="n">
-        <v>7000102</v>
+        <v>7000208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3271,9 +3258,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,22 +3290,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835637</v>
+        <v>122830095</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3312,31 +3314,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3345,10 +3351,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529527</v>
+        <v>529529</v>
       </c>
       <c r="R24" t="n">
-        <v>7000270</v>
+        <v>7000102</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3378,24 +3384,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,22 +3401,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122834978</v>
+        <v>122832733</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>98355</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3434,31 +3425,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R25" t="n">
-        <v>7000208</v>
+        <v>7000270</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122844745</v>
+        <v>122844420</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,46 +3560,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529519</v>
+        <v>529532</v>
       </c>
       <c r="R26" t="n">
-        <v>7000310</v>
+        <v>7000325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3631,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,6 +3640,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3670,12 +3666,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3693,7 +3689,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122849927</v>
+        <v>122847410</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3734,24 +3730,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529495</v>
+        <v>529482</v>
       </c>
       <c r="R27" t="n">
-        <v>7000242</v>
+        <v>7000271</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3785,7 +3777,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122850306</v>
+        <v>122844041</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3858,49 +3850,40 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529539</v>
+        <v>529559</v>
       </c>
       <c r="R28" t="n">
-        <v>7000235</v>
+        <v>7000333</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3934,7 +3917,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3943,6 +3926,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3953,7 +3937,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3966,9 +3950,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3986,7 +3975,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122847410</v>
+        <v>122842399</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -4027,17 +4016,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529482</v>
+        <v>529556</v>
       </c>
       <c r="R29" t="n">
-        <v>7000271</v>
+        <v>7000374</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4074,7 +4067,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4093,7 +4086,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4131,7 +4124,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843242</v>
+        <v>122850306</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4169,7 +4162,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4183,13 +4176,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529586</v>
+        <v>529539</v>
       </c>
       <c r="R30" t="n">
-        <v>7000356</v>
+        <v>7000235</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4223,7 +4216,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4242,7 +4235,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4255,14 +4248,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4280,7 +4268,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122843609</v>
+        <v>122843718</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4332,10 +4320,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529564</v>
+        <v>529568</v>
       </c>
       <c r="R31" t="n">
-        <v>7000340</v>
+        <v>7000344</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4372,7 +4360,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4429,7 +4417,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842800</v>
+        <v>122849927</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4467,7 +4455,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4477,17 +4465,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529564</v>
+        <v>529495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000368</v>
+        <v>7000242</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4521,7 +4509,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4540,7 +4528,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4578,10 +4566,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122844041</v>
+        <v>122843242</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4594,37 +4582,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529559</v>
+        <v>529586</v>
       </c>
       <c r="R33" t="n">
-        <v>7000333</v>
+        <v>7000356</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4661,7 +4658,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4670,7 +4667,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4696,12 +4692,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4719,7 +4715,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122848070</v>
+        <v>122849991</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4758,17 +4754,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529485</v>
+        <v>529495</v>
       </c>
       <c r="R34" t="n">
-        <v>7000279</v>
+        <v>7000242</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4798,11 +4794,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4837,12 +4828,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4860,7 +4851,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122848017</v>
+        <v>122844246</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4912,10 +4903,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529485</v>
+        <v>529543</v>
       </c>
       <c r="R35" t="n">
-        <v>7000279</v>
+        <v>7000331</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4952,7 +4943,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4971,7 +4962,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -5009,10 +5000,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842399</v>
+        <v>122844922</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5025,46 +5016,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529556</v>
+        <v>529490</v>
       </c>
       <c r="R36" t="n">
-        <v>7000374</v>
+        <v>7000318</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5101,7 +5087,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5110,6 +5096,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5120,7 +5107,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5135,12 +5122,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5158,10 +5145,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122844420</v>
+        <v>122848017</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5174,41 +5161,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529532</v>
+        <v>529485</v>
       </c>
       <c r="R37" t="n">
-        <v>7000325</v>
+        <v>7000279</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5245,7 +5237,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5254,7 +5246,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5280,12 +5271,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5303,7 +5294,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122844246</v>
+        <v>122849488</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5355,10 +5346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529543</v>
+        <v>529504</v>
       </c>
       <c r="R38" t="n">
-        <v>7000331</v>
+        <v>7000251</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5414,7 +5405,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5452,7 +5443,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122843718</v>
+        <v>122843609</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5504,10 +5495,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529568</v>
+        <v>529564</v>
       </c>
       <c r="R39" t="n">
-        <v>7000344</v>
+        <v>7000340</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5544,7 +5535,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5601,10 +5592,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122844922</v>
+        <v>122842800</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5617,41 +5608,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529490</v>
+        <v>529564</v>
       </c>
       <c r="R40" t="n">
-        <v>7000318</v>
+        <v>7000368</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5688,7 +5684,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5697,7 +5693,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5708,7 +5703,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5723,12 +5718,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5746,10 +5741,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122849488</v>
+        <v>122848070</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5762,46 +5757,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529504</v>
+        <v>529485</v>
       </c>
       <c r="R41" t="n">
-        <v>7000251</v>
+        <v>7000279</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5838,7 +5824,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5847,6 +5833,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5872,12 +5859,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6034,10 +6021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122849991</v>
+        <v>122844745</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6050,40 +6037,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529495</v>
+        <v>529519</v>
       </c>
       <c r="R43" t="n">
-        <v>7000242</v>
+        <v>7000310</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6115,13 +6111,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835621</v>
+        <v>122832328</v>
       </c>
       <c r="B2" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529556</v>
+        <v>529625</v>
       </c>
       <c r="R2" t="n">
-        <v>7000147</v>
+        <v>7000333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -780,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122831851</v>
+        <v>122834962</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R3" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835065</v>
+        <v>122832733</v>
       </c>
       <c r="B4" t="n">
-        <v>77699</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,28 +930,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -952,7 +975,7 @@
         <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1017,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1049,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835016</v>
+        <v>122834941</v>
       </c>
       <c r="B5" t="n">
-        <v>90909</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,38 +1061,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529528</v>
+        <v>529485</v>
       </c>
       <c r="R5" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1133,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1143,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122834822</v>
+        <v>122835601</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,42 +1186,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R6" t="n">
-        <v>7000270</v>
+        <v>7000147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,12 +1255,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,22 +1275,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122832074</v>
+        <v>122835055</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1284,39 +1303,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529610</v>
+        <v>529555</v>
       </c>
       <c r="R7" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,12 +1372,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1515,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122832599</v>
+        <v>122835016</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,25 +1541,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1555,10 +1569,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529625</v>
+        <v>529528</v>
       </c>
       <c r="R9" t="n">
-        <v>7000333</v>
+        <v>7000177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1614,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122835637</v>
+        <v>122830095</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,31 +1658,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529527</v>
+        <v>529529</v>
       </c>
       <c r="R10" t="n">
-        <v>7000270</v>
+        <v>7000102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,24 +1728,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,22 +1745,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122835079</v>
+        <v>122834978</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,37 +1773,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R11" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S11" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1829,7 +1837,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,12 +1847,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835055</v>
+        <v>122834862</v>
       </c>
       <c r="B12" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1887,21 +1895,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1911,10 +1919,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R12" t="n">
-        <v>7000239</v>
+        <v>7000301</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,12 +1964,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,7 +1996,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122834884</v>
+        <v>122835651</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -2028,10 +2036,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R13" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +2071,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,12 +2081,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,22 +2096,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835040</v>
+        <v>122832599</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>78503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,52 +2120,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529514</v>
+        <v>529625</v>
       </c>
       <c r="R14" t="n">
-        <v>7000177</v>
+        <v>7000333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2204,12 +2193,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2236,10 +2225,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835651</v>
+        <v>122834838</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,21 +2241,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2276,10 +2265,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529527</v>
+        <v>529541</v>
       </c>
       <c r="R15" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2321,7 +2310,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,22 +2330,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122834991</v>
+        <v>122835079</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2364,21 +2358,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2388,13 +2382,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2423,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2433,12 +2427,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2465,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122834862</v>
+        <v>122835637</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2481,34 +2475,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529541</v>
+        <v>529527</v>
       </c>
       <c r="R17" t="n">
-        <v>7000301</v>
+        <v>7000270</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2540,7 +2539,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2550,12 +2549,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,22 +2569,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122834941</v>
+        <v>122832074</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2594,35 +2593,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2631,10 +2626,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529485</v>
+        <v>529610</v>
       </c>
       <c r="R18" t="n">
-        <v>7000239</v>
+        <v>7000425</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2666,7 +2661,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2676,7 +2671,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2703,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122835601</v>
+        <v>122835059</v>
       </c>
       <c r="B19" t="n">
         <v>74863</v>
@@ -2743,10 +2743,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R19" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2808,22 +2808,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122832328</v>
+        <v>122835040</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,35 +2832,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2869,10 +2874,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529625</v>
+        <v>529514</v>
       </c>
       <c r="R20" t="n">
-        <v>7000333</v>
+        <v>7000177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,7 +2909,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2914,12 +2919,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,10 +2951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122835059</v>
+        <v>122831851</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>78800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,21 +2967,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529555</v>
+        <v>529624</v>
       </c>
       <c r="R21" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3021,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3031,12 +3036,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,10 +3068,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122834838</v>
+        <v>122835621</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,21 +3084,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3103,10 +3108,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529541</v>
+        <v>529556</v>
       </c>
       <c r="R22" t="n">
-        <v>7000301</v>
+        <v>7000147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3138,7 +3143,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3148,7 +3153,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3168,22 +3173,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122834978</v>
+        <v>122835065</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3196,39 +3201,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R23" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3302,10 +3302,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122830095</v>
+        <v>122834822</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3314,20 +3314,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3335,26 +3335,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529529</v>
+        <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000102</v>
+        <v>7000270</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,9 +3383,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3401,22 +3415,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122832733</v>
+        <v>122834991</v>
       </c>
       <c r="B25" t="n">
-        <v>98355</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3425,52 +3439,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R25" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122844420</v>
+        <v>122842399</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,41 +3560,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529532</v>
+        <v>529556</v>
       </c>
       <c r="R26" t="n">
-        <v>7000325</v>
+        <v>7000374</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3631,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,7 +3645,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3651,7 +3655,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3666,12 +3670,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3689,7 +3693,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122847410</v>
+        <v>122843718</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3727,20 +3731,24 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529482</v>
+        <v>529568</v>
       </c>
       <c r="R27" t="n">
-        <v>7000271</v>
+        <v>7000344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3777,7 +3785,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,7 +3804,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3834,7 +3842,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844041</v>
+        <v>122844922</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3869,7 +3877,11 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529559</v>
+        <v>529490</v>
       </c>
       <c r="R28" t="n">
-        <v>7000333</v>
+        <v>7000318</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3917,7 +3929,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3937,7 +3949,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3952,12 +3964,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3975,10 +3987,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122842399</v>
+        <v>122848070</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,46 +4003,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529556</v>
+        <v>529485</v>
       </c>
       <c r="R29" t="n">
-        <v>7000374</v>
+        <v>7000279</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4067,7 +4070,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4076,6 +4079,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4086,7 +4090,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4101,12 +4105,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4124,7 +4128,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122850306</v>
+        <v>122842800</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4176,13 +4180,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529539</v>
+        <v>529564</v>
       </c>
       <c r="R30" t="n">
-        <v>7000235</v>
+        <v>7000368</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4216,7 +4220,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4235,7 +4239,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4248,9 +4252,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4268,7 +4277,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122843718</v>
+        <v>122843609</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4320,10 +4329,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529568</v>
+        <v>529564</v>
       </c>
       <c r="R31" t="n">
-        <v>7000344</v>
+        <v>7000340</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4360,7 +4369,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4417,7 +4426,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122849927</v>
+        <v>122847410</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4458,24 +4467,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529495</v>
+        <v>529482</v>
       </c>
       <c r="R32" t="n">
-        <v>7000242</v>
+        <v>7000271</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4509,7 +4514,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4566,7 +4571,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122843242</v>
+        <v>122844745</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4614,14 +4619,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529586</v>
+        <v>529519</v>
       </c>
       <c r="R33" t="n">
-        <v>7000356</v>
+        <v>7000310</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4658,7 +4663,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4677,7 +4682,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4715,7 +4720,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122849991</v>
+        <v>122844041</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4758,13 +4763,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529495</v>
+        <v>529559</v>
       </c>
       <c r="R34" t="n">
-        <v>7000242</v>
+        <v>7000333</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4794,6 +4799,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4813,7 +4823,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4828,12 +4838,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5000,10 +5010,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122844922</v>
+        <v>122849927</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5016,44 +5026,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529490</v>
+        <v>529495</v>
       </c>
       <c r="R36" t="n">
-        <v>7000318</v>
+        <v>7000242</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5087,7 +5102,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5096,7 +5111,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5122,12 +5136,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5145,7 +5159,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122848017</v>
+        <v>122845104</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5197,13 +5211,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529485</v>
+        <v>529481</v>
       </c>
       <c r="R37" t="n">
-        <v>7000279</v>
+        <v>7000274</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5237,7 +5251,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5259,16 +5273,6 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM37" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -5276,7 +5280,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5294,7 +5298,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122849488</v>
+        <v>122848017</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5346,10 +5350,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529504</v>
+        <v>529485</v>
       </c>
       <c r="R38" t="n">
-        <v>7000251</v>
+        <v>7000279</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5386,7 +5390,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5443,7 +5447,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122843609</v>
+        <v>122848281</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5495,10 +5499,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529564</v>
+        <v>529501</v>
       </c>
       <c r="R39" t="n">
-        <v>7000340</v>
+        <v>7000255</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5535,7 +5539,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5554,7 +5558,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5569,12 +5573,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5592,7 +5596,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122842800</v>
+        <v>122850306</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5644,13 +5648,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529564</v>
+        <v>529539</v>
       </c>
       <c r="R40" t="n">
-        <v>7000368</v>
+        <v>7000235</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5684,7 +5688,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5703,7 +5707,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5716,14 +5720,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5741,7 +5740,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122848070</v>
+        <v>122844420</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5776,18 +5775,22 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529485</v>
+        <v>529532</v>
       </c>
       <c r="R41" t="n">
-        <v>7000279</v>
+        <v>7000325</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5824,7 +5827,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5859,12 +5862,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5882,7 +5885,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122845104</v>
+        <v>122843242</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5920,7 +5923,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5934,13 +5937,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529481</v>
+        <v>529586</v>
       </c>
       <c r="R42" t="n">
-        <v>7000274</v>
+        <v>7000356</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5974,7 +5977,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5993,7 +5996,17 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -6003,7 +6016,7 @@
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6021,10 +6034,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122844745</v>
+        <v>122849991</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6037,49 +6050,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529519</v>
+        <v>529495</v>
       </c>
       <c r="R43" t="n">
-        <v>7000310</v>
+        <v>7000242</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6111,17 +6115,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122848281</v>
+        <v>122849488</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529501</v>
+        <v>529504</v>
       </c>
       <c r="R44" t="n">
-        <v>7000255</v>
+        <v>7000251</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -2581,10 +2581,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122832074</v>
+        <v>122835059</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,39 +2597,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529610</v>
+        <v>529555</v>
       </c>
       <c r="R18" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2661,7 +2656,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2671,12 +2666,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,10 +2698,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122835059</v>
+        <v>122832074</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2719,34 +2714,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529555</v>
+        <v>529610</v>
       </c>
       <c r="R19" t="n">
-        <v>7000239</v>
+        <v>7000425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122835040</v>
+        <v>122831851</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>78800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,52 +2832,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529514</v>
+        <v>529624</v>
       </c>
       <c r="R20" t="n">
-        <v>7000177</v>
+        <v>7000364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2909,7 +2895,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2919,12 +2905,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122831851</v>
+        <v>122835040</v>
       </c>
       <c r="B21" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2963,38 +2949,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529624</v>
+        <v>529514</v>
       </c>
       <c r="R21" t="n">
-        <v>7000364</v>
+        <v>7000177</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -1646,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122830095</v>
+        <v>122834978</v>
       </c>
       <c r="B10" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1679,14 +1679,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529529</v>
+        <v>529514</v>
       </c>
       <c r="R10" t="n">
-        <v>7000102</v>
+        <v>7000208</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,9 +1724,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,22 +1756,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834978</v>
+        <v>122830095</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,20 +1780,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1790,10 +1801,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1802,10 +1817,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529514</v>
+        <v>529529</v>
       </c>
       <c r="R11" t="n">
-        <v>7000208</v>
+        <v>7000102</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,24 +1850,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1867,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122831851</v>
+        <v>122835040</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,38 +2832,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529624</v>
+        <v>529514</v>
       </c>
       <c r="R20" t="n">
-        <v>7000364</v>
+        <v>7000177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2895,7 +2909,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2905,12 +2919,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,10 +2951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122835040</v>
+        <v>122835621</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>77699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,52 +2963,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529514</v>
+        <v>529556</v>
       </c>
       <c r="R21" t="n">
-        <v>7000177</v>
+        <v>7000147</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,22 +3056,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122835621</v>
+        <v>122831851</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>78800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529556</v>
+        <v>529624</v>
       </c>
       <c r="R22" t="n">
-        <v>7000147</v>
+        <v>7000364</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,22 +3173,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835065</v>
+        <v>122834822</v>
       </c>
       <c r="B23" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3201,24 +3201,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3228,7 +3236,7 @@
         <v>529555</v>
       </c>
       <c r="R23" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3260,7 +3268,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3270,12 +3278,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3302,10 +3310,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122834822</v>
+        <v>122835065</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,32 +3326,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3353,7 +3353,7 @@
         <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -1646,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122834978</v>
+        <v>122830095</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1679,10 +1679,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1691,10 +1695,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529514</v>
+        <v>529529</v>
       </c>
       <c r="R10" t="n">
-        <v>7000208</v>
+        <v>7000102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,24 +1728,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,22 +1745,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122830095</v>
+        <v>122834978</v>
       </c>
       <c r="B11" t="n">
-        <v>57428</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,20 +1769,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1801,14 +1790,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1817,10 +1802,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529529</v>
+        <v>529514</v>
       </c>
       <c r="R11" t="n">
-        <v>7000102</v>
+        <v>7000208</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1850,9 +1835,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,12 +1867,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122835040</v>
+        <v>122831851</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>78800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2832,52 +2832,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529514</v>
+        <v>529624</v>
       </c>
       <c r="R20" t="n">
-        <v>7000177</v>
+        <v>7000364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2909,7 +2895,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2919,12 +2905,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122835621</v>
+        <v>122835040</v>
       </c>
       <c r="B21" t="n">
-        <v>77699</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2963,38 +2949,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529556</v>
+        <v>529514</v>
       </c>
       <c r="R21" t="n">
-        <v>7000147</v>
+        <v>7000177</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,22 +3056,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122831851</v>
+        <v>122835621</v>
       </c>
       <c r="B22" t="n">
-        <v>78800</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3084,21 +3084,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529624</v>
+        <v>529556</v>
       </c>
       <c r="R22" t="n">
-        <v>7000364</v>
+        <v>7000147</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,12 +3173,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122849927</v>
+        <v>122848017</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5048,7 +5048,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5058,17 +5058,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529495</v>
+        <v>529485</v>
       </c>
       <c r="R36" t="n">
-        <v>7000242</v>
+        <v>7000279</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5159,7 +5159,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122845104</v>
+        <v>122849927</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5197,7 +5197,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5207,14 +5207,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529481</v>
+        <v>529495</v>
       </c>
       <c r="R37" t="n">
-        <v>7000274</v>
+        <v>7000242</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5273,6 +5273,16 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM37" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -5280,7 +5290,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5298,7 +5308,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122848017</v>
+        <v>122845104</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5350,13 +5360,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529485</v>
+        <v>529481</v>
       </c>
       <c r="R38" t="n">
-        <v>7000279</v>
+        <v>7000274</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5390,7 +5400,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5412,16 +5422,6 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM38" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122832328</v>
+        <v>122835651</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529625</v>
+        <v>529527</v>
       </c>
       <c r="R2" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,12 +775,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -918,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122832733</v>
+        <v>122835637</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,40 +916,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,7 +949,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R4" t="n">
         <v>7000270</v>
@@ -1007,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834941</v>
+        <v>122835601</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>74863</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,47 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529485</v>
+        <v>529556</v>
       </c>
       <c r="R5" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1143,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835601</v>
+        <v>122835079</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1210,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R6" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1255,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122835055</v>
+        <v>122831851</v>
       </c>
       <c r="B7" t="n">
-        <v>77709</v>
+        <v>78800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>314</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529555</v>
+        <v>529624</v>
       </c>
       <c r="R7" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1362,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834913</v>
+        <v>122835059</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1420,32 +1393,24 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1458,7 +1423,7 @@
         <v>7000239</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1497,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835016</v>
+        <v>122834978</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1541,38 +1506,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529528</v>
+        <v>529514</v>
       </c>
       <c r="R9" t="n">
-        <v>7000177</v>
+        <v>7000208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1604,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,12 +1584,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122830095</v>
+        <v>122832328</v>
       </c>
       <c r="B10" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,35 +1628,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1695,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529529</v>
+        <v>529625</v>
       </c>
       <c r="R10" t="n">
-        <v>7000102</v>
+        <v>7000333</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,9 +1698,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,19 +1730,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834978</v>
+        <v>122834822</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1791,21 +1776,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R11" t="n">
-        <v>7000208</v>
+        <v>7000270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1837,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1847,12 +1835,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1879,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122834862</v>
+        <v>122835016</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,25 +1879,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1919,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529541</v>
+        <v>529528</v>
       </c>
       <c r="R12" t="n">
-        <v>7000301</v>
+        <v>7000177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1954,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,12 +1952,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122835651</v>
+        <v>122832599</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529527</v>
+        <v>529625</v>
       </c>
       <c r="R13" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2069,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,22 +2089,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122832599</v>
+        <v>122830095</v>
       </c>
       <c r="B14" t="n">
-        <v>78503</v>
+        <v>57428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,38 +2113,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>102621</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529625</v>
+        <v>529529</v>
       </c>
       <c r="R14" t="n">
-        <v>7000333</v>
+        <v>7000102</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2181,24 +2183,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,22 +2200,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122834838</v>
+        <v>122834913</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,37 +2228,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R15" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2300,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2310,12 +2305,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122835079</v>
+        <v>122832733</v>
       </c>
       <c r="B16" t="n">
-        <v>78503</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2354,28 +2349,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -2385,10 +2394,10 @@
         <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S16" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,7 +2426,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,12 +2436,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122835637</v>
+        <v>122835055</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>77709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,39 +2484,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R17" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2539,7 +2543,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2549,12 +2553,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,22 +2573,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122835059</v>
+        <v>122834838</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,21 +2601,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2621,10 +2625,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R18" t="n">
-        <v>7000239</v>
+        <v>7000301</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2666,12 +2670,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2698,10 +2702,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122832074</v>
+        <v>122834941</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2710,31 +2714,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2743,10 +2751,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529610</v>
+        <v>529485</v>
       </c>
       <c r="R19" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2778,7 +2786,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2788,12 +2796,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122831851</v>
+        <v>122835065</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>77699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,21 +2839,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2860,10 +2863,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R20" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2895,7 +2898,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2905,12 +2908,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,10 +2940,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122835040</v>
+        <v>122834862</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2949,52 +2952,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529514</v>
+        <v>529541</v>
       </c>
       <c r="R21" t="n">
-        <v>7000177</v>
+        <v>7000301</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3026,7 +3015,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3036,12 +3025,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3068,10 +3057,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122835621</v>
+        <v>122832074</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3084,34 +3073,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529556</v>
+        <v>529610</v>
       </c>
       <c r="R22" t="n">
-        <v>7000147</v>
+        <v>7000425</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3143,7 +3137,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3153,12 +3147,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3173,22 +3167,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122834822</v>
+        <v>122835621</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3201,42 +3195,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R23" t="n">
-        <v>7000270</v>
+        <v>7000147</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3254,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3278,12 +3264,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3298,22 +3284,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835065</v>
+        <v>122835040</v>
       </c>
       <c r="B24" t="n">
-        <v>77699</v>
+        <v>98357</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,38 +3308,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R24" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122842399</v>
+        <v>122849927</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3592,17 +3592,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529556</v>
+        <v>529495</v>
       </c>
       <c r="R26" t="n">
-        <v>7000374</v>
+        <v>7000242</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3693,7 +3693,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122843718</v>
+        <v>122847410</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3731,24 +3731,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529568</v>
+        <v>529482</v>
       </c>
       <c r="R27" t="n">
-        <v>7000344</v>
+        <v>7000271</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3785,7 +3781,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3804,7 +3800,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3842,10 +3838,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844922</v>
+        <v>122843718</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3858,41 +3854,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529490</v>
+        <v>529568</v>
       </c>
       <c r="R28" t="n">
-        <v>7000318</v>
+        <v>7000344</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3929,7 +3930,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3938,7 +3939,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122848070</v>
+        <v>122844922</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -4022,18 +4022,22 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529485</v>
+        <v>529490</v>
       </c>
       <c r="R29" t="n">
-        <v>7000279</v>
+        <v>7000318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4070,7 +4074,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4105,12 +4109,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4128,10 +4132,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122842800</v>
+        <v>122849991</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4144,49 +4148,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529564</v>
+        <v>529495</v>
       </c>
       <c r="R30" t="n">
-        <v>7000368</v>
+        <v>7000242</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4218,17 +4213,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4239,7 +4230,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4254,12 +4245,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4277,7 +4268,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122843609</v>
+        <v>122842800</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4332,7 +4323,7 @@
         <v>529564</v>
       </c>
       <c r="R31" t="n">
-        <v>7000340</v>
+        <v>7000368</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4369,7 +4360,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4426,7 +4417,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122847410</v>
+        <v>122843242</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4467,17 +4458,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529482</v>
+        <v>529586</v>
       </c>
       <c r="R32" t="n">
-        <v>7000271</v>
+        <v>7000356</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4509,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4533,7 +4528,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4571,7 +4566,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122844745</v>
+        <v>122850306</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4609,7 +4604,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -4619,17 +4614,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529519</v>
+        <v>529539</v>
       </c>
       <c r="R33" t="n">
-        <v>7000310</v>
+        <v>7000235</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4663,7 +4658,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4695,14 +4690,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4720,10 +4710,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122844041</v>
+        <v>122849488</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4736,37 +4726,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529559</v>
+        <v>529504</v>
       </c>
       <c r="R34" t="n">
-        <v>7000333</v>
+        <v>7000251</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4803,7 +4802,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4812,7 +4811,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4823,7 +4821,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4838,12 +4836,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4861,7 +4859,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122844246</v>
+        <v>122848281</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4913,10 +4911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529543</v>
+        <v>529501</v>
       </c>
       <c r="R35" t="n">
-        <v>7000331</v>
+        <v>7000255</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4953,7 +4951,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4972,7 +4970,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4987,12 +4985,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5010,7 +5008,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122848017</v>
+        <v>122845104</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5062,13 +5060,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529485</v>
+        <v>529481</v>
       </c>
       <c r="R36" t="n">
-        <v>7000279</v>
+        <v>7000274</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5102,7 +5100,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5124,16 +5122,6 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM36" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -5141,7 +5129,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5159,10 +5147,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122849927</v>
+        <v>122844420</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5175,49 +5163,44 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529495</v>
+        <v>529532</v>
       </c>
       <c r="R37" t="n">
-        <v>7000242</v>
+        <v>7000325</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5251,7 +5234,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5260,6 +5243,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5285,12 +5269,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5308,10 +5292,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122845104</v>
+        <v>122844041</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5324,49 +5308,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529481</v>
+        <v>529559</v>
       </c>
       <c r="R38" t="n">
-        <v>7000274</v>
+        <v>7000333</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5400,7 +5375,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5409,6 +5384,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5419,17 +5395,27 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5447,7 +5433,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122848281</v>
+        <v>122842399</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5485,7 +5471,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5499,10 +5485,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529501</v>
+        <v>529556</v>
       </c>
       <c r="R39" t="n">
-        <v>7000255</v>
+        <v>7000374</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5539,7 +5525,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5558,7 +5544,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5573,12 +5559,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5596,7 +5582,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122850306</v>
+        <v>122844745</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5634,7 +5620,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5644,17 +5630,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529539</v>
+        <v>529519</v>
       </c>
       <c r="R40" t="n">
-        <v>7000235</v>
+        <v>7000310</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5688,7 +5674,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5720,9 +5706,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5740,10 +5731,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122844420</v>
+        <v>122844246</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5756,41 +5747,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529532</v>
+        <v>529543</v>
       </c>
       <c r="R41" t="n">
-        <v>7000325</v>
+        <v>7000331</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5827,7 +5823,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5836,7 +5832,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5847,7 +5842,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5862,12 +5857,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5885,7 +5880,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122843242</v>
+        <v>122848017</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5923,7 +5918,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5937,10 +5932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529586</v>
+        <v>529485</v>
       </c>
       <c r="R42" t="n">
-        <v>7000356</v>
+        <v>7000279</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5977,7 +5972,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5996,7 +5991,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6034,7 +6029,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122849991</v>
+        <v>122848070</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -6073,17 +6068,17 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529495</v>
+        <v>529485</v>
       </c>
       <c r="R43" t="n">
-        <v>7000242</v>
+        <v>7000279</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6113,6 +6108,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122849488</v>
+        <v>122850162</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6222,10 +6222,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529504</v>
+        <v>529529</v>
       </c>
       <c r="R44" t="n">
-        <v>7000251</v>
+        <v>7000221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6319,7 +6319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122850162</v>
+        <v>122843609</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529529</v>
+        <v>529564</v>
       </c>
       <c r="R45" t="n">
-        <v>7000221</v>
+        <v>7000340</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835601</v>
+        <v>122835079</v>
       </c>
       <c r="B5" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R5" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835079</v>
+        <v>122835601</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>74863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1159,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R6" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,12 +1248,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835651</v>
+        <v>122834822</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R2" t="n">
         <v>7000270</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +788,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122834962</v>
+        <v>122832328</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +816,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R3" t="n">
-        <v>7000239</v>
+        <v>7000333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +894,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +926,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835637</v>
+        <v>122834978</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,27 +942,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529527</v>
+        <v>529514</v>
       </c>
       <c r="R4" t="n">
-        <v>7000270</v>
+        <v>7000208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1036,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835079</v>
+        <v>122835040</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,41 +1060,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R5" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1137,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1147,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835601</v>
+        <v>122835621</v>
       </c>
       <c r="B6" t="n">
-        <v>74863</v>
+        <v>77699</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1195,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1260,10 +1296,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122831851</v>
+        <v>122835016</v>
       </c>
       <c r="B7" t="n">
-        <v>78800</v>
+        <v>90917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,25 +1308,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1336,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529624</v>
+        <v>529528</v>
       </c>
       <c r="R7" t="n">
-        <v>7000364</v>
+        <v>7000177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122835059</v>
+        <v>122834838</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1429,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1453,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R8" t="n">
-        <v>7000239</v>
+        <v>7000301</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1488,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,12 +1498,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,7 +1530,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122834978</v>
+        <v>122834913</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1528,24 +1564,27 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R9" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1574,7 +1613,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,12 +1623,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1655,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832328</v>
+        <v>122830095</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,35 +1667,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1704,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529625</v>
+        <v>529529</v>
       </c>
       <c r="R10" t="n">
-        <v>7000333</v>
+        <v>7000102</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,24 +1737,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,22 +1754,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834822</v>
+        <v>122832599</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,42 +1782,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R11" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1841,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,12 +1851,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835016</v>
+        <v>122834991</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1879,25 +1895,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,7 +1923,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529528</v>
+        <v>529500</v>
       </c>
       <c r="R12" t="n">
         <v>7000177</v>
@@ -1942,7 +1958,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,12 +1968,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122832599</v>
+        <v>122835637</v>
       </c>
       <c r="B13" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2000,34 +2016,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529625</v>
+        <v>529527</v>
       </c>
       <c r="R13" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,7 +2080,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,12 +2090,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,22 +2110,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122830095</v>
+        <v>122831851</v>
       </c>
       <c r="B14" t="n">
-        <v>57428</v>
+        <v>78800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,47 +2134,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102621</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529529</v>
+        <v>529624</v>
       </c>
       <c r="R14" t="n">
-        <v>7000102</v>
+        <v>7000364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,9 +2195,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,22 +2227,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122834913</v>
+        <v>122835065</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,32 +2255,24 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -2266,7 +2285,7 @@
         <v>7000239</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,7 +2314,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,12 +2324,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2337,10 +2356,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122832733</v>
+        <v>122835651</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,49 +2368,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R16" t="n">
         <v>7000270</v>
@@ -2426,7 +2431,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2436,12 +2441,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I gammal granskog</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,22 +2456,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122835055</v>
+        <v>122834962</v>
       </c>
       <c r="B17" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,21 +2484,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122834838</v>
+        <v>122834862</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,21 +2601,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2702,10 +2702,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122834941</v>
+        <v>122835079</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>78503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2714,50 +2714,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529485</v>
+        <v>529555</v>
       </c>
       <c r="R19" t="n">
         <v>7000239</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2786,7 +2777,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2796,7 +2787,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2823,10 +2819,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122835065</v>
+        <v>122832074</v>
       </c>
       <c r="B20" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,34 +2835,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529555</v>
+        <v>529610</v>
       </c>
       <c r="R20" t="n">
-        <v>7000239</v>
+        <v>7000425</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2898,7 +2899,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2908,12 +2909,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2940,10 +2941,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122834862</v>
+        <v>122834941</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,38 +2953,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529541</v>
+        <v>529485</v>
       </c>
       <c r="R21" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3015,7 +3025,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3025,12 +3035,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3057,10 +3062,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122832074</v>
+        <v>122835059</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,39 +3078,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529610</v>
+        <v>529555</v>
       </c>
       <c r="R22" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835621</v>
+        <v>122832733</v>
       </c>
       <c r="B23" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,38 +3191,52 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R23" t="n">
-        <v>7000147</v>
+        <v>7000270</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3254,7 +3268,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3264,12 +3278,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3284,22 +3298,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835040</v>
+        <v>122835055</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>77709</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3308,52 +3322,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,10 +3427,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122834991</v>
+        <v>122835601</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3443,21 +3443,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529500</v>
+        <v>529556</v>
       </c>
       <c r="R25" t="n">
-        <v>7000177</v>
+        <v>7000147</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,22 +3532,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122849927</v>
+        <v>122844041</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,49 +3560,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529495</v>
+        <v>529559</v>
       </c>
       <c r="R26" t="n">
-        <v>7000242</v>
+        <v>7000333</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3636,7 +3627,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,6 +3636,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3655,7 +3647,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3670,12 +3662,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3693,7 +3685,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122847410</v>
+        <v>122845104</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3731,23 +3723,27 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529482</v>
+        <v>529481</v>
       </c>
       <c r="R27" t="n">
-        <v>7000271</v>
+        <v>7000274</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3781,7 +3777,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3803,16 +3799,6 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM27" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -3820,7 +3806,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3838,7 +3824,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122843718</v>
+        <v>122849927</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3876,7 +3862,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3886,17 +3872,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529568</v>
+        <v>529495</v>
       </c>
       <c r="R28" t="n">
-        <v>7000344</v>
+        <v>7000242</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3930,7 +3916,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3949,7 +3935,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3987,10 +3973,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122844922</v>
+        <v>122844246</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4003,41 +3989,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529490</v>
+        <v>529543</v>
       </c>
       <c r="R29" t="n">
-        <v>7000318</v>
+        <v>7000331</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4074,7 +4065,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4083,7 +4074,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4094,7 +4084,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4109,12 +4099,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4132,10 +4122,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122849991</v>
+        <v>122843609</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4148,40 +4138,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529495</v>
+        <v>529564</v>
       </c>
       <c r="R30" t="n">
-        <v>7000242</v>
+        <v>7000340</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4213,13 +4212,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4230,7 +4233,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4245,12 +4248,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842800</v>
+        <v>122843718</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4320,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529564</v>
+        <v>529568</v>
       </c>
       <c r="R31" t="n">
-        <v>7000368</v>
+        <v>7000344</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4417,7 +4420,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122843242</v>
+        <v>122842800</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4455,7 +4458,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4469,10 +4472,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529586</v>
+        <v>529564</v>
       </c>
       <c r="R32" t="n">
-        <v>7000356</v>
+        <v>7000368</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4509,7 +4512,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4566,7 +4569,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122850306</v>
+        <v>122847410</v>
       </c>
       <c r="B33" t="n">
         <v>57478</v>
@@ -4604,27 +4607,23 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529539</v>
+        <v>529482</v>
       </c>
       <c r="R33" t="n">
-        <v>7000235</v>
+        <v>7000271</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4658,7 +4657,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4690,9 +4689,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4710,7 +4714,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122849488</v>
+        <v>122850306</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4762,13 +4766,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529504</v>
+        <v>529539</v>
       </c>
       <c r="R34" t="n">
-        <v>7000251</v>
+        <v>7000235</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4802,7 +4806,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4834,14 +4838,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4859,7 +4858,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122848281</v>
+        <v>122842399</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4897,7 +4896,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4911,10 +4910,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529501</v>
+        <v>529556</v>
       </c>
       <c r="R35" t="n">
-        <v>7000255</v>
+        <v>7000374</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4951,7 +4950,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4970,7 +4969,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4985,12 +4984,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5008,10 +5007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122845104</v>
+        <v>122849991</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5024,46 +5023,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529481</v>
+        <v>529495</v>
       </c>
       <c r="R36" t="n">
-        <v>7000274</v>
+        <v>7000242</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5098,17 +5088,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5122,14 +5108,24 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5147,10 +5143,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122844420</v>
+        <v>122848281</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5163,41 +5159,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529532</v>
+        <v>529501</v>
       </c>
       <c r="R37" t="n">
-        <v>7000325</v>
+        <v>7000255</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5234,7 +5235,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5243,7 +5244,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5292,7 +5292,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122844041</v>
+        <v>122844420</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5327,7 +5327,11 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5335,10 +5339,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529559</v>
+        <v>529532</v>
       </c>
       <c r="R38" t="n">
-        <v>7000333</v>
+        <v>7000325</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5375,7 +5379,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5395,7 +5399,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5410,12 +5414,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5433,7 +5437,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842399</v>
+        <v>122849488</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5471,7 +5475,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5485,10 +5489,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529556</v>
+        <v>529504</v>
       </c>
       <c r="R39" t="n">
-        <v>7000374</v>
+        <v>7000251</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5525,7 +5529,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5544,7 +5548,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5582,7 +5586,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122844745</v>
+        <v>122843242</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5630,14 +5634,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529519</v>
+        <v>529586</v>
       </c>
       <c r="R40" t="n">
-        <v>7000310</v>
+        <v>7000356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5674,7 +5678,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5693,7 +5697,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5731,7 +5735,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122844246</v>
+        <v>122844745</v>
       </c>
       <c r="B41" t="n">
         <v>57478</v>
@@ -5769,7 +5773,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -5779,14 +5783,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529543</v>
+        <v>529519</v>
       </c>
       <c r="R41" t="n">
-        <v>7000331</v>
+        <v>7000310</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5823,7 +5827,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5842,7 +5846,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -6170,10 +6174,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122850162</v>
+        <v>122844922</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6186,46 +6190,41 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529529</v>
+        <v>529490</v>
       </c>
       <c r="R44" t="n">
-        <v>7000221</v>
+        <v>7000318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6262,7 +6261,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6271,6 +6270,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6296,12 +6296,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122843609</v>
+        <v>122850162</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529564</v>
+        <v>529529</v>
       </c>
       <c r="R45" t="n">
-        <v>7000340</v>
+        <v>7000221</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -3179,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122832733</v>
+        <v>122835055</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>77709</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,42 +3191,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3236,7 +3222,7 @@
         <v>529555</v>
       </c>
       <c r="R23" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3254,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3278,12 +3264,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3310,10 +3296,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835055</v>
+        <v>122832733</v>
       </c>
       <c r="B24" t="n">
-        <v>77709</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,28 +3308,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3353,7 +3353,7 @@
         <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122834822</v>
+        <v>122835016</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>90917</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529555</v>
+        <v>529528</v>
       </c>
       <c r="R2" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122832328</v>
+        <v>122832599</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,33 +808,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -899,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122834978</v>
+        <v>122830095</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57428</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,20 +921,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,10 +942,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -971,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529514</v>
+        <v>529529</v>
       </c>
       <c r="R4" t="n">
-        <v>7000208</v>
+        <v>7000102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,24 +991,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835040</v>
+        <v>122835055</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>77709</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,52 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R5" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1147,12 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835621</v>
+        <v>122834991</v>
       </c>
       <c r="B6" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,21 +1153,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1219,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529556</v>
+        <v>529500</v>
       </c>
       <c r="R6" t="n">
-        <v>7000147</v>
+        <v>7000177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1254,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,12 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122835016</v>
+        <v>122835651</v>
       </c>
       <c r="B7" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1336,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529528</v>
+        <v>529527</v>
       </c>
       <c r="R7" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:34</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834838</v>
+        <v>122834962</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1453,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R8" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1488,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1498,12 +1451,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122834913</v>
+        <v>122835079</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,32 +1499,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1584,7 +1529,7 @@
         <v>7000239</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1613,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1623,12 +1568,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122830095</v>
+        <v>122834862</v>
       </c>
       <c r="B10" t="n">
-        <v>57428</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,47 +1612,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529529</v>
+        <v>529541</v>
       </c>
       <c r="R10" t="n">
-        <v>7000102</v>
+        <v>7000301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1737,9 +1673,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122832599</v>
+        <v>122835637</v>
       </c>
       <c r="B11" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1782,34 +1733,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529625</v>
+        <v>529527</v>
       </c>
       <c r="R11" t="n">
-        <v>7000333</v>
+        <v>7000270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1841,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1851,12 +1807,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,22 +1827,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122834991</v>
+        <v>122832733</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1895,38 +1851,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R12" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1958,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1968,12 +1938,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122835637</v>
+        <v>122835065</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2016,39 +1986,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R13" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2080,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2090,12 +2055,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2110,22 +2075,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122831851</v>
+        <v>122835059</v>
       </c>
       <c r="B14" t="n">
-        <v>78800</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,21 +2103,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2162,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R14" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2197,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2207,12 +2172,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835065</v>
+        <v>122835601</v>
       </c>
       <c r="B15" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,21 +2220,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R15" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2314,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2324,12 +2289,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,22 +2309,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122835651</v>
+        <v>122834913</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2372,37 +2337,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2431,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2441,7 +2414,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,22 +2434,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122834962</v>
+        <v>122832328</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,34 +2462,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R17" t="n">
-        <v>7000239</v>
+        <v>7000333</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,7 +2530,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2553,12 +2540,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,10 +2572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122834862</v>
+        <v>122835621</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,21 +2588,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2625,10 +2612,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529541</v>
+        <v>529556</v>
       </c>
       <c r="R18" t="n">
-        <v>7000301</v>
+        <v>7000147</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2660,7 +2647,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2670,12 +2657,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,22 +2677,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122835079</v>
+        <v>122835040</v>
       </c>
       <c r="B19" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2714,41 +2701,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R19" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S19" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2777,7 +2778,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2787,12 +2788,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,10 +2820,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122832074</v>
+        <v>122831851</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78798</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,39 +2836,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529610</v>
+        <v>529624</v>
       </c>
       <c r="R20" t="n">
-        <v>7000425</v>
+        <v>7000364</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2899,7 +2895,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2909,12 +2905,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2941,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122834941</v>
+        <v>122834838</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,47 +2949,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529485</v>
+        <v>529541</v>
       </c>
       <c r="R21" t="n">
-        <v>7000239</v>
+        <v>7000301</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3025,7 +3012,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3035,7 +3022,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3062,10 +3054,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122835059</v>
+        <v>122834822</v>
       </c>
       <c r="B22" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3078,24 +3070,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3105,7 +3105,7 @@
         <v>529555</v>
       </c>
       <c r="R22" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3179,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835055</v>
+        <v>122834978</v>
       </c>
       <c r="B23" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3195,34 +3195,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R23" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3254,7 +3259,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3264,12 +3269,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,10 +3301,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122832733</v>
+        <v>122832074</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3308,40 +3313,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3350,10 +3346,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529555</v>
+        <v>529610</v>
       </c>
       <c r="R24" t="n">
-        <v>7000270</v>
+        <v>7000425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3381,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3391,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122835601</v>
+        <v>122834941</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3439,38 +3435,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529556</v>
+        <v>529485</v>
       </c>
       <c r="R25" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3507,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3517,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3532,22 +3532,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122844041</v>
+        <v>122844246</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,37 +3560,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529559</v>
+        <v>529543</v>
       </c>
       <c r="R26" t="n">
-        <v>7000333</v>
+        <v>7000331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,7 +3645,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3662,12 +3670,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3685,7 +3693,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122845104</v>
+        <v>122842800</v>
       </c>
       <c r="B27" t="n">
         <v>57478</v>
@@ -3737,13 +3745,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529481</v>
+        <v>529564</v>
       </c>
       <c r="R27" t="n">
-        <v>7000274</v>
+        <v>7000368</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3777,7 +3785,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3796,7 +3804,17 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -3806,7 +3824,7 @@
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3824,7 +3842,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122849927</v>
+        <v>122844745</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3876,13 +3894,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529495</v>
+        <v>529519</v>
       </c>
       <c r="R28" t="n">
-        <v>7000242</v>
+        <v>7000310</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3916,7 +3934,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3973,10 +3991,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122844246</v>
+        <v>122844922</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3989,46 +4007,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529543</v>
+        <v>529490</v>
       </c>
       <c r="R29" t="n">
-        <v>7000331</v>
+        <v>7000318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4065,7 +4078,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,6 +4087,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4084,7 +4098,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4099,12 +4113,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4122,7 +4136,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843609</v>
+        <v>122843242</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -4160,7 +4174,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4174,10 +4188,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529564</v>
+        <v>529586</v>
       </c>
       <c r="R30" t="n">
-        <v>7000340</v>
+        <v>7000356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4214,7 +4228,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4271,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122843718</v>
+        <v>122848070</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4287,46 +4301,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529568</v>
+        <v>529485</v>
       </c>
       <c r="R31" t="n">
-        <v>7000344</v>
+        <v>7000279</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4368,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4372,6 +4377,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4382,7 +4388,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4397,12 +4403,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4420,7 +4426,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122842800</v>
+        <v>122847410</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4458,24 +4464,20 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529564</v>
+        <v>529482</v>
       </c>
       <c r="R32" t="n">
-        <v>7000368</v>
+        <v>7000271</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,7 +4514,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4531,7 +4533,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4569,10 +4571,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122847410</v>
+        <v>122844041</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4585,42 +4587,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529482</v>
+        <v>529559</v>
       </c>
       <c r="R33" t="n">
-        <v>7000271</v>
+        <v>7000333</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4657,7 +4654,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4666,6 +4663,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4676,7 +4674,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4691,12 +4689,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4714,7 +4712,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122850306</v>
+        <v>122843609</v>
       </c>
       <c r="B34" t="n">
         <v>57478</v>
@@ -4766,13 +4764,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529539</v>
+        <v>529564</v>
       </c>
       <c r="R34" t="n">
-        <v>7000235</v>
+        <v>7000340</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4806,7 +4804,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4825,7 +4823,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4838,9 +4836,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4858,7 +4861,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122842399</v>
+        <v>122843718</v>
       </c>
       <c r="B35" t="n">
         <v>57478</v>
@@ -4896,7 +4899,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4910,10 +4913,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529556</v>
+        <v>529568</v>
       </c>
       <c r="R35" t="n">
-        <v>7000374</v>
+        <v>7000344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4950,7 +4953,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5007,10 +5010,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122849991</v>
+        <v>122850162</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5023,40 +5026,49 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529495</v>
+        <v>529529</v>
       </c>
       <c r="R36" t="n">
-        <v>7000242</v>
+        <v>7000221</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5088,13 +5100,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5120,12 +5136,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5143,7 +5159,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122848281</v>
+        <v>122849927</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5181,7 +5197,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5191,17 +5207,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529501</v>
+        <v>529495</v>
       </c>
       <c r="R37" t="n">
-        <v>7000255</v>
+        <v>7000242</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5235,7 +5251,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5269,12 +5285,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5292,10 +5308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122844420</v>
+        <v>122849488</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5308,41 +5324,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529532</v>
+        <v>529504</v>
       </c>
       <c r="R38" t="n">
-        <v>7000325</v>
+        <v>7000251</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5379,7 +5400,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5388,7 +5409,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5414,12 +5434,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5437,7 +5457,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122849488</v>
+        <v>122848281</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5489,10 +5509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529504</v>
+        <v>529501</v>
       </c>
       <c r="R39" t="n">
-        <v>7000251</v>
+        <v>7000255</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5529,7 +5549,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5563,12 +5583,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5586,7 +5606,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122843242</v>
+        <v>122850306</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5624,7 +5644,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5638,13 +5658,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529586</v>
+        <v>529539</v>
       </c>
       <c r="R40" t="n">
-        <v>7000356</v>
+        <v>7000235</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5678,7 +5698,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5697,7 +5717,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5710,14 +5730,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5735,10 +5750,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122844745</v>
+        <v>122849991</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5751,49 +5766,40 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529519</v>
+        <v>529495</v>
       </c>
       <c r="R41" t="n">
-        <v>7000310</v>
+        <v>7000242</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5825,17 +5831,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5861,12 +5863,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5884,7 +5886,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122848017</v>
+        <v>122842399</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5922,7 +5924,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -5936,10 +5938,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529485</v>
+        <v>529556</v>
       </c>
       <c r="R42" t="n">
-        <v>7000279</v>
+        <v>7000374</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5976,7 +5978,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5995,7 +5997,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6033,7 +6035,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122848070</v>
+        <v>122844420</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -6068,18 +6070,22 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529485</v>
+        <v>529532</v>
       </c>
       <c r="R43" t="n">
-        <v>7000279</v>
+        <v>7000325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6116,7 +6122,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6151,12 +6157,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6174,10 +6180,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122844922</v>
+        <v>122848017</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6190,41 +6196,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529490</v>
+        <v>529485</v>
       </c>
       <c r="R44" t="n">
-        <v>7000318</v>
+        <v>7000279</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6261,7 +6272,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6270,7 +6281,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6296,12 +6306,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6319,7 +6329,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122850162</v>
+        <v>122845104</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -6371,13 +6381,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529529</v>
+        <v>529481</v>
       </c>
       <c r="R45" t="n">
-        <v>7000221</v>
+        <v>7000274</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6411,7 +6421,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6433,16 +6443,6 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM45" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -2087,7 +2087,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835059</v>
+        <v>122835601</v>
       </c>
       <c r="B14" t="n">
         <v>74863</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R14" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,19 +2192,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835601</v>
+        <v>122835059</v>
       </c>
       <c r="B15" t="n">
         <v>74863</v>
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R15" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,12 +2309,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122834978</v>
+        <v>122834941</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,31 +3191,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3224,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529514</v>
+        <v>529485</v>
       </c>
       <c r="R23" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3269,12 +3273,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3301,7 +3300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122832074</v>
+        <v>122834978</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3337,7 +3336,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3346,10 +3345,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529610</v>
+        <v>529514</v>
       </c>
       <c r="R24" t="n">
-        <v>7000425</v>
+        <v>7000208</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3381,7 +3380,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3391,12 +3390,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3423,10 +3422,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122834941</v>
+        <v>122832074</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3435,35 +3434,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3472,10 +3467,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529485</v>
+        <v>529610</v>
       </c>
       <c r="R25" t="n">
-        <v>7000239</v>
+        <v>7000425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3507,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3517,7 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4136,10 +4136,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122843242</v>
+        <v>122848070</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4152,46 +4152,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529586</v>
+        <v>529485</v>
       </c>
       <c r="R30" t="n">
-        <v>7000356</v>
+        <v>7000279</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4228,7 +4219,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4237,6 +4228,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4247,7 +4239,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4262,12 +4254,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,10 +4277,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122848070</v>
+        <v>122843242</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4301,37 +4293,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529485</v>
+        <v>529586</v>
       </c>
       <c r="R31" t="n">
-        <v>7000279</v>
+        <v>7000356</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4368,7 +4369,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4377,7 +4378,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122830095</v>
+        <v>122835055</v>
       </c>
       <c r="B4" t="n">
-        <v>57428</v>
+        <v>77709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,47 +921,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102621</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529529</v>
+        <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000102</v>
+        <v>7000239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,9 +982,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835055</v>
+        <v>122834991</v>
       </c>
       <c r="B5" t="n">
-        <v>77709</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R5" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122834991</v>
+        <v>122830095</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1155,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529500</v>
+        <v>529529</v>
       </c>
       <c r="R6" t="n">
-        <v>7000177</v>
+        <v>7000102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,24 +1225,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,12 +1242,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835016</v>
+        <v>122835055</v>
       </c>
       <c r="B2" t="n">
-        <v>90917</v>
+        <v>77709</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529528</v>
+        <v>529555</v>
       </c>
       <c r="R2" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122832599</v>
+        <v>122835079</v>
       </c>
       <c r="B3" t="n">
         <v>78503</v>
@@ -832,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R3" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835055</v>
+        <v>122834978</v>
       </c>
       <c r="B4" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R4" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834991</v>
+        <v>122834884</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R5" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122830095</v>
+        <v>122834838</v>
       </c>
       <c r="B6" t="n">
-        <v>57428</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,47 +1160,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102621</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529529</v>
+        <v>529541</v>
       </c>
       <c r="R6" t="n">
-        <v>7000102</v>
+        <v>7000301</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1225,9 +1221,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122835651</v>
+        <v>122832328</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,34 +1281,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529527</v>
+        <v>529625</v>
       </c>
       <c r="R7" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834962</v>
+        <v>122831851</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1407,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1431,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529555</v>
+        <v>529624</v>
       </c>
       <c r="R8" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1476,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835079</v>
+        <v>122835621</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,21 +1524,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1523,13 +1548,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R9" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1558,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1593,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,22 +1613,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122834862</v>
+        <v>122835601</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,21 +1641,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1640,10 +1665,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529541</v>
+        <v>529556</v>
       </c>
       <c r="R10" t="n">
-        <v>7000301</v>
+        <v>7000147</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1700,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1710,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,22 +1730,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122835637</v>
+        <v>122834862</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,39 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529527</v>
+        <v>529541</v>
       </c>
       <c r="R11" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,12 +1827,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,22 +1847,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122832733</v>
+        <v>122835016</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,52 +1871,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529555</v>
+        <v>529528</v>
       </c>
       <c r="R12" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1944,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122835065</v>
+        <v>122832733</v>
       </c>
       <c r="B13" t="n">
-        <v>77699</v>
+        <v>98365</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1982,28 +1988,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -2013,7 +2033,7 @@
         <v>529555</v>
       </c>
       <c r="R13" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2065,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,12 +2075,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2107,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835601</v>
+        <v>122835637</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,34 +2123,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529556</v>
+        <v>529527</v>
       </c>
       <c r="R14" t="n">
-        <v>7000147</v>
+        <v>7000270</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2187,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2197,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835059</v>
+        <v>122835651</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,21 +2245,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2244,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R15" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2314,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,22 +2329,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122834913</v>
+        <v>122834991</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2337,45 +2357,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R16" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,7 +2416,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2414,12 +2426,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122832328</v>
+        <v>122834941</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2458,35 +2470,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2495,10 +2507,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529625</v>
+        <v>529485</v>
       </c>
       <c r="R17" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,7 +2542,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,12 +2552,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2572,7 +2579,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122835621</v>
+        <v>122835065</v>
       </c>
       <c r="B18" t="n">
         <v>77699</v>
@@ -2612,10 +2619,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R18" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2664,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,12 +2684,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2820,10 +2827,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122831851</v>
+        <v>122835059</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2836,21 +2843,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2860,10 +2867,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R20" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2895,7 +2902,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2905,12 +2912,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,10 +2944,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122834838</v>
+        <v>122832074</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2953,34 +2960,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529541</v>
+        <v>529610</v>
       </c>
       <c r="R21" t="n">
-        <v>7000301</v>
+        <v>7000425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3012,7 +3024,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3022,12 +3034,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3179,10 +3191,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122834941</v>
+        <v>122830095</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>57428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,35 +3203,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3228,10 +3240,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529485</v>
+        <v>529529</v>
       </c>
       <c r="R23" t="n">
-        <v>7000239</v>
+        <v>7000102</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3261,19 +3273,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:20</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3288,19 +3290,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122834978</v>
+        <v>122834913</v>
       </c>
       <c r="B24" t="n">
         <v>57478</v>
@@ -3334,24 +3336,27 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3380,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3390,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3422,10 +3427,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122832074</v>
+        <v>122832599</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3438,39 +3443,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529610</v>
+        <v>529625</v>
       </c>
       <c r="R25" t="n">
-        <v>7000425</v>
+        <v>7000333</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122844246</v>
+        <v>122850162</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529543</v>
+        <v>529529</v>
       </c>
       <c r="R26" t="n">
-        <v>7000331</v>
+        <v>7000221</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3693,10 +3693,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122842800</v>
+        <v>122848070</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,46 +3709,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529564</v>
+        <v>529485</v>
       </c>
       <c r="R27" t="n">
-        <v>7000368</v>
+        <v>7000279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3785,7 +3776,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3794,6 +3785,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3804,7 +3796,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3819,12 +3811,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3842,7 +3834,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844745</v>
+        <v>122843242</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3890,14 +3882,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529519</v>
+        <v>529586</v>
       </c>
       <c r="R28" t="n">
-        <v>7000310</v>
+        <v>7000356</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3934,7 +3926,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3953,7 +3945,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3991,10 +3983,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122844922</v>
+        <v>122848281</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4007,41 +3999,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529490</v>
+        <v>529501</v>
       </c>
       <c r="R29" t="n">
-        <v>7000318</v>
+        <v>7000255</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4078,7 +4075,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4087,7 +4084,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4113,12 +4109,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4136,7 +4132,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122848070</v>
+        <v>122844922</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -4171,18 +4167,22 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529485</v>
+        <v>529490</v>
       </c>
       <c r="R30" t="n">
-        <v>7000279</v>
+        <v>7000318</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122843242</v>
+        <v>122849488</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4315,7 +4315,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529586</v>
+        <v>529504</v>
       </c>
       <c r="R31" t="n">
-        <v>7000356</v>
+        <v>7000251</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4571,7 +4571,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122844041</v>
+        <v>122849991</v>
       </c>
       <c r="B33" t="n">
         <v>78766</v>
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529559</v>
+        <v>529495</v>
       </c>
       <c r="R33" t="n">
-        <v>7000333</v>
+        <v>7000242</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4650,11 +4650,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4674,7 +4669,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -4689,12 +4684,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4712,10 +4707,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122843609</v>
+        <v>122844041</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4728,46 +4723,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529564</v>
+        <v>529559</v>
       </c>
       <c r="R34" t="n">
-        <v>7000340</v>
+        <v>7000333</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4804,7 +4790,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4813,6 +4799,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4838,12 +4825,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4861,10 +4848,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122843718</v>
+        <v>122844420</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4877,46 +4864,41 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529568</v>
+        <v>529532</v>
       </c>
       <c r="R35" t="n">
-        <v>7000344</v>
+        <v>7000325</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4953,7 +4935,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4962,6 +4944,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4972,7 +4955,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4987,12 +4970,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5010,7 +4993,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122850162</v>
+        <v>122844745</v>
       </c>
       <c r="B36" t="n">
         <v>57478</v>
@@ -5048,7 +5031,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5058,14 +5041,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529529</v>
+        <v>529519</v>
       </c>
       <c r="R36" t="n">
-        <v>7000221</v>
+        <v>7000310</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5102,7 +5085,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5159,7 +5142,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122849927</v>
+        <v>122843609</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5197,7 +5180,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5207,17 +5190,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529495</v>
+        <v>529564</v>
       </c>
       <c r="R37" t="n">
-        <v>7000242</v>
+        <v>7000340</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5251,7 +5234,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5270,7 +5253,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5308,7 +5291,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122849488</v>
+        <v>122848017</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5360,10 +5343,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529504</v>
+        <v>529485</v>
       </c>
       <c r="R38" t="n">
-        <v>7000251</v>
+        <v>7000279</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5400,7 +5383,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5457,7 +5440,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122848281</v>
+        <v>122845104</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5509,13 +5492,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529501</v>
+        <v>529481</v>
       </c>
       <c r="R39" t="n">
-        <v>7000255</v>
+        <v>7000274</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5549,7 +5532,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5571,24 +5554,14 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5750,10 +5723,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122849991</v>
+        <v>122843718</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5766,40 +5739,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529495</v>
+        <v>529568</v>
       </c>
       <c r="R41" t="n">
-        <v>7000242</v>
+        <v>7000344</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5831,13 +5813,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5848,7 +5834,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5863,12 +5849,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5886,7 +5872,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122842399</v>
+        <v>122849927</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5934,17 +5920,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529556</v>
+        <v>529495</v>
       </c>
       <c r="R42" t="n">
-        <v>7000374</v>
+        <v>7000242</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5978,7 +5964,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5997,7 +5983,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -6035,10 +6021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122844420</v>
+        <v>122842800</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6051,41 +6037,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529532</v>
+        <v>529564</v>
       </c>
       <c r="R43" t="n">
-        <v>7000325</v>
+        <v>7000368</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6122,7 +6113,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6131,7 +6122,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6142,7 +6132,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6157,12 +6147,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6180,7 +6170,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122848017</v>
+        <v>122844246</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6232,10 +6222,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529485</v>
+        <v>529543</v>
       </c>
       <c r="R44" t="n">
-        <v>7000279</v>
+        <v>7000331</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6272,7 +6262,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6291,7 +6281,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6329,7 +6319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122845104</v>
+        <v>122842399</v>
       </c>
       <c r="B45" t="n">
         <v>57478</v>
@@ -6367,7 +6357,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -6381,13 +6371,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529481</v>
+        <v>529556</v>
       </c>
       <c r="R45" t="n">
-        <v>7000274</v>
+        <v>7000374</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6421,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6440,7 +6430,17 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835055</v>
+        <v>122835059</v>
       </c>
       <c r="B2" t="n">
-        <v>77709</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -765,7 +765,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122835079</v>
+        <v>122835055</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>77709</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,7 +838,7 @@
         <v>7000239</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122834978</v>
+        <v>122834822</v>
       </c>
       <c r="B4" t="n">
         <v>57478</v>
@@ -943,21 +943,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000208</v>
+        <v>7000270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1148,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122834838</v>
+        <v>122834913</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,37 +1167,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R6" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1223,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122832328</v>
+        <v>122835621</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,43 +1292,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529625</v>
+        <v>529556</v>
       </c>
       <c r="R7" t="n">
-        <v>7000333</v>
+        <v>7000147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1361,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1379,22 +1381,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122831851</v>
+        <v>122834991</v>
       </c>
       <c r="B8" t="n">
-        <v>78798</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,21 +1409,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1431,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529624</v>
+        <v>529500</v>
       </c>
       <c r="R8" t="n">
-        <v>7000364</v>
+        <v>7000177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,12 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835621</v>
+        <v>122830095</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>57428</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,38 +1522,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529556</v>
+        <v>529529</v>
       </c>
       <c r="R9" t="n">
-        <v>7000147</v>
+        <v>7000102</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1581,24 +1592,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:39</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,22 +1609,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122835601</v>
+        <v>122832599</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1665,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529556</v>
+        <v>529625</v>
       </c>
       <c r="R10" t="n">
-        <v>7000147</v>
+        <v>7000333</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1700,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1710,12 +1706,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,19 +1726,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834862</v>
+        <v>122835651</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1782,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529541</v>
+        <v>529527</v>
       </c>
       <c r="R11" t="n">
-        <v>7000301</v>
+        <v>7000270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,12 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,22 +1838,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835016</v>
+        <v>122835637</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,38 +1862,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529528</v>
+        <v>529527</v>
       </c>
       <c r="R12" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,12 +1940,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,19 +1960,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122832733</v>
+        <v>122835040</v>
       </c>
       <c r="B13" t="n">
         <v>98365</v>
@@ -2011,7 +2007,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R13" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2061,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,12 +2071,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2107,7 +2103,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835637</v>
+        <v>122834838</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2141,21 +2137,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529527</v>
+        <v>529541</v>
       </c>
       <c r="R14" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2187,7 +2178,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2197,12 +2188,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,19 +2208,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835651</v>
+        <v>122834862</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2269,10 +2260,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529527</v>
+        <v>529541</v>
       </c>
       <c r="R15" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2305,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,22 +2325,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122834991</v>
+        <v>122832733</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2353,38 +2349,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2416,7 +2426,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2426,12 +2436,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122834941</v>
+        <v>122831851</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>78798</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,47 +2480,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529485</v>
+        <v>529624</v>
       </c>
       <c r="R17" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2543,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2552,7 +2553,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2579,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122835065</v>
+        <v>122834978</v>
       </c>
       <c r="B18" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2595,34 +2601,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R18" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2665,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,12 +2675,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2707,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122835040</v>
+        <v>122832074</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,40 +2719,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2750,10 +2752,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529514</v>
+        <v>529610</v>
       </c>
       <c r="R19" t="n">
-        <v>7000177</v>
+        <v>7000425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2785,7 +2787,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2795,12 +2797,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2827,7 +2829,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122835059</v>
+        <v>122835601</v>
       </c>
       <c r="B20" t="n">
         <v>74863</v>
@@ -2867,10 +2869,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R20" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,7 +2904,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2912,12 +2914,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,22 +2934,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122832074</v>
+        <v>122835065</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2960,39 +2962,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529610</v>
+        <v>529555</v>
       </c>
       <c r="R21" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3024,7 +3021,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3034,12 +3031,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,10 +3063,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122834822</v>
+        <v>122832328</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3082,42 +3079,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R22" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3149,7 +3147,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3159,12 +3157,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3191,10 +3189,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122830095</v>
+        <v>122835016</v>
       </c>
       <c r="B23" t="n">
-        <v>57428</v>
+        <v>90917</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3207,43 +3205,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529529</v>
+        <v>529528</v>
       </c>
       <c r="R23" t="n">
-        <v>7000102</v>
+        <v>7000177</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3273,9 +3262,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3290,22 +3294,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122834913</v>
+        <v>122835079</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,32 +3322,24 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -3356,7 +3352,7 @@
         <v>7000239</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3385,7 +3381,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3391,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3427,10 +3423,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122832599</v>
+        <v>122834941</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3439,38 +3435,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529625</v>
+        <v>529485</v>
       </c>
       <c r="R25" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3507,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3517,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122850162</v>
+        <v>122844922</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,46 +3560,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529529</v>
+        <v>529490</v>
       </c>
       <c r="R26" t="n">
-        <v>7000221</v>
+        <v>7000318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3631,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,6 +3640,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3670,12 +3666,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3693,10 +3689,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122848070</v>
+        <v>122849927</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,40 +3705,49 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529485</v>
+        <v>529495</v>
       </c>
       <c r="R27" t="n">
-        <v>7000279</v>
+        <v>7000242</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3776,7 +3781,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3785,7 +3790,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3811,12 +3815,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3834,7 +3838,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122843242</v>
+        <v>122848017</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3872,7 +3876,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3886,10 +3890,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529586</v>
+        <v>529485</v>
       </c>
       <c r="R28" t="n">
-        <v>7000356</v>
+        <v>7000279</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3926,7 +3930,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3945,7 +3949,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3983,7 +3987,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122848281</v>
+        <v>122843718</v>
       </c>
       <c r="B29" t="n">
         <v>57478</v>
@@ -4035,10 +4039,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529501</v>
+        <v>529568</v>
       </c>
       <c r="R29" t="n">
-        <v>7000255</v>
+        <v>7000344</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4075,7 +4079,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4094,7 +4098,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4109,12 +4113,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4132,10 +4136,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122844922</v>
+        <v>122848281</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4148,41 +4152,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529490</v>
+        <v>529501</v>
       </c>
       <c r="R30" t="n">
-        <v>7000318</v>
+        <v>7000255</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4219,7 +4228,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4228,7 +4237,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4254,12 +4262,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4277,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122849488</v>
+        <v>122849991</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4293,49 +4301,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529504</v>
+        <v>529495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000251</v>
+        <v>7000242</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4367,17 +4366,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4403,12 +4398,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4426,7 +4421,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122847410</v>
+        <v>122850162</v>
       </c>
       <c r="B32" t="n">
         <v>57478</v>
@@ -4464,20 +4459,24 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529482</v>
+        <v>529529</v>
       </c>
       <c r="R32" t="n">
-        <v>7000271</v>
+        <v>7000221</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4514,7 +4513,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4571,10 +4570,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122849991</v>
+        <v>122849488</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4587,40 +4586,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529495</v>
+        <v>529504</v>
       </c>
       <c r="R33" t="n">
-        <v>7000242</v>
+        <v>7000251</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4652,13 +4660,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4684,12 +4696,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4707,10 +4719,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122844041</v>
+        <v>122843242</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4723,37 +4735,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529559</v>
+        <v>529586</v>
       </c>
       <c r="R34" t="n">
-        <v>7000333</v>
+        <v>7000356</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4790,7 +4811,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4799,7 +4820,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4825,12 +4845,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4848,10 +4868,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122844420</v>
+        <v>122850306</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4864,44 +4884,49 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529532</v>
+        <v>529539</v>
       </c>
       <c r="R35" t="n">
-        <v>7000325</v>
+        <v>7000235</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4935,7 +4960,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4944,7 +4969,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4968,14 +4992,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4993,10 +5012,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122844745</v>
+        <v>122844420</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5009,46 +5028,41 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529519</v>
+        <v>529532</v>
       </c>
       <c r="R36" t="n">
-        <v>7000310</v>
+        <v>7000325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5085,7 +5099,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5094,6 +5108,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5119,12 +5134,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5142,7 +5157,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843609</v>
+        <v>122842399</v>
       </c>
       <c r="B37" t="n">
         <v>57478</v>
@@ -5180,7 +5195,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5194,10 +5209,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529564</v>
+        <v>529556</v>
       </c>
       <c r="R37" t="n">
-        <v>7000340</v>
+        <v>7000374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5234,7 +5249,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5291,7 +5306,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122848017</v>
+        <v>122844745</v>
       </c>
       <c r="B38" t="n">
         <v>57478</v>
@@ -5329,7 +5344,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5339,14 +5354,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529485</v>
+        <v>529519</v>
       </c>
       <c r="R38" t="n">
-        <v>7000279</v>
+        <v>7000310</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5383,7 +5398,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5440,7 +5455,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122845104</v>
+        <v>122843609</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5492,13 +5507,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529481</v>
+        <v>529564</v>
       </c>
       <c r="R39" t="n">
-        <v>7000274</v>
+        <v>7000340</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5532,7 +5547,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5551,7 +5566,17 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -5561,7 +5586,7 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5579,7 +5604,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122850306</v>
+        <v>122844246</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5631,13 +5656,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529539</v>
+        <v>529543</v>
       </c>
       <c r="R40" t="n">
-        <v>7000235</v>
+        <v>7000331</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5671,7 +5696,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5690,7 +5715,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5703,9 +5728,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5723,10 +5753,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122843718</v>
+        <v>122844041</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5739,46 +5769,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529568</v>
+        <v>529559</v>
       </c>
       <c r="R41" t="n">
-        <v>7000344</v>
+        <v>7000333</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5815,7 +5836,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5824,6 +5845,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5849,12 +5871,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5872,7 +5894,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122849927</v>
+        <v>122847410</v>
       </c>
       <c r="B42" t="n">
         <v>57478</v>
@@ -5913,24 +5935,20 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529495</v>
+        <v>529482</v>
       </c>
       <c r="R42" t="n">
-        <v>7000242</v>
+        <v>7000271</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5964,7 +5982,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6170,7 +6188,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122844246</v>
+        <v>122845104</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -6222,13 +6240,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529543</v>
+        <v>529481</v>
       </c>
       <c r="R44" t="n">
-        <v>7000331</v>
+        <v>7000274</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6281,17 +6299,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -6301,7 +6309,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6319,10 +6327,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122842399</v>
+        <v>122848070</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6335,46 +6343,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529556</v>
+        <v>529485</v>
       </c>
       <c r="R45" t="n">
-        <v>7000374</v>
+        <v>7000279</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6411,7 +6410,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6420,6 +6419,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -6445,12 +6445,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122835055</v>
+        <v>122834822</v>
       </c>
       <c r="B3" t="n">
-        <v>77709</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,24 +808,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -835,7 +843,7 @@
         <v>529555</v>
       </c>
       <c r="R3" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +885,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122834822</v>
+        <v>122835055</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>77709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,32 +933,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -960,7 +960,7 @@
         <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122835040</v>
+        <v>122834838</v>
       </c>
       <c r="B13" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,52 +1984,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529514</v>
+        <v>529541</v>
       </c>
       <c r="R13" t="n">
-        <v>7000177</v>
+        <v>7000301</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2061,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2071,12 +2057,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122834838</v>
+        <v>122835040</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,38 +2101,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529541</v>
+        <v>529514</v>
       </c>
       <c r="R14" t="n">
-        <v>7000301</v>
+        <v>7000177</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2468,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122831851</v>
+        <v>122835601</v>
       </c>
       <c r="B17" t="n">
-        <v>78798</v>
+        <v>74863</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,21 +2484,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529624</v>
+        <v>529556</v>
       </c>
       <c r="R17" t="n">
-        <v>7000364</v>
+        <v>7000147</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2573,22 +2573,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122834978</v>
+        <v>122831851</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78798</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2601,39 +2601,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529514</v>
+        <v>529624</v>
       </c>
       <c r="R18" t="n">
-        <v>7000208</v>
+        <v>7000364</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,7 +2660,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2675,12 +2670,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2707,7 +2702,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122832074</v>
+        <v>122834978</v>
       </c>
       <c r="B19" t="n">
         <v>57478</v>
@@ -2743,7 +2738,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2752,10 +2747,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529610</v>
+        <v>529514</v>
       </c>
       <c r="R19" t="n">
-        <v>7000425</v>
+        <v>7000208</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2787,7 +2782,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2797,12 +2792,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2829,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122835601</v>
+        <v>122832074</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2845,34 +2840,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529556</v>
+        <v>529610</v>
       </c>
       <c r="R20" t="n">
-        <v>7000147</v>
+        <v>7000425</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2934,12 +2934,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122849991</v>
+        <v>122850162</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4301,40 +4301,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529495</v>
+        <v>529529</v>
       </c>
       <c r="R31" t="n">
-        <v>7000242</v>
+        <v>7000221</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4366,13 +4375,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4398,12 +4411,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,10 +4434,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850162</v>
+        <v>122849991</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4437,49 +4450,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529529</v>
+        <v>529495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000221</v>
+        <v>7000242</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4511,17 +4515,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -4285,10 +4285,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850162</v>
+        <v>122849991</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4301,49 +4301,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529529</v>
+        <v>529495</v>
       </c>
       <c r="R31" t="n">
-        <v>7000221</v>
+        <v>7000242</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4375,17 +4366,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4411,12 +4398,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4434,10 +4421,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122849991</v>
+        <v>122850162</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4450,40 +4437,49 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529495</v>
+        <v>529529</v>
       </c>
       <c r="R32" t="n">
-        <v>7000242</v>
+        <v>7000221</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4515,13 +4511,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122835059</v>
+        <v>122834838</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R2" t="n">
-        <v>7000239</v>
+        <v>7000301</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122834822</v>
+        <v>122832733</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,36 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -875,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122835055</v>
+        <v>122831851</v>
       </c>
       <c r="B4" t="n">
-        <v>77709</v>
+        <v>78801</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +939,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>314</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529555</v>
+        <v>529624</v>
       </c>
       <c r="R4" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834884</v>
+        <v>122835055</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>77712</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,21 +1056,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1109,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122834913</v>
+        <v>122835079</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,32 +1173,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1205,7 +1203,7 @@
         <v>7000239</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1234,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122835621</v>
+        <v>122834913</v>
       </c>
       <c r="B7" t="n">
-        <v>77699</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,37 +1290,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R7" t="n">
-        <v>7000147</v>
+        <v>7000239</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1361,12 +1367,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,22 +1387,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834991</v>
+        <v>122835065</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>77702</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,21 +1415,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1433,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R8" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1484,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1510,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122830095</v>
+        <v>122835651</v>
       </c>
       <c r="B9" t="n">
-        <v>57428</v>
+        <v>79850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,47 +1528,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529529</v>
+        <v>529527</v>
       </c>
       <c r="R9" t="n">
-        <v>7000102</v>
+        <v>7000270</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1592,9 +1589,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,22 +1616,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832599</v>
+        <v>122835040</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,38 +1640,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529625</v>
+        <v>529514</v>
       </c>
       <c r="R10" t="n">
-        <v>7000333</v>
+        <v>7000177</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,12 +1727,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1759,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122835651</v>
+        <v>122834978</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,34 +1775,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529527</v>
+        <v>529514</v>
       </c>
       <c r="R11" t="n">
-        <v>7000270</v>
+        <v>7000208</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1823,7 +1849,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,22 +1869,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835637</v>
+        <v>122835016</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>90920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,43 +1893,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529527</v>
+        <v>529528</v>
       </c>
       <c r="R12" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1956,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,12 +1966,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,22 +1986,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122834838</v>
+        <v>122834941</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1984,38 +2010,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529541</v>
+        <v>529485</v>
       </c>
       <c r="R13" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,12 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2119,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122835040</v>
+        <v>122834822</v>
       </c>
       <c r="B14" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,52 +2131,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R14" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,7 +2202,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2188,12 +2212,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122834862</v>
+        <v>122834884</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,10 +2284,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529541</v>
+        <v>529555</v>
       </c>
       <c r="R15" t="n">
-        <v>7000301</v>
+        <v>7000239</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2319,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2329,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2337,10 +2361,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122832733</v>
+        <v>122832328</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,40 +2373,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2391,10 +2410,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R16" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,7 +2445,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2436,12 +2455,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2468,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122835601</v>
+        <v>122835621</v>
       </c>
       <c r="B17" t="n">
-        <v>74863</v>
+        <v>77702</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,21 +2503,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2585,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122831851</v>
+        <v>122830095</v>
       </c>
       <c r="B18" t="n">
-        <v>78798</v>
+        <v>57431</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,38 +2616,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>102621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529624</v>
+        <v>529529</v>
       </c>
       <c r="R18" t="n">
-        <v>7000364</v>
+        <v>7000102</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2658,24 +2686,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,22 +2703,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122834978</v>
+        <v>122832074</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2738,7 +2751,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2747,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529514</v>
+        <v>529610</v>
       </c>
       <c r="R19" t="n">
-        <v>7000208</v>
+        <v>7000425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2782,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2792,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2824,10 +2837,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122832074</v>
+        <v>122834991</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,39 +2853,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529610</v>
+        <v>529500</v>
       </c>
       <c r="R20" t="n">
-        <v>7000425</v>
+        <v>7000177</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2904,7 +2912,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2914,12 +2922,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,10 +2954,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122835065</v>
+        <v>122832599</v>
       </c>
       <c r="B21" t="n">
-        <v>77699</v>
+        <v>78506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2962,21 +2970,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2986,10 +2994,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R21" t="n">
-        <v>7000239</v>
+        <v>7000333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3031,12 +3039,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,10 +3071,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122832328</v>
+        <v>122834862</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,43 +3087,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529625</v>
+        <v>529541</v>
       </c>
       <c r="R22" t="n">
-        <v>7000333</v>
+        <v>7000301</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3147,7 +3146,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3157,12 +3156,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,10 +3188,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835016</v>
+        <v>122835601</v>
       </c>
       <c r="B23" t="n">
-        <v>90917</v>
+        <v>74866</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3201,25 +3200,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3229,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529528</v>
+        <v>529556</v>
       </c>
       <c r="R23" t="n">
-        <v>7000177</v>
+        <v>7000147</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3264,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3274,12 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,22 +3293,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835079</v>
+        <v>122835637</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,37 +3321,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R24" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S24" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3381,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3391,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,22 +3415,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122834941</v>
+        <v>122835059</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>74866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3435,44 +3439,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529485</v>
+        <v>529555</v>
       </c>
       <c r="R25" t="n">
         <v>7000239</v>
@@ -3507,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3517,7 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122844922</v>
+        <v>122848070</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3579,22 +3579,18 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529490</v>
+        <v>529485</v>
       </c>
       <c r="R26" t="n">
-        <v>7000318</v>
+        <v>7000279</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3631,7 +3627,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3666,12 +3662,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3689,10 +3685,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122849927</v>
+        <v>122843242</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3737,17 +3733,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529495</v>
+        <v>529586</v>
       </c>
       <c r="R27" t="n">
-        <v>7000242</v>
+        <v>7000356</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3781,7 +3777,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3800,7 +3796,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3838,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122848017</v>
+        <v>122844041</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3854,46 +3850,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529485</v>
+        <v>529559</v>
       </c>
       <c r="R28" t="n">
-        <v>7000279</v>
+        <v>7000333</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3930,7 +3917,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3939,6 +3926,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3949,7 +3937,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -3964,12 +3952,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3987,10 +3975,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122843718</v>
+        <v>122844922</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4003,46 +3991,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529568</v>
+        <v>529490</v>
       </c>
       <c r="R29" t="n">
-        <v>7000344</v>
+        <v>7000318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4079,7 +4062,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4088,6 +4071,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4098,7 +4082,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4113,12 +4097,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4136,10 +4120,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122848281</v>
+        <v>122845104</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4188,13 +4172,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529501</v>
+        <v>529481</v>
       </c>
       <c r="R30" t="n">
-        <v>7000255</v>
+        <v>7000274</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4228,7 +4212,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,24 +4234,14 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4285,10 +4259,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122849991</v>
+        <v>122842399</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4301,40 +4275,49 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529495</v>
+        <v>529556</v>
       </c>
       <c r="R31" t="n">
-        <v>7000242</v>
+        <v>7000374</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4366,13 +4349,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4383,7 +4370,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4398,12 +4385,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4421,10 +4408,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122850162</v>
+        <v>122849991</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4437,49 +4424,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529529</v>
+        <v>529495</v>
       </c>
       <c r="R32" t="n">
-        <v>7000221</v>
+        <v>7000242</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4511,17 +4489,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4547,12 +4521,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4570,10 +4544,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122849488</v>
+        <v>122848017</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4622,10 +4596,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529504</v>
+        <v>529485</v>
       </c>
       <c r="R33" t="n">
-        <v>7000251</v>
+        <v>7000279</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4662,7 +4636,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4719,10 +4693,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122843242</v>
+        <v>122844745</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4767,14 +4741,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529586</v>
+        <v>529519</v>
       </c>
       <c r="R34" t="n">
-        <v>7000356</v>
+        <v>7000310</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4811,7 +4785,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4830,7 +4804,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4868,10 +4842,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122850306</v>
+        <v>122849488</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4920,13 +4894,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529539</v>
+        <v>529504</v>
       </c>
       <c r="R35" t="n">
-        <v>7000235</v>
+        <v>7000251</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4960,7 +4934,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4992,9 +4966,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5012,10 +4991,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122844420</v>
+        <v>122842800</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5028,41 +5007,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529532</v>
+        <v>529564</v>
       </c>
       <c r="R36" t="n">
-        <v>7000325</v>
+        <v>7000368</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5099,7 +5083,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5108,7 +5092,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5119,7 +5102,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -5134,12 +5117,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5157,10 +5140,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122842399</v>
+        <v>122843718</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5195,7 +5178,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5209,10 +5192,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529556</v>
+        <v>529568</v>
       </c>
       <c r="R37" t="n">
-        <v>7000374</v>
+        <v>7000344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5249,7 +5232,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5306,10 +5289,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122844745</v>
+        <v>122847410</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5347,21 +5330,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529519</v>
+        <v>529482</v>
       </c>
       <c r="R38" t="n">
-        <v>7000310</v>
+        <v>7000271</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5455,10 +5434,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122843609</v>
+        <v>122844246</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5507,10 +5486,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529564</v>
+        <v>529543</v>
       </c>
       <c r="R39" t="n">
-        <v>7000340</v>
+        <v>7000331</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5547,7 +5526,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5604,10 +5583,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122844246</v>
+        <v>122843609</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5656,10 +5635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529543</v>
+        <v>529564</v>
       </c>
       <c r="R40" t="n">
-        <v>7000331</v>
+        <v>7000340</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5696,7 +5675,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5753,10 +5732,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122844041</v>
+        <v>122849927</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5769,40 +5748,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529559</v>
+        <v>529495</v>
       </c>
       <c r="R41" t="n">
-        <v>7000333</v>
+        <v>7000242</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5836,7 +5824,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5845,7 +5833,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5856,7 +5843,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -5871,12 +5858,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5894,10 +5881,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122847410</v>
+        <v>122850162</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5932,20 +5919,24 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529482</v>
+        <v>529529</v>
       </c>
       <c r="R42" t="n">
-        <v>7000271</v>
+        <v>7000221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5982,7 +5973,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6039,10 +6030,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122842800</v>
+        <v>122844420</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6055,46 +6046,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529564</v>
+        <v>529532</v>
       </c>
       <c r="R43" t="n">
-        <v>7000368</v>
+        <v>7000325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6131,7 +6117,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6140,6 +6126,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6150,7 +6137,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6165,12 +6152,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6188,10 +6175,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122845104</v>
+        <v>122850306</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6240,10 +6227,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529481</v>
+        <v>529539</v>
       </c>
       <c r="R44" t="n">
-        <v>7000274</v>
+        <v>7000235</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6280,7 +6267,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6302,14 +6289,19 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6327,10 +6319,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122848070</v>
+        <v>122848281</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6343,37 +6335,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529485</v>
+        <v>529501</v>
       </c>
       <c r="R45" t="n">
-        <v>7000279</v>
+        <v>7000255</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6410,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6419,7 +6420,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6445,12 +6445,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122834838</v>
+        <v>122834978</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529541</v>
+        <v>529514</v>
       </c>
       <c r="R2" t="n">
-        <v>7000301</v>
+        <v>7000208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122832733</v>
+        <v>122834862</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,52 +809,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R3" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122831851</v>
+        <v>122834884</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529624</v>
+        <v>529555</v>
       </c>
       <c r="R4" t="n">
-        <v>7000364</v>
+        <v>7000239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122835055</v>
+        <v>122834941</v>
       </c>
       <c r="B5" t="n">
-        <v>77712</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,35 +1043,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529555</v>
+        <v>529485</v>
       </c>
       <c r="R5" t="n">
         <v>7000239</v>
@@ -1115,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835079</v>
+        <v>122835059</v>
       </c>
       <c r="B6" t="n">
-        <v>78506</v>
+        <v>74866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1168,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,7 +1198,7 @@
         <v>7000239</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122834913</v>
+        <v>122831851</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>78803</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,45 +1285,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529555</v>
+        <v>529624</v>
       </c>
       <c r="R7" t="n">
-        <v>7000239</v>
+        <v>7000364</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,12 +1354,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122835065</v>
+        <v>122834991</v>
       </c>
       <c r="B8" t="n">
-        <v>77702</v>
+        <v>79852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,21 +1402,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529555</v>
+        <v>529500</v>
       </c>
       <c r="R8" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835651</v>
+        <v>122835040</v>
       </c>
       <c r="B9" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,38 +1515,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529527</v>
+        <v>529514</v>
       </c>
       <c r="R9" t="n">
-        <v>7000270</v>
+        <v>7000177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1591,7 +1592,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1601,7 +1602,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,22 +1622,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122835040</v>
+        <v>122832328</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,40 +1646,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1682,10 +1683,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529514</v>
+        <v>529625</v>
       </c>
       <c r="R10" t="n">
-        <v>7000177</v>
+        <v>7000333</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1717,7 +1718,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,12 +1728,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På marken i gammal skog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122834978</v>
+        <v>122835601</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,39 +1776,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529514</v>
+        <v>529556</v>
       </c>
       <c r="R11" t="n">
-        <v>7000208</v>
+        <v>7000147</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1839,7 +1835,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,12 +1845,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,22 +1865,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835016</v>
+        <v>122835637</v>
       </c>
       <c r="B12" t="n">
-        <v>90920</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,38 +1889,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529528</v>
+        <v>529527</v>
       </c>
       <c r="R12" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1956,7 +1957,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1966,12 +1967,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,22 +1987,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122834941</v>
+        <v>122834822</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2010,47 +2011,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529485</v>
+        <v>529555</v>
       </c>
       <c r="R13" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2092,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2119,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122834822</v>
+        <v>122834838</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,42 +2140,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529555</v>
+        <v>529541</v>
       </c>
       <c r="R14" t="n">
-        <v>7000270</v>
+        <v>7000301</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2202,7 +2199,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,12 +2209,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,10 +2241,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122834884</v>
+        <v>122835079</v>
       </c>
       <c r="B15" t="n">
-        <v>79850</v>
+        <v>78508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,21 +2257,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2290,7 +2287,7 @@
         <v>7000239</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2319,7 +2316,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2329,12 +2326,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2361,10 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122832328</v>
+        <v>122835065</v>
       </c>
       <c r="B16" t="n">
-        <v>78769</v>
+        <v>77704</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2377,43 +2374,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R16" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,7 +2433,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2455,12 +2443,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,7 +2478,7 @@
         <v>122835621</v>
       </c>
       <c r="B17" t="n">
-        <v>77702</v>
+        <v>77704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2604,10 +2592,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122830095</v>
+        <v>122835651</v>
       </c>
       <c r="B18" t="n">
-        <v>57431</v>
+        <v>79852</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2616,47 +2604,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529529</v>
+        <v>529527</v>
       </c>
       <c r="R18" t="n">
-        <v>7000102</v>
+        <v>7000270</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2686,9 +2665,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,22 +2692,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122832074</v>
+        <v>122832599</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>78508</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2731,39 +2720,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529610</v>
+        <v>529625</v>
       </c>
       <c r="R19" t="n">
-        <v>7000425</v>
+        <v>7000333</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2795,7 +2779,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2789,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2837,10 +2821,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122834991</v>
+        <v>122832733</v>
       </c>
       <c r="B20" t="n">
-        <v>79850</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2849,38 +2833,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529500</v>
+        <v>529555</v>
       </c>
       <c r="R20" t="n">
-        <v>7000177</v>
+        <v>7000270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2912,7 +2910,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2922,12 +2920,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,10 +2952,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122832599</v>
+        <v>122834913</v>
       </c>
       <c r="B21" t="n">
-        <v>78506</v>
+        <v>57481</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,37 +2968,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R21" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3029,7 +3035,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3039,12 +3045,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3071,10 +3077,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122834862</v>
+        <v>122830095</v>
       </c>
       <c r="B22" t="n">
-        <v>79850</v>
+        <v>57431</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3083,38 +3089,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529541</v>
+        <v>529529</v>
       </c>
       <c r="R22" t="n">
-        <v>7000301</v>
+        <v>7000102</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3144,24 +3159,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,22 +3176,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835601</v>
+        <v>122835016</v>
       </c>
       <c r="B23" t="n">
-        <v>74866</v>
+        <v>90922</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3200,25 +3200,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529556</v>
+        <v>529528</v>
       </c>
       <c r="R23" t="n">
-        <v>7000147</v>
+        <v>7000177</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3293,22 +3293,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835637</v>
+        <v>122835055</v>
       </c>
       <c r="B24" t="n">
-        <v>78769</v>
+        <v>77714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3321,39 +3321,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R24" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3385,7 +3380,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3395,12 +3390,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3415,22 +3410,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122835059</v>
+        <v>122832074</v>
       </c>
       <c r="B25" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3443,34 +3438,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529555</v>
+        <v>529610</v>
       </c>
       <c r="R25" t="n">
-        <v>7000239</v>
+        <v>7000425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,10 +3544,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122848070</v>
+        <v>122843609</v>
       </c>
       <c r="B26" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3560,37 +3560,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529485</v>
+        <v>529564</v>
       </c>
       <c r="R26" t="n">
-        <v>7000279</v>
+        <v>7000340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,7 +3645,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -3662,12 +3670,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3685,10 +3693,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122843242</v>
+        <v>122848070</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3701,46 +3709,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529586</v>
+        <v>529485</v>
       </c>
       <c r="R27" t="n">
-        <v>7000356</v>
+        <v>7000279</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3777,7 +3776,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3786,6 +3785,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3834,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844041</v>
+        <v>122844246</v>
       </c>
       <c r="B28" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3850,37 +3850,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529559</v>
+        <v>529543</v>
       </c>
       <c r="R28" t="n">
-        <v>7000333</v>
+        <v>7000331</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3917,7 +3926,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3926,7 +3935,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3952,12 +3960,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3975,10 +3983,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122844922</v>
+        <v>122849488</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3991,41 +3999,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529490</v>
+        <v>529504</v>
       </c>
       <c r="R29" t="n">
-        <v>7000318</v>
+        <v>7000251</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4062,7 +4075,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,7 +4084,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4097,12 +4109,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4120,7 +4132,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122845104</v>
+        <v>122842800</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -4172,13 +4184,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529481</v>
+        <v>529564</v>
       </c>
       <c r="R30" t="n">
-        <v>7000274</v>
+        <v>7000368</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4212,7 +4224,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4231,7 +4243,17 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4241,7 +4263,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4259,7 +4281,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122842399</v>
+        <v>122850306</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -4297,7 +4319,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4311,13 +4333,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529556</v>
+        <v>529539</v>
       </c>
       <c r="R31" t="n">
-        <v>7000374</v>
+        <v>7000235</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4351,7 +4373,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4370,7 +4392,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4383,14 +4405,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4408,10 +4425,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122849991</v>
+        <v>122849927</v>
       </c>
       <c r="B32" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4424,27 +4441,36 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
@@ -4489,13 +4515,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4521,12 +4551,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4544,7 +4574,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122848017</v>
+        <v>122847410</v>
       </c>
       <c r="B33" t="n">
         <v>57481</v>
@@ -4582,24 +4612,20 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529485</v>
+        <v>529482</v>
       </c>
       <c r="R33" t="n">
-        <v>7000279</v>
+        <v>7000271</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4636,7 +4662,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4842,7 +4868,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122849488</v>
+        <v>122843718</v>
       </c>
       <c r="B35" t="n">
         <v>57481</v>
@@ -4894,10 +4920,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529504</v>
+        <v>529568</v>
       </c>
       <c r="R35" t="n">
-        <v>7000251</v>
+        <v>7000344</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4934,7 +4960,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4953,7 +4979,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4991,10 +5017,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122842800</v>
+        <v>122844041</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5007,46 +5033,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529564</v>
+        <v>529559</v>
       </c>
       <c r="R36" t="n">
-        <v>7000368</v>
+        <v>7000333</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5083,7 +5100,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5092,6 +5109,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5117,12 +5135,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5140,7 +5158,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122843718</v>
+        <v>122848017</v>
       </c>
       <c r="B37" t="n">
         <v>57481</v>
@@ -5192,10 +5210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529568</v>
+        <v>529485</v>
       </c>
       <c r="R37" t="n">
-        <v>7000344</v>
+        <v>7000279</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5232,7 +5250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5251,7 +5269,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5289,10 +5307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122847410</v>
+        <v>122849991</v>
       </c>
       <c r="B38" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5305,45 +5323,40 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529482</v>
+        <v>529495</v>
       </c>
       <c r="R38" t="n">
-        <v>7000271</v>
+        <v>7000242</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5375,17 +5388,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5411,12 +5420,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5434,7 +5443,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122844246</v>
+        <v>122842399</v>
       </c>
       <c r="B39" t="n">
         <v>57481</v>
@@ -5472,7 +5481,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5486,10 +5495,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529543</v>
+        <v>529556</v>
       </c>
       <c r="R39" t="n">
-        <v>7000331</v>
+        <v>7000374</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5526,7 +5535,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5583,7 +5592,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122843609</v>
+        <v>122848281</v>
       </c>
       <c r="B40" t="n">
         <v>57481</v>
@@ -5635,10 +5644,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529564</v>
+        <v>529501</v>
       </c>
       <c r="R40" t="n">
-        <v>7000340</v>
+        <v>7000255</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5675,7 +5684,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5694,7 +5703,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5709,12 +5718,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5732,10 +5741,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122849927</v>
+        <v>122844420</v>
       </c>
       <c r="B41" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5748,49 +5757,44 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529495</v>
+        <v>529532</v>
       </c>
       <c r="R41" t="n">
-        <v>7000242</v>
+        <v>7000325</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5833,6 +5837,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5858,12 +5863,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6030,10 +6035,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122844420</v>
+        <v>122843242</v>
       </c>
       <c r="B43" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6046,41 +6051,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529532</v>
+        <v>529586</v>
       </c>
       <c r="R43" t="n">
-        <v>7000325</v>
+        <v>7000356</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6117,7 +6127,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6126,7 +6136,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6137,7 +6146,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -6152,12 +6161,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6175,10 +6184,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122850306</v>
+        <v>122844922</v>
       </c>
       <c r="B44" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6191,49 +6200,44 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529539</v>
+        <v>529490</v>
       </c>
       <c r="R44" t="n">
-        <v>7000235</v>
+        <v>7000318</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6267,7 +6271,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6276,6 +6280,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6299,9 +6304,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6319,7 +6329,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122848281</v>
+        <v>122845104</v>
       </c>
       <c r="B45" t="n">
         <v>57481</v>
@@ -6371,13 +6381,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529501</v>
+        <v>529481</v>
       </c>
       <c r="R45" t="n">
-        <v>7000255</v>
+        <v>7000274</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6411,7 +6421,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6433,24 +6443,14 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122834884</v>
+        <v>122834941</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,35 +926,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529555</v>
+        <v>529485</v>
       </c>
       <c r="R4" t="n">
         <v>7000239</v>
@@ -989,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:14</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122834941</v>
+        <v>122834884</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,44 +1047,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529485</v>
+        <v>529555</v>
       </c>
       <c r="R5" t="n">
         <v>7000239</v>
@@ -1115,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122834978</v>
+        <v>122834913</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -709,24 +709,27 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529514</v>
+        <v>529555</v>
       </c>
       <c r="R2" t="n">
-        <v>7000208</v>
+        <v>7000239</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +768,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122834862</v>
+        <v>122834991</v>
       </c>
       <c r="B3" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529541</v>
+        <v>529500</v>
       </c>
       <c r="R3" t="n">
-        <v>7000301</v>
+        <v>7000177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122834941</v>
+        <v>122835016</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>90928</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,47 +929,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529485</v>
+        <v>529528</v>
       </c>
       <c r="R4" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1002,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1037,7 @@
         <v>122834884</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1152,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122835059</v>
+        <v>122834822</v>
       </c>
       <c r="B6" t="n">
-        <v>74866</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,24 +1167,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
@@ -1195,7 +1202,7 @@
         <v>529555</v>
       </c>
       <c r="R6" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1244,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Färska och äldre ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1276,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122831851</v>
+        <v>122834862</v>
       </c>
       <c r="B7" t="n">
-        <v>78803</v>
+        <v>79853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,21 +1292,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1316,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529624</v>
+        <v>529541</v>
       </c>
       <c r="R7" t="n">
-        <v>7000364</v>
+        <v>7000301</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1351,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1361,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122834991</v>
+        <v>122835621</v>
       </c>
       <c r="B8" t="n">
-        <v>79852</v>
+        <v>77705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,21 +1409,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1426,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529500</v>
+        <v>529556</v>
       </c>
       <c r="R8" t="n">
-        <v>7000177</v>
+        <v>7000147</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1498,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122835040</v>
+        <v>122830095</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,40 +1522,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1557,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529514</v>
+        <v>529529</v>
       </c>
       <c r="R9" t="n">
-        <v>7000177</v>
+        <v>7000102</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,24 +1592,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,22 +1609,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122832328</v>
+        <v>122834838</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1667,26 +1654,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529625</v>
+        <v>529541</v>
       </c>
       <c r="R10" t="n">
-        <v>7000333</v>
+        <v>7000301</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1728,7 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1760,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122835601</v>
+        <v>122832733</v>
       </c>
       <c r="B11" t="n">
-        <v>74866</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,38 +1750,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529556</v>
+        <v>529555</v>
       </c>
       <c r="R11" t="n">
-        <v>7000147</v>
+        <v>7000270</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,7 +1827,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1845,12 +1837,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>I gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1865,22 +1857,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122835637</v>
+        <v>122835065</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>77705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,39 +1885,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529527</v>
+        <v>529555</v>
       </c>
       <c r="R12" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1957,7 +1944,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1967,12 +1954,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Med apothecier, på gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1987,19 +1974,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122834822</v>
+        <v>122832074</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -2033,24 +2020,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529555</v>
+        <v>529610</v>
       </c>
       <c r="R13" t="n">
-        <v>7000270</v>
+        <v>7000425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2066,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2076,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2124,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122834838</v>
+        <v>122831851</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>78804</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,21 +2124,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2164,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529541</v>
+        <v>529624</v>
       </c>
       <c r="R14" t="n">
-        <v>7000301</v>
+        <v>7000364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2199,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2209,12 +2193,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2234,17 +2218,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122835079</v>
+        <v>122835601</v>
       </c>
       <c r="B15" t="n">
-        <v>78508</v>
+        <v>74866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,21 +2241,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2281,13 +2265,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529555</v>
+        <v>529556</v>
       </c>
       <c r="R15" t="n">
-        <v>7000239</v>
+        <v>7000147</v>
       </c>
       <c r="S15" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2316,7 +2300,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2326,12 +2310,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,22 +2330,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122835065</v>
+        <v>122835651</v>
       </c>
       <c r="B16" t="n">
-        <v>77704</v>
+        <v>79853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2374,21 +2358,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2398,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529555</v>
+        <v>529527</v>
       </c>
       <c r="R16" t="n">
-        <v>7000239</v>
+        <v>7000270</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2433,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2443,12 +2427,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2463,22 +2442,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122835621</v>
+        <v>122835637</v>
       </c>
       <c r="B17" t="n">
-        <v>77704</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2491,34 +2470,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529556</v>
+        <v>529527</v>
       </c>
       <c r="R17" t="n">
-        <v>7000147</v>
+        <v>7000270</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2550,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2560,12 +2544,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Med apothecier, på gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2592,10 +2576,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122835651</v>
+        <v>122834941</v>
       </c>
       <c r="B18" t="n">
-        <v>79852</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,38 +2588,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529527</v>
+        <v>529485</v>
       </c>
       <c r="R18" t="n">
-        <v>7000270</v>
+        <v>7000239</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,7 +2660,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2677,7 +2670,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2685,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122832599</v>
+        <v>122835055</v>
       </c>
       <c r="B19" t="n">
-        <v>78508</v>
+        <v>77715</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2720,21 +2713,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,10 +2737,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529625</v>
+        <v>529555</v>
       </c>
       <c r="R19" t="n">
-        <v>7000333</v>
+        <v>7000239</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2779,7 +2772,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2789,12 +2782,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På kolad ved på grov gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2821,10 +2814,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122832733</v>
+        <v>122832328</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2833,40 +2826,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2875,10 +2863,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529555</v>
+        <v>529625</v>
       </c>
       <c r="R20" t="n">
-        <v>7000270</v>
+        <v>7000333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2910,7 +2898,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2920,12 +2908,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2952,7 +2940,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122834913</v>
+        <v>122834978</v>
       </c>
       <c r="B21" t="n">
         <v>57481</v>
@@ -2986,27 +2974,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R21" t="n">
-        <v>7000239</v>
+        <v>7000208</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3035,7 +3020,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3045,12 +3030,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på gammal gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3077,10 +3062,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122830095</v>
+        <v>122832599</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>78509</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3089,47 +3074,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529529</v>
+        <v>529625</v>
       </c>
       <c r="R22" t="n">
-        <v>7000102</v>
+        <v>7000333</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,9 +3135,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3176,22 +3167,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122835016</v>
+        <v>122835079</v>
       </c>
       <c r="B23" t="n">
-        <v>90922</v>
+        <v>78509</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3200,25 +3191,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3228,13 +3219,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529528</v>
+        <v>529555</v>
       </c>
       <c r="R23" t="n">
-        <v>7000177</v>
+        <v>7000239</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3263,7 +3254,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3273,12 +3264,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3305,10 +3296,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122835055</v>
+        <v>122835040</v>
       </c>
       <c r="B24" t="n">
-        <v>77714</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3317,38 +3308,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>314</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529555</v>
+        <v>529514</v>
       </c>
       <c r="R24" t="n">
-        <v>7000239</v>
+        <v>7000177</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3380,7 +3385,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3390,12 +3395,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På marken i gammal skog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3422,10 +3427,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122832074</v>
+        <v>122835059</v>
       </c>
       <c r="B25" t="n">
-        <v>57481</v>
+        <v>74866</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3438,39 +3443,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529610</v>
+        <v>529555</v>
       </c>
       <c r="R25" t="n">
-        <v>7000425</v>
+        <v>7000239</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3544,7 +3544,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122843609</v>
+        <v>122844246</v>
       </c>
       <c r="B26" t="n">
         <v>57481</v>
@@ -3596,10 +3596,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529564</v>
+        <v>529543</v>
       </c>
       <c r="R26" t="n">
-        <v>7000340</v>
+        <v>7000331</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3693,10 +3693,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122848070</v>
+        <v>122843609</v>
       </c>
       <c r="B27" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3709,37 +3709,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529485</v>
+        <v>529564</v>
       </c>
       <c r="R27" t="n">
-        <v>7000279</v>
+        <v>7000340</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3776,7 +3785,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3785,7 +3794,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3796,7 +3804,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3811,12 +3819,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3834,7 +3842,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122844246</v>
+        <v>122843242</v>
       </c>
       <c r="B28" t="n">
         <v>57481</v>
@@ -3872,7 +3880,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3886,10 +3894,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529543</v>
+        <v>529586</v>
       </c>
       <c r="R28" t="n">
-        <v>7000331</v>
+        <v>7000356</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3926,7 +3934,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3983,10 +3991,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122849488</v>
+        <v>122844922</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3999,46 +4007,41 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>529504</v>
+        <v>529490</v>
       </c>
       <c r="R29" t="n">
-        <v>7000251</v>
+        <v>7000318</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4075,7 +4078,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4084,6 +4087,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4109,12 +4113,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4132,7 +4136,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122842800</v>
+        <v>122849927</v>
       </c>
       <c r="B30" t="n">
         <v>57481</v>
@@ -4170,7 +4174,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4180,17 +4184,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>529564</v>
+        <v>529495</v>
       </c>
       <c r="R30" t="n">
-        <v>7000368</v>
+        <v>7000242</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4224,7 +4228,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4243,7 +4247,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4281,7 +4285,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122850306</v>
+        <v>122850162</v>
       </c>
       <c r="B31" t="n">
         <v>57481</v>
@@ -4333,13 +4337,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529539</v>
+        <v>529529</v>
       </c>
       <c r="R31" t="n">
-        <v>7000235</v>
+        <v>7000221</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4373,7 +4377,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4405,9 +4409,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4425,10 +4434,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122849927</v>
+        <v>122849991</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4441,36 +4450,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
@@ -4515,17 +4515,13 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med färska och även äldre ringhack på stammen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4551,12 +4547,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4574,7 +4570,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122847410</v>
+        <v>122849488</v>
       </c>
       <c r="B33" t="n">
         <v>57481</v>
@@ -4612,20 +4608,24 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>529482</v>
+        <v>529504</v>
       </c>
       <c r="R33" t="n">
-        <v>7000271</v>
+        <v>7000251</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4719,7 +4719,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122844745</v>
+        <v>122848281</v>
       </c>
       <c r="B34" t="n">
         <v>57481</v>
@@ -4757,7 +4757,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4767,14 +4767,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>529519</v>
+        <v>529501</v>
       </c>
       <c r="R34" t="n">
-        <v>7000310</v>
+        <v>7000255</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4845,12 +4845,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4868,10 +4868,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122843718</v>
+        <v>122848070</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4884,46 +4884,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529568</v>
+        <v>529485</v>
       </c>
       <c r="R35" t="n">
-        <v>7000344</v>
+        <v>7000279</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4960,7 +4951,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4969,6 +4960,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4979,7 +4971,7 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4994,12 +4986,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5017,10 +5009,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122844041</v>
+        <v>122842399</v>
       </c>
       <c r="B36" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5033,37 +5025,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>529559</v>
+        <v>529556</v>
       </c>
       <c r="R36" t="n">
-        <v>7000333</v>
+        <v>7000374</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5100,7 +5101,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5109,7 +5110,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122848017</v>
+        <v>122843718</v>
       </c>
       <c r="B37" t="n">
         <v>57481</v>
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>529485</v>
+        <v>529568</v>
       </c>
       <c r="R37" t="n">
-        <v>7000279</v>
+        <v>7000344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122849991</v>
+        <v>122847410</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5323,40 +5323,45 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529495</v>
+        <v>529482</v>
       </c>
       <c r="R38" t="n">
-        <v>7000242</v>
+        <v>7000271</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5388,13 +5393,17 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5420,12 +5429,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5443,7 +5452,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122842399</v>
+        <v>122844745</v>
       </c>
       <c r="B39" t="n">
         <v>57481</v>
@@ -5491,14 +5500,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529556</v>
+        <v>529519</v>
       </c>
       <c r="R39" t="n">
-        <v>7000374</v>
+        <v>7000310</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5535,7 +5544,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack och även äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Färska och äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5554,7 +5563,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -5592,10 +5601,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122848281</v>
+        <v>122844041</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5608,46 +5617,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529501</v>
+        <v>529559</v>
       </c>
       <c r="R40" t="n">
-        <v>7000255</v>
+        <v>7000333</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre ringhack på en knäckt död liggande granstam. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5693,6 +5693,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5703,7 +5704,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5718,12 +5719,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5741,10 +5742,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122844420</v>
+        <v>122850306</v>
       </c>
       <c r="B41" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5757,44 +5758,49 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529532</v>
+        <v>529539</v>
       </c>
       <c r="R41" t="n">
-        <v>7000325</v>
+        <v>7000235</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5828,7 +5834,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på stammen av en gran intill en på annat sätt hackspettsbearbetad död gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5837,7 +5843,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5861,14 +5866,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5886,10 +5886,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122850162</v>
+        <v>122844420</v>
       </c>
       <c r="B42" t="n">
-        <v>57481</v>
+        <v>78772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5902,46 +5902,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>529529</v>
+        <v>529532</v>
       </c>
       <c r="R42" t="n">
-        <v>7000221</v>
+        <v>7000325</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5978,7 +5973,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Ymnigt med garnlav på gran. Långväxta fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5987,6 +5982,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6012,12 +6008,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6035,7 +6031,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122843242</v>
+        <v>122845104</v>
       </c>
       <c r="B43" t="n">
         <v>57481</v>
@@ -6073,7 +6069,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6087,13 +6083,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>529586</v>
+        <v>529481</v>
       </c>
       <c r="R43" t="n">
-        <v>7000356</v>
+        <v>7000274</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6127,7 +6123,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6146,17 +6142,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -6166,7 +6152,7 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6184,10 +6170,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122844922</v>
+        <v>122842800</v>
       </c>
       <c r="B44" t="n">
-        <v>78771</v>
+        <v>57481</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6200,41 +6186,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529490</v>
+        <v>529564</v>
       </c>
       <c r="R44" t="n">
-        <v>7000318</v>
+        <v>7000368</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6271,7 +6262,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Gott om garnlav på gran. Långväxta fertila bålar med apothecier.</t>
+          <t>Äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6280,7 +6271,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6291,7 +6281,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
+          <t>Grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -6306,12 +6296,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6329,7 +6319,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122845104</v>
+        <v>122848017</v>
       </c>
       <c r="B45" t="n">
         <v>57481</v>
@@ -6381,13 +6371,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>529481</v>
+        <v>529485</v>
       </c>
       <c r="R45" t="n">
-        <v>7000274</v>
+        <v>7000279</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6421,7 +6411,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack på stambasen av en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
+          <t>Tydliga äldre ringhack på en gran. Fyndplatsen finns i gammal granskog med höga till mycket höga livsmiljövärden för tretåig hackspett baserat på mängden stående död ved.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6443,6 +6433,16 @@
           <t>Gammal grandominerad flerskiktad kontinuitetsskog med träd av olika ålder.</t>
         </is>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AM45" t="inlineStr">
         <is>
           <t>Trädstam på levande träd</t>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -1154,11 +1154,11 @@
         <v>122830095</v>
       </c>
       <c r="B6" t="n">
-        <v>57431</v>
+        <v>57441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124468603</v>
+        <v>124464556</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6480,55 +6480,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529657</v>
+        <v>529670</v>
       </c>
       <c r="R46" t="n">
-        <v>6999949</v>
+        <v>6999909</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6557,7 +6543,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6567,12 +6553,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,2 m2.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6587,6 +6568,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6604,10 +6605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124465862</v>
+        <v>124471744</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6616,55 +6617,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529657</v>
+        <v>529601</v>
       </c>
       <c r="R47" t="n">
-        <v>6999868</v>
+        <v>7000312</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6693,7 +6680,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6703,12 +6690,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6722,7 +6704,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6740,10 +6742,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124462373</v>
+        <v>124471570</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6752,46 +6754,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529580</v>
+        <v>529604</v>
       </c>
       <c r="R48" t="n">
-        <v>6999912</v>
+        <v>7000308</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6818,14 +6815,19 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6840,26 +6842,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6877,10 +6859,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124468934</v>
+        <v>124463284</v>
       </c>
       <c r="B49" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6889,46 +6871,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529638</v>
+        <v>529624</v>
       </c>
       <c r="R49" t="n">
-        <v>6999974</v>
+        <v>6999926</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6957,7 +6934,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6967,7 +6944,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6986,22 +6963,22 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7019,10 +6996,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124462260</v>
+        <v>124471362</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7031,31 +7008,40 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7064,13 +7050,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529584</v>
+        <v>529623</v>
       </c>
       <c r="R50" t="n">
-        <v>6999935</v>
+        <v>7000094</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7099,7 +7085,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7109,12 +7095,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
+          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7128,27 +7114,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7166,10 +7132,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124462835</v>
+        <v>124462373</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7178,40 +7144,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7220,13 +7177,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529579</v>
+        <v>529580</v>
       </c>
       <c r="R51" t="n">
-        <v>6999920</v>
+        <v>6999912</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7253,24 +7210,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 38 plantor inom ca 0,5 m2.</t>
+          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7285,6 +7232,26 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7302,10 +7269,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124468294</v>
+        <v>124462545</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7314,40 +7281,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7356,13 +7314,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529689</v>
+        <v>529580</v>
       </c>
       <c r="R52" t="n">
-        <v>6999938</v>
+        <v>6999910</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7391,7 +7349,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7401,12 +7359,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
+          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7420,7 +7378,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7438,10 +7416,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124464353</v>
+        <v>124468910</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7454,21 +7432,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7483,10 +7461,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529642</v>
+        <v>529641</v>
       </c>
       <c r="R53" t="n">
-        <v>6999931</v>
+        <v>6999979</v>
       </c>
       <c r="S53" t="n">
         <v>9</v>
@@ -7518,7 +7496,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7528,7 +7506,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7580,10 +7558,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124464556</v>
+        <v>124467882</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7592,41 +7570,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529670</v>
+        <v>529678</v>
       </c>
       <c r="R54" t="n">
-        <v>6999909</v>
+        <v>6999878</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7655,7 +7647,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7665,7 +7657,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7680,26 +7677,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7717,10 +7694,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124463284</v>
+        <v>124465862</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7729,38 +7706,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529624</v>
+        <v>529657</v>
       </c>
       <c r="R55" t="n">
-        <v>6999926</v>
+        <v>6999868</v>
       </c>
       <c r="S55" t="n">
         <v>9</v>
@@ -7792,7 +7783,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7802,7 +7793,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7817,26 +7813,6 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7854,10 +7830,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124468910</v>
+        <v>124463366</v>
       </c>
       <c r="B56" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7870,21 +7846,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7899,13 +7875,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529641</v>
+        <v>529608</v>
       </c>
       <c r="R56" t="n">
-        <v>6999979</v>
+        <v>6999935</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7934,7 +7910,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7944,7 +7920,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7958,7 +7934,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -7996,10 +7972,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124463397</v>
+        <v>124470698</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8008,31 +7984,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8041,13 +8026,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529620</v>
+        <v>529625</v>
       </c>
       <c r="R57" t="n">
-        <v>6999932</v>
+        <v>7000048</v>
       </c>
       <c r="S57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8076,7 +8061,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8086,7 +8071,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8101,26 +8091,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8138,7 +8108,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124470698</v>
+        <v>124465010</v>
       </c>
       <c r="B58" t="n">
         <v>98101</v>
@@ -8173,7 +8143,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -8192,13 +8162,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529625</v>
+        <v>529689</v>
       </c>
       <c r="R58" t="n">
-        <v>7000048</v>
+        <v>6999902</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8227,7 +8197,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8237,12 +8207,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 0,5 m2.</t>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8256,7 +8226,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8274,10 +8244,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124471506</v>
+        <v>124468969</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8290,21 +8260,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8314,13 +8284,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529632</v>
+        <v>529652</v>
       </c>
       <c r="R59" t="n">
-        <v>7000254</v>
+        <v>6999989</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8349,7 +8319,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8359,12 +8329,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:50</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8378,27 +8343,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8416,7 +8381,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124471744</v>
+        <v>124453319</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -8456,13 +8421,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529601</v>
+        <v>529470</v>
       </c>
       <c r="R60" t="n">
-        <v>7000312</v>
+        <v>7000406</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8491,7 +8456,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8501,7 +8466,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8553,10 +8518,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124464827</v>
+        <v>124470399</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8565,55 +8530,55 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529687</v>
+        <v>529662</v>
       </c>
       <c r="R61" t="n">
-        <v>6999902</v>
+        <v>7000031</v>
       </c>
       <c r="S61" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8642,7 +8607,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8652,12 +8617,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8671,7 +8636,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8689,10 +8654,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124469884</v>
+        <v>124463106</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8701,40 +8666,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8743,13 +8699,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529708</v>
+        <v>529619</v>
       </c>
       <c r="R62" t="n">
-        <v>7000000</v>
+        <v>6999959</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8778,7 +8734,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8788,12 +8744,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8807,7 +8763,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8825,10 +8801,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124471362</v>
+        <v>124471506</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8837,55 +8813,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529623</v>
+        <v>529632</v>
       </c>
       <c r="R63" t="n">
-        <v>7000094</v>
+        <v>7000254</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8914,7 +8876,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8924,12 +8886,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8943,7 +8905,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8961,10 +8943,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124462545</v>
+        <v>124462835</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8973,31 +8955,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -9006,13 +8997,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529580</v>
+        <v>529579</v>
       </c>
       <c r="R64" t="n">
-        <v>6999910</v>
+        <v>6999920</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9041,7 +9032,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9051,12 +9042,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
+          <t>Minst 38 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9071,26 +9062,6 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9108,10 +9079,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124453319</v>
+        <v>124469884</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9120,38 +9091,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529470</v>
+        <v>529708</v>
       </c>
       <c r="R65" t="n">
-        <v>7000406</v>
+        <v>7000000</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -9183,7 +9168,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9193,7 +9178,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9208,26 +9198,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9245,10 +9215,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124465430</v>
+        <v>124468603</v>
       </c>
       <c r="B66" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9257,31 +9227,40 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9290,10 +9269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529636</v>
+        <v>529657</v>
       </c>
       <c r="R66" t="n">
-        <v>6999890</v>
+        <v>6999949</v>
       </c>
       <c r="S66" t="n">
         <v>9</v>
@@ -9325,7 +9304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9335,7 +9314,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9350,26 +9334,6 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9387,7 +9351,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124464307</v>
+        <v>124468294</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9422,7 +9386,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9441,10 +9405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529649</v>
+        <v>529689</v>
       </c>
       <c r="R67" t="n">
-        <v>6999915</v>
+        <v>6999938</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -9476,7 +9440,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9486,12 +9450,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9523,7 +9487,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124465010</v>
+        <v>124464307</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -9558,7 +9522,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -9577,10 +9541,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529689</v>
+        <v>529649</v>
       </c>
       <c r="R68" t="n">
-        <v>6999902</v>
+        <v>6999915</v>
       </c>
       <c r="S68" t="n">
         <v>8</v>
@@ -9612,7 +9576,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9622,12 +9586,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9659,10 +9623,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124470399</v>
+        <v>124464353</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9671,40 +9635,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9713,13 +9668,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529662</v>
+        <v>529642</v>
       </c>
       <c r="R69" t="n">
-        <v>7000031</v>
+        <v>6999931</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9748,7 +9703,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9758,12 +9713,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9777,7 +9727,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9795,7 +9765,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124463106</v>
+        <v>124462260</v>
       </c>
       <c r="B70" t="n">
         <v>79891</v>
@@ -9840,13 +9810,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529619</v>
+        <v>529584</v>
       </c>
       <c r="R70" t="n">
-        <v>6999959</v>
+        <v>6999935</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9875,7 +9845,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9885,12 +9855,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad sälg.</t>
+          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9904,7 +9874,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -9942,10 +9912,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124467882</v>
+        <v>124463397</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9954,40 +9924,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9996,10 +9957,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529678</v>
+        <v>529620</v>
       </c>
       <c r="R71" t="n">
-        <v>6999878</v>
+        <v>6999932</v>
       </c>
       <c r="S71" t="n">
         <v>8</v>
@@ -10031,7 +9992,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10041,12 +10002,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10060,7 +10016,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10078,10 +10054,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124463366</v>
+        <v>124468934</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10090,31 +10066,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10123,13 +10099,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529608</v>
+        <v>529638</v>
       </c>
       <c r="R72" t="n">
-        <v>6999935</v>
+        <v>6999974</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10158,7 +10134,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10168,7 +10144,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10182,7 +10158,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10220,10 +10196,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124471570</v>
+        <v>124470921</v>
       </c>
       <c r="B73" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10232,41 +10208,55 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529604</v>
+        <v>529573</v>
       </c>
       <c r="R73" t="n">
-        <v>7000308</v>
+        <v>7000067</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10295,7 +10285,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10305,7 +10295,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Minst 43 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10319,7 +10314,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10337,10 +10332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124468969</v>
+        <v>124465430</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10353,37 +10348,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>529652</v>
+        <v>529636</v>
       </c>
       <c r="R74" t="n">
-        <v>6999989</v>
+        <v>6999890</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10441,22 +10441,22 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124470921</v>
+        <v>124464827</v>
       </c>
       <c r="B75" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10486,55 +10486,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>529573</v>
+        <v>529687</v>
       </c>
       <c r="R75" t="n">
-        <v>7000067</v>
+        <v>6999902</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Minst 43 plantor inom ca 0,5 m2.</t>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10610,10 +10610,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124541322</v>
+        <v>124540608</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10626,26 +10626,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10653,10 +10657,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>529565</v>
+        <v>529477</v>
       </c>
       <c r="R76" t="n">
-        <v>7000430</v>
+        <v>7000468</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10688,7 +10692,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10698,7 +10702,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10728,12 +10737,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10751,10 +10760,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124541216</v>
+        <v>124541133</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10767,45 +10776,44 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>529524</v>
+        <v>529497</v>
       </c>
       <c r="R77" t="n">
-        <v>7000440</v>
+        <v>7000443</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10834,7 +10842,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10844,12 +10852,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
+          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10858,6 +10866,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -10868,22 +10877,22 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10901,10 +10910,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124540781</v>
+        <v>124540447</v>
       </c>
       <c r="B78" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10917,49 +10926,40 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>529468</v>
+        <v>529509</v>
       </c>
       <c r="R78" t="n">
-        <v>7000465</v>
+        <v>7000467</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10998,12 +10998,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11012,12 +11012,13 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -11032,12 +11033,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11055,10 +11056,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124541247</v>
+        <v>124540904</v>
       </c>
       <c r="B79" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11071,42 +11072,41 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>529530</v>
+        <v>529475</v>
       </c>
       <c r="R79" t="n">
-        <v>7000434</v>
+        <v>7000452</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Fertil lunglav på en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11162,32 +11162,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11205,10 +11206,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124540904</v>
+        <v>124541322</v>
       </c>
       <c r="B80" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11221,41 +11222,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>529475</v>
+        <v>529565</v>
       </c>
       <c r="R80" t="n">
-        <v>7000452</v>
+        <v>7000430</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11287,7 +11284,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11297,12 +11294,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en lutande smal sälg.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11317,27 +11309,27 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11514,7 +11506,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124540308</v>
+        <v>124540781</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11552,7 +11544,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11566,13 +11558,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>529573</v>
+        <v>529468</v>
       </c>
       <c r="R82" t="n">
-        <v>7000446</v>
+        <v>7000465</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11601,7 +11593,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11611,12 +11603,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, en bit upp på en granstam.</t>
+          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11630,7 +11622,7 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11668,10 +11660,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124540608</v>
+        <v>124540308</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11684,41 +11676,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>529477</v>
+        <v>529573</v>
       </c>
       <c r="R83" t="n">
-        <v>7000468</v>
+        <v>7000446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11750,7 +11747,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11760,12 +11757,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
+          <t>Ringhack, äldre, en bit upp på en granstam.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11774,7 +11771,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11795,12 +11791,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11818,10 +11814,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124540447</v>
+        <v>124541341</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11830,44 +11826,61 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>529509</v>
+        <v>529549</v>
       </c>
       <c r="R84" t="n">
-        <v>7000467</v>
+        <v>7000412</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11896,7 +11909,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11906,12 +11919,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11920,7 +11928,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11929,24 +11936,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11964,10 +11956,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124541341</v>
+        <v>124541247</v>
       </c>
       <c r="B85" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11976,20 +11968,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11997,40 +11989,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>529549</v>
+        <v>529530</v>
       </c>
       <c r="R85" t="n">
-        <v>7000412</v>
+        <v>7000434</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -12059,7 +12039,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12069,7 +12049,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12086,9 +12071,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12252,10 +12252,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124541347</v>
+        <v>124541216</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12268,26 +12268,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -12295,10 +12300,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>529549</v>
+        <v>529524</v>
       </c>
       <c r="R87" t="n">
-        <v>7000412</v>
+        <v>7000440</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -12330,7 +12335,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12340,12 +12345,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>På en tallstam.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12354,7 +12359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -12363,29 +12367,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12403,10 +12402,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124541133</v>
+        <v>124541347</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12419,44 +12418,40 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>529497</v>
+        <v>529549</v>
       </c>
       <c r="R88" t="n">
-        <v>7000443</v>
+        <v>7000412</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12485,7 +12480,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12495,12 +12490,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
+          <t>På en tallstam.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12518,14 +12513,19 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -12535,7 +12535,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12553,10 +12553,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124541545</v>
+        <v>124541568</v>
       </c>
       <c r="B89" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -12569,40 +12569,49 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>529524</v>
+        <v>529514</v>
       </c>
       <c r="R89" t="n">
-        <v>7000430</v>
+        <v>7000432</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -12631,7 +12640,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12641,12 +12650,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -12655,7 +12664,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12676,12 +12684,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -12699,10 +12707,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124541662</v>
+        <v>124541684</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12715,26 +12723,30 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -12742,13 +12754,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>529500</v>
+        <v>529457</v>
       </c>
       <c r="R90" t="n">
-        <v>7000417</v>
+        <v>7000423</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12777,7 +12789,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12787,12 +12799,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12807,27 +12819,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12845,10 +12857,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124541526</v>
+        <v>124541689</v>
       </c>
       <c r="B91" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12861,42 +12873,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>529524</v>
+        <v>529457</v>
       </c>
       <c r="R91" t="n">
-        <v>7000430</v>
+        <v>7000423</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12928,7 +12935,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12938,12 +12945,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12952,12 +12959,13 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12972,12 +12980,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -12995,10 +13003,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124541707</v>
+        <v>124541545</v>
       </c>
       <c r="B92" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13011,46 +13019,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>529452</v>
+        <v>529524</v>
       </c>
       <c r="R92" t="n">
-        <v>7000440</v>
+        <v>7000430</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -13082,7 +13081,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13092,12 +13091,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13106,12 +13105,13 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -13126,12 +13126,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13149,10 +13149,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124541689</v>
+        <v>124541526</v>
       </c>
       <c r="B93" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13165,37 +13165,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>529457</v>
+        <v>529524</v>
       </c>
       <c r="R93" t="n">
-        <v>7000423</v>
+        <v>7000430</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -13227,7 +13232,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13237,12 +13242,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13251,13 +13256,12 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -13272,12 +13276,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13295,10 +13299,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124541684</v>
+        <v>124541662</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13311,30 +13315,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -13342,13 +13342,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>529457</v>
+        <v>529500</v>
       </c>
       <c r="R94" t="n">
-        <v>7000423</v>
+        <v>7000417</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13387,12 +13387,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13407,27 +13407,27 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13445,7 +13445,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124541568</v>
+        <v>124541707</v>
       </c>
       <c r="B95" t="n">
         <v>57513</v>
@@ -13483,7 +13483,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -13497,13 +13497,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>529514</v>
+        <v>529452</v>
       </c>
       <c r="R95" t="n">
-        <v>7000432</v>
+        <v>7000440</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13561,7 +13561,7 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124464556</v>
+        <v>124464827</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6484,37 +6484,51 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529670</v>
+        <v>529687</v>
       </c>
       <c r="R46" t="n">
-        <v>6999909</v>
+        <v>6999902</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6543,7 +6557,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6553,7 +6567,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6568,26 +6587,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6605,10 +6604,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124471744</v>
+        <v>124470698</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6617,41 +6616,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529601</v>
+        <v>529625</v>
       </c>
       <c r="R47" t="n">
-        <v>7000312</v>
+        <v>7000048</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6680,7 +6693,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6690,7 +6703,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6705,26 +6723,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6742,10 +6740,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124471570</v>
+        <v>124468294</v>
       </c>
       <c r="B48" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6754,41 +6752,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529604</v>
+        <v>529689</v>
       </c>
       <c r="R48" t="n">
-        <v>7000308</v>
+        <v>6999938</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6817,7 +6829,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6827,7 +6839,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6841,7 +6858,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6859,10 +6876,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124463284</v>
+        <v>124465430</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6875,34 +6892,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529624</v>
+        <v>529636</v>
       </c>
       <c r="R49" t="n">
-        <v>6999926</v>
+        <v>6999890</v>
       </c>
       <c r="S49" t="n">
         <v>9</v>
@@ -6934,7 +6956,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6944,7 +6966,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6973,12 +6995,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6996,7 +7018,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124471362</v>
+        <v>124465862</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -7031,7 +7053,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7050,13 +7072,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529623</v>
+        <v>529657</v>
       </c>
       <c r="R50" t="n">
-        <v>7000094</v>
+        <v>6999868</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7085,7 +7107,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7095,12 +7117,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7114,7 +7136,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7132,10 +7154,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124462373</v>
+        <v>124469884</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7144,31 +7166,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7177,10 +7208,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529580</v>
+        <v>529708</v>
       </c>
       <c r="R51" t="n">
-        <v>6999912</v>
+        <v>7000000</v>
       </c>
       <c r="S51" t="n">
         <v>7</v>
@@ -7210,14 +7241,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
+          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7232,26 +7273,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7269,7 +7290,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124462545</v>
+        <v>124464353</v>
       </c>
       <c r="B52" t="n">
         <v>79891</v>
@@ -7314,10 +7335,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529580</v>
+        <v>529642</v>
       </c>
       <c r="R52" t="n">
-        <v>6999910</v>
+        <v>6999931</v>
       </c>
       <c r="S52" t="n">
         <v>9</v>
@@ -7349,7 +7370,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7359,12 +7380,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7378,7 +7394,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -7416,10 +7432,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124468910</v>
+        <v>124463366</v>
       </c>
       <c r="B53" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7432,21 +7448,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7461,13 +7477,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529641</v>
+        <v>529608</v>
       </c>
       <c r="R53" t="n">
-        <v>6999979</v>
+        <v>6999935</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7496,7 +7512,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7506,7 +7522,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7520,7 +7536,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7558,7 +7574,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124467882</v>
+        <v>124465010</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -7593,7 +7609,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -7612,10 +7628,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529678</v>
+        <v>529689</v>
       </c>
       <c r="R54" t="n">
-        <v>6999878</v>
+        <v>6999902</v>
       </c>
       <c r="S54" t="n">
         <v>8</v>
@@ -7647,7 +7663,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7657,12 +7673,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7694,7 +7710,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124465862</v>
+        <v>124470399</v>
       </c>
       <c r="B55" t="n">
         <v>98101</v>
@@ -7729,7 +7745,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7748,13 +7764,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529657</v>
+        <v>529662</v>
       </c>
       <c r="R55" t="n">
-        <v>6999868</v>
+        <v>7000031</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7783,7 +7799,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7793,12 +7809,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7812,7 +7828,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7830,10 +7846,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124463366</v>
+        <v>124463284</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7846,42 +7862,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529608</v>
+        <v>529624</v>
       </c>
       <c r="R56" t="n">
-        <v>6999935</v>
+        <v>6999926</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7910,7 +7921,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7920,7 +7931,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7934,27 +7945,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7972,10 +7983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124470698</v>
+        <v>124462260</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7984,40 +7995,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8026,10 +8028,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529625</v>
+        <v>529584</v>
       </c>
       <c r="R57" t="n">
-        <v>7000048</v>
+        <v>6999935</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -8061,7 +8063,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8071,12 +8073,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 0,5 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8091,6 +8093,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8108,10 +8130,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124465010</v>
+        <v>124468910</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8120,40 +8142,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8162,13 +8175,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529689</v>
+        <v>529641</v>
       </c>
       <c r="R58" t="n">
-        <v>6999902</v>
+        <v>6999979</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8197,7 +8210,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8207,12 +8220,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8227,6 +8235,26 @@
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8244,7 +8272,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124468969</v>
+        <v>124463397</v>
       </c>
       <c r="B59" t="n">
         <v>79891</v>
@@ -8278,19 +8306,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529652</v>
+        <v>529620</v>
       </c>
       <c r="R59" t="n">
-        <v>6999989</v>
+        <v>6999932</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8319,7 +8352,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8329,7 +8362,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8343,7 +8376,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -8381,10 +8414,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124453319</v>
+        <v>124470921</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8393,38 +8426,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529470</v>
+        <v>529573</v>
       </c>
       <c r="R60" t="n">
-        <v>7000406</v>
+        <v>7000067</v>
       </c>
       <c r="S60" t="n">
         <v>7</v>
@@ -8456,7 +8503,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8466,7 +8513,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:34</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 43 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8480,27 +8532,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8518,7 +8550,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124470399</v>
+        <v>124471362</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -8553,7 +8585,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -8572,13 +8604,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529662</v>
+        <v>529623</v>
       </c>
       <c r="R61" t="n">
-        <v>7000031</v>
+        <v>7000094</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8607,7 +8639,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8617,12 +8649,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8636,7 +8668,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8801,10 +8833,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124471506</v>
+        <v>124464307</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8813,41 +8845,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529632</v>
+        <v>529649</v>
       </c>
       <c r="R63" t="n">
-        <v>7000254</v>
+        <v>6999915</v>
       </c>
       <c r="S63" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8876,7 +8922,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8886,12 +8932,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8905,27 +8951,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8943,10 +8969,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124462835</v>
+        <v>124468969</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8955,55 +8981,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529579</v>
+        <v>529652</v>
       </c>
       <c r="R64" t="n">
-        <v>6999920</v>
+        <v>6999989</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9032,7 +9044,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9042,12 +9054,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 38 plantor inom ca 0,5 m2.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9061,7 +9068,27 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9079,10 +9106,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124469884</v>
+        <v>124468934</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9091,40 +9118,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9133,13 +9151,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529708</v>
+        <v>529638</v>
       </c>
       <c r="R65" t="n">
-        <v>7000000</v>
+        <v>6999974</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9168,7 +9186,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9178,12 +9196,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9197,7 +9210,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9215,10 +9248,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124468603</v>
+        <v>124471570</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>79919</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9227,55 +9260,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529657</v>
+        <v>529604</v>
       </c>
       <c r="R66" t="n">
-        <v>6999949</v>
+        <v>7000308</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9304,7 +9323,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9314,12 +9333,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,2 m2.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9333,7 +9347,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9351,7 +9365,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124468294</v>
+        <v>124467882</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9386,7 +9400,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>160</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9405,10 +9419,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529689</v>
+        <v>529678</v>
       </c>
       <c r="R67" t="n">
-        <v>6999938</v>
+        <v>6999878</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -9440,7 +9454,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9450,12 +9464,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9487,10 +9501,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124464307</v>
+        <v>124462373</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9499,40 +9513,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9541,13 +9546,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529649</v>
+        <v>529580</v>
       </c>
       <c r="R68" t="n">
-        <v>6999915</v>
+        <v>6999912</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9574,24 +9579,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9605,7 +9600,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9623,7 +9638,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124464353</v>
+        <v>124462545</v>
       </c>
       <c r="B69" t="n">
         <v>79891</v>
@@ -9668,10 +9683,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529642</v>
+        <v>529580</v>
       </c>
       <c r="R69" t="n">
-        <v>6999931</v>
+        <v>6999910</v>
       </c>
       <c r="S69" t="n">
         <v>9</v>
@@ -9703,7 +9718,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9713,7 +9728,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9727,7 +9747,7 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -9765,10 +9785,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124462260</v>
+        <v>124464556</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9781,42 +9801,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529584</v>
+        <v>529670</v>
       </c>
       <c r="R70" t="n">
-        <v>6999935</v>
+        <v>6999909</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9845,7 +9860,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9855,12 +9870,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9874,27 +9884,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9912,10 +9922,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124463397</v>
+        <v>124453319</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9928,42 +9938,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529620</v>
+        <v>529470</v>
       </c>
       <c r="R71" t="n">
-        <v>6999932</v>
+        <v>7000406</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9992,7 +9997,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10002,7 +10007,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10021,22 +10026,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10054,10 +10059,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124468934</v>
+        <v>124471744</v>
       </c>
       <c r="B72" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10066,46 +10071,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529638</v>
+        <v>529601</v>
       </c>
       <c r="R72" t="n">
-        <v>6999974</v>
+        <v>7000312</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10158,27 +10158,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10196,7 +10196,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124470921</v>
+        <v>124468603</v>
       </c>
       <c r="B73" t="n">
         <v>98101</v>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -10250,13 +10250,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529573</v>
+        <v>529657</v>
       </c>
       <c r="R73" t="n">
-        <v>7000067</v>
+        <v>6999949</v>
       </c>
       <c r="S73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Minst 43 plantor inom ca 0,5 m2.</t>
+          <t>Minst 18 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10332,10 +10332,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124465430</v>
+        <v>124471506</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10348,42 +10348,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>529636</v>
+        <v>529632</v>
       </c>
       <c r="R74" t="n">
-        <v>6999890</v>
+        <v>7000254</v>
       </c>
       <c r="S74" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10412,7 +10407,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10422,7 +10417,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124464827</v>
+        <v>124462835</v>
       </c>
       <c r="B75" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10486,55 +10486,55 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>529687</v>
+        <v>529579</v>
       </c>
       <c r="R75" t="n">
-        <v>6999902</v>
+        <v>6999920</v>
       </c>
       <c r="S75" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10573,12 +10573,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
+          <t>Minst 38 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10610,10 +10610,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124540608</v>
+        <v>124541341</v>
       </c>
       <c r="B76" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10622,48 +10622,61 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>529477</v>
+        <v>529549</v>
       </c>
       <c r="R76" t="n">
-        <v>7000468</v>
+        <v>7000412</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10692,7 +10705,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10702,12 +10715,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:55</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10716,7 +10724,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10725,24 +10732,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10760,7 +10752,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124541133</v>
+        <v>124540904</v>
       </c>
       <c r="B77" t="n">
         <v>79891</v>
@@ -10807,10 +10799,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>529497</v>
+        <v>529475</v>
       </c>
       <c r="R77" t="n">
-        <v>7000443</v>
+        <v>7000452</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10842,7 +10834,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10852,12 +10844,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
+          <t>Fertil lunglav på en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10872,7 +10864,7 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -10910,10 +10902,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124540447</v>
+        <v>124540712</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10926,37 +10918,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>529509</v>
+        <v>529477</v>
       </c>
       <c r="R78" t="n">
-        <v>7000467</v>
+        <v>7000468</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10988,7 +10989,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10998,12 +10999,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11012,7 +11013,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -11021,6 +11021,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Gammal granskog med fin bäckmiljö.</t>
+        </is>
+      </c>
       <c r="AJ78" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11033,12 +11038,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11056,10 +11061,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124540904</v>
+        <v>124541265</v>
       </c>
       <c r="B79" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -11072,41 +11077,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>529475</v>
+        <v>529530</v>
       </c>
       <c r="R79" t="n">
-        <v>7000452</v>
+        <v>7000434</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -11138,7 +11139,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11148,12 +11149,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en lutande smal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11168,27 +11169,27 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11206,7 +11207,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124541322</v>
+        <v>124541347</v>
       </c>
       <c r="B80" t="n">
         <v>78810</v>
@@ -11249,13 +11250,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>529565</v>
+        <v>529549</v>
       </c>
       <c r="R80" t="n">
-        <v>7000430</v>
+        <v>7000412</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11284,7 +11285,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11294,7 +11295,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en tallstam.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11312,24 +11318,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11347,7 +11358,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124540712</v>
+        <v>124540308</v>
       </c>
       <c r="B81" t="n">
         <v>57513</v>
@@ -11385,7 +11396,7 @@
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -11399,10 +11410,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>529477</v>
+        <v>529573</v>
       </c>
       <c r="R81" t="n">
-        <v>7000468</v>
+        <v>7000446</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11434,7 +11445,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11444,12 +11455,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
+          <t>Ringhack, äldre, en bit upp på en granstam.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11466,11 +11477,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Gammal granskog med fin bäckmiljö.</t>
-        </is>
-      </c>
       <c r="AJ81" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11483,12 +11489,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11506,7 +11512,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124540781</v>
+        <v>124541247</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11544,27 +11550,23 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>529468</v>
+        <v>529530</v>
       </c>
       <c r="R82" t="n">
-        <v>7000465</v>
+        <v>7000434</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11593,7 +11595,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11603,12 +11605,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11622,7 +11624,7 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11660,7 +11662,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124540308</v>
+        <v>124540781</v>
       </c>
       <c r="B83" t="n">
         <v>57513</v>
@@ -11698,7 +11700,7 @@
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -11712,13 +11714,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>529573</v>
+        <v>529468</v>
       </c>
       <c r="R83" t="n">
-        <v>7000446</v>
+        <v>7000465</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11747,7 +11749,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11757,12 +11759,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, en bit upp på en granstam.</t>
+          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11776,7 +11778,7 @@
       </c>
       <c r="AH83" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -11814,10 +11816,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124541341</v>
+        <v>124540608</v>
       </c>
       <c r="B84" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11826,61 +11828,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>529549</v>
+        <v>529477</v>
       </c>
       <c r="R84" t="n">
-        <v>7000412</v>
+        <v>7000468</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11909,7 +11898,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11919,7 +11908,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11928,6 +11922,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11936,9 +11931,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11956,10 +11966,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124541247</v>
+        <v>124541133</v>
       </c>
       <c r="B85" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11972,42 +11982,41 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>529530</v>
+        <v>529497</v>
       </c>
       <c r="R85" t="n">
-        <v>7000434</v>
+        <v>7000443</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -12039,7 +12048,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12049,12 +12058,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12063,6 +12072,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -12073,22 +12083,22 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -12106,7 +12116,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124541265</v>
+        <v>124540447</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -12145,14 +12155,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>529530</v>
+        <v>529509</v>
       </c>
       <c r="R86" t="n">
-        <v>7000434</v>
+        <v>7000467</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -12184,7 +12194,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12194,7 +12204,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12402,7 +12412,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124541347</v>
+        <v>124541322</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -12445,13 +12455,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>529549</v>
+        <v>529565</v>
       </c>
       <c r="R88" t="n">
-        <v>7000412</v>
+        <v>7000430</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12480,7 +12490,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12490,12 +12500,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På en tallstam.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12513,29 +12518,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12857,10 +12857,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124541689</v>
+        <v>124541526</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12873,37 +12873,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>529457</v>
+        <v>529524</v>
       </c>
       <c r="R91" t="n">
-        <v>7000423</v>
+        <v>7000430</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12935,7 +12940,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12945,12 +12950,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12959,13 +12964,12 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -12980,12 +12984,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13003,7 +13007,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124541545</v>
+        <v>124541662</v>
       </c>
       <c r="B92" t="n">
         <v>78810</v>
@@ -13042,17 +13046,17 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>529524</v>
+        <v>529500</v>
       </c>
       <c r="R92" t="n">
-        <v>7000430</v>
+        <v>7000417</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -13081,7 +13085,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13091,7 +13095,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
@@ -13149,10 +13153,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124541526</v>
+        <v>124541689</v>
       </c>
       <c r="B93" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13165,42 +13169,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>529524</v>
+        <v>529457</v>
       </c>
       <c r="R93" t="n">
-        <v>7000430</v>
+        <v>7000423</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -13232,7 +13231,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13242,12 +13241,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13256,12 +13255,13 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -13276,12 +13276,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13299,7 +13299,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124541662</v>
+        <v>124541545</v>
       </c>
       <c r="B94" t="n">
         <v>78810</v>
@@ -13338,17 +13338,17 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>529500</v>
+        <v>529524</v>
       </c>
       <c r="R94" t="n">
-        <v>7000417</v>
+        <v>7000430</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
@@ -13597,6 +13597,2216 @@
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>124791153</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>529464</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7000280</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Gott om bålar på en gammal sälg med grov fårad bark.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>124791066</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>529482</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7000366</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>124791162</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79926</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>529464</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7000280</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Intill lunglav på en gammal sälg.</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>124791260</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>529442</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7000277</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>På en gammal sälg intill lunglav.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>124791104</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>529457</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7000281</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på många granar! Och här finns fertila exemplar.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Många granar.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Många granar.</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>124791246</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>529442</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7000277</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>124791265</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>529442</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7000277</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>124791073</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>529482</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7000366</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>124791389</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>529464</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7000252</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Växer här ymnigt på en sälg.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>124791391</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57883</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>529464</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7000252</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>124791358</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>529435</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7000275</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>124791374</v>
+      </c>
+      <c r="B107" t="n">
+        <v>105102</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>529435</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7000275</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>124791428</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>529468</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7000332</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>124791408</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>529456</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7000329</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>124791365</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Trättflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>529435</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7000275</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Rikligt på flera granar.</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124462260</v>
+        <v>124464307</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6480,31 +6480,40 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6513,13 +6522,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529584</v>
+        <v>529649</v>
       </c>
       <c r="R46" t="n">
-        <v>6999935</v>
+        <v>6999915</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6548,7 +6557,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6558,12 +6567,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6577,27 +6586,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6615,10 +6604,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124470698</v>
+        <v>124464556</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6627,55 +6616,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529625</v>
+        <v>529670</v>
       </c>
       <c r="R47" t="n">
-        <v>7000048</v>
+        <v>6999909</v>
       </c>
       <c r="S47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6704,7 +6679,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6714,12 +6689,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>19:25</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 0,5 m2.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6733,7 +6703,27 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6751,10 +6741,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124464556</v>
+        <v>124468294</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6763,41 +6753,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529670</v>
+        <v>529689</v>
       </c>
       <c r="R48" t="n">
-        <v>6999909</v>
+        <v>6999938</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6826,7 +6830,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6836,7 +6840,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6851,26 +6860,6 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6888,10 +6877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124465430</v>
+        <v>124470399</v>
       </c>
       <c r="B49" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6900,31 +6889,40 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6933,13 +6931,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529636</v>
+        <v>529662</v>
       </c>
       <c r="R49" t="n">
-        <v>6999890</v>
+        <v>7000031</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6968,7 +6966,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6978,7 +6976,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6992,27 +6995,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7030,10 +7013,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124468603</v>
+        <v>124471506</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7042,55 +7025,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529657</v>
+        <v>529632</v>
       </c>
       <c r="R50" t="n">
-        <v>6999949</v>
+        <v>7000254</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7119,7 +7088,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7129,12 +7098,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 18 plantor inom ca 0,2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7148,7 +7117,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7166,10 +7155,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124462545</v>
+        <v>124462835</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7178,31 +7167,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7211,13 +7209,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529580</v>
+        <v>529579</v>
       </c>
       <c r="R51" t="n">
-        <v>6999910</v>
+        <v>6999920</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7246,7 +7244,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7256,12 +7254,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
+          <t>Minst 38 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7276,26 +7274,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7313,10 +7291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124468910</v>
+        <v>124465010</v>
       </c>
       <c r="B52" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7325,31 +7303,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7358,13 +7345,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529641</v>
+        <v>529689</v>
       </c>
       <c r="R52" t="n">
-        <v>6999979</v>
+        <v>6999902</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7393,7 +7380,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7403,7 +7390,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7418,26 +7410,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7455,10 +7427,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124462835</v>
+        <v>124462260</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7467,40 +7439,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -7509,13 +7472,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529579</v>
+        <v>529584</v>
       </c>
       <c r="R53" t="n">
-        <v>6999920</v>
+        <v>6999935</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7544,7 +7507,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7554,12 +7517,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 38 plantor inom ca 0,5 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7574,6 +7537,26 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7591,10 +7574,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124463284</v>
+        <v>124467882</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7603,41 +7586,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529624</v>
+        <v>529678</v>
       </c>
       <c r="R54" t="n">
-        <v>6999926</v>
+        <v>6999878</v>
       </c>
       <c r="S54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7666,7 +7663,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7676,7 +7673,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7691,26 +7693,6 @@
       <c r="AH54" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7865,10 +7847,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124471570</v>
+        <v>124463284</v>
       </c>
       <c r="B56" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7877,25 +7859,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7905,13 +7887,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529604</v>
+        <v>529624</v>
       </c>
       <c r="R56" t="n">
-        <v>7000308</v>
+        <v>6999926</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7940,7 +7922,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7950,7 +7932,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7964,7 +7946,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7982,10 +7984,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124464827</v>
+        <v>124471570</v>
       </c>
       <c r="B57" t="n">
-        <v>57666</v>
+        <v>79919</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7994,55 +7996,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529687</v>
+        <v>529604</v>
       </c>
       <c r="R57" t="n">
-        <v>6999902</v>
+        <v>7000308</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8071,7 +8059,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8081,12 +8069,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8100,7 +8083,7 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8118,10 +8101,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124464307</v>
+        <v>124462373</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8130,40 +8113,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8172,13 +8146,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529649</v>
+        <v>529580</v>
       </c>
       <c r="R58" t="n">
-        <v>6999915</v>
+        <v>6999912</v>
       </c>
       <c r="S58" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8205,24 +8179,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>16:51</t>
-        </is>
-      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8236,7 +8200,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8254,10 +8238,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124464353</v>
+        <v>124468910</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8270,21 +8254,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -8299,10 +8283,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529642</v>
+        <v>529641</v>
       </c>
       <c r="R59" t="n">
-        <v>6999931</v>
+        <v>6999979</v>
       </c>
       <c r="S59" t="n">
         <v>9</v>
@@ -8334,7 +8318,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8344,7 +8328,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8396,10 +8380,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124468969</v>
+        <v>124468934</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8408,38 +8392,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529652</v>
+        <v>529638</v>
       </c>
       <c r="R60" t="n">
-        <v>6999989</v>
+        <v>6999974</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8471,7 +8460,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8481,7 +8470,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8533,7 +8522,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124462373</v>
+        <v>124468969</v>
       </c>
       <c r="B61" t="n">
         <v>79891</v>
@@ -8567,24 +8556,19 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529580</v>
+        <v>529652</v>
       </c>
       <c r="R61" t="n">
-        <v>6999912</v>
+        <v>6999989</v>
       </c>
       <c r="S61" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8611,14 +8595,19 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8632,7 +8621,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -8670,10 +8659,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124471506</v>
+        <v>124463366</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8686,34 +8675,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529632</v>
+        <v>529608</v>
       </c>
       <c r="R62" t="n">
-        <v>7000254</v>
+        <v>6999935</v>
       </c>
       <c r="S62" t="n">
         <v>7</v>
@@ -8745,7 +8739,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8755,12 +8749,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:50</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8779,22 +8768,22 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8812,10 +8801,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124470399</v>
+        <v>124464827</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8824,55 +8813,55 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529662</v>
+        <v>529687</v>
       </c>
       <c r="R63" t="n">
-        <v>7000031</v>
+        <v>6999902</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8901,7 +8890,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8911,12 +8900,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8930,7 +8919,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8948,7 +8937,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124465862</v>
+        <v>124468603</v>
       </c>
       <c r="B64" t="n">
         <v>98101</v>
@@ -8983,7 +8972,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -9005,7 +8994,7 @@
         <v>529657</v>
       </c>
       <c r="R64" t="n">
-        <v>6999868</v>
+        <v>6999949</v>
       </c>
       <c r="S64" t="n">
         <v>9</v>
@@ -9037,7 +9026,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9047,12 +9036,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
+          <t>Minst 18 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9084,10 +9073,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124471362</v>
+        <v>124464353</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9096,40 +9085,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9138,13 +9118,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529623</v>
+        <v>529642</v>
       </c>
       <c r="R65" t="n">
-        <v>7000094</v>
+        <v>6999931</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9173,7 +9153,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9183,12 +9163,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:41</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9202,7 +9177,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9220,7 +9215,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124467882</v>
+        <v>124469884</v>
       </c>
       <c r="B66" t="n">
         <v>98101</v>
@@ -9255,7 +9250,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -9274,13 +9269,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529678</v>
+        <v>529708</v>
       </c>
       <c r="R66" t="n">
-        <v>6999878</v>
+        <v>7000000</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9309,7 +9304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9319,12 +9314,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9338,7 +9333,7 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9356,7 +9351,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124468294</v>
+        <v>124471362</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9391,7 +9386,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9410,10 +9405,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529689</v>
+        <v>529623</v>
       </c>
       <c r="R67" t="n">
-        <v>6999938</v>
+        <v>7000094</v>
       </c>
       <c r="S67" t="n">
         <v>8</v>
@@ -9445,7 +9440,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9455,12 +9450,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9474,7 +9469,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9492,10 +9487,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124463366</v>
+        <v>124465862</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9504,31 +9499,40 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9537,13 +9541,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529608</v>
+        <v>529657</v>
       </c>
       <c r="R68" t="n">
-        <v>6999935</v>
+        <v>6999868</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9572,7 +9576,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9582,7 +9586,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9596,27 +9605,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9634,10 +9623,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124465010</v>
+        <v>124462545</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9646,40 +9635,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9688,13 +9668,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529689</v>
+        <v>529580</v>
       </c>
       <c r="R69" t="n">
-        <v>6999902</v>
+        <v>6999910</v>
       </c>
       <c r="S69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9723,7 +9703,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9733,12 +9713,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
+          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9752,7 +9732,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9770,10 +9770,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124469884</v>
+        <v>124465430</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9782,40 +9782,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9824,13 +9815,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529708</v>
+        <v>529636</v>
       </c>
       <c r="R70" t="n">
-        <v>7000000</v>
+        <v>6999890</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9859,7 +9850,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9869,12 +9860,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9888,7 +9874,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9906,10 +9912,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124471744</v>
+        <v>124463106</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9922,34 +9928,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529601</v>
+        <v>529619</v>
       </c>
       <c r="R71" t="n">
-        <v>7000312</v>
+        <v>6999959</v>
       </c>
       <c r="S71" t="n">
         <v>8</v>
@@ -9981,7 +9992,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9991,7 +10002,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Växer på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10005,27 +10021,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10043,7 +10059,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124463106</v>
+        <v>124463397</v>
       </c>
       <c r="B72" t="n">
         <v>79891</v>
@@ -10088,10 +10104,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529619</v>
+        <v>529620</v>
       </c>
       <c r="R72" t="n">
-        <v>6999959</v>
+        <v>6999932</v>
       </c>
       <c r="S72" t="n">
         <v>8</v>
@@ -10123,7 +10139,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10133,12 +10149,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad sälg.</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10152,7 +10163,7 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -10190,10 +10201,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124468934</v>
+        <v>124471744</v>
       </c>
       <c r="B73" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -10202,46 +10213,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529638</v>
+        <v>529601</v>
       </c>
       <c r="R73" t="n">
-        <v>6999974</v>
+        <v>7000312</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10270,7 +10276,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10280,7 +10286,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10294,27 +10300,27 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -10332,10 +10338,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124463397</v>
+        <v>124470698</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10344,31 +10350,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10377,13 +10392,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>529620</v>
+        <v>529625</v>
       </c>
       <c r="R74" t="n">
-        <v>6999932</v>
+        <v>7000048</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10412,7 +10427,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10422,7 +10437,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10437,26 +10457,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10474,7 +10474,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124540447</v>
+        <v>124541347</v>
       </c>
       <c r="B75" t="n">
         <v>78810</v>
@@ -10513,17 +10513,17 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>529509</v>
+        <v>529549</v>
       </c>
       <c r="R75" t="n">
-        <v>7000467</v>
+        <v>7000412</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en tallstam.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10585,24 +10585,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10620,10 +10625,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124540904</v>
+        <v>124541322</v>
       </c>
       <c r="B76" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10636,41 +10641,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>529475</v>
+        <v>529565</v>
       </c>
       <c r="R76" t="n">
-        <v>7000452</v>
+        <v>7000430</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10702,7 +10703,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10712,12 +10713,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en lutande smal sälg.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10732,27 +10728,27 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10770,10 +10766,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124541247</v>
+        <v>124541341</v>
       </c>
       <c r="B77" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10782,20 +10778,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10803,28 +10799,40 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>529530</v>
+        <v>529549</v>
       </c>
       <c r="R77" t="n">
-        <v>7000434</v>
+        <v>7000412</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10853,7 +10861,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10863,12 +10871,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10885,24 +10888,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10920,7 +10908,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124541133</v>
+        <v>124540904</v>
       </c>
       <c r="B78" t="n">
         <v>79891</v>
@@ -10967,10 +10955,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>529497</v>
+        <v>529475</v>
       </c>
       <c r="R78" t="n">
-        <v>7000443</v>
+        <v>7000452</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -11002,7 +10990,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11012,12 +11000,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
+          <t>Fertil lunglav på en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11032,7 +11020,7 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -11070,7 +11058,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124540712</v>
+        <v>124540781</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11108,7 +11096,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11122,13 +11110,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>529477</v>
+        <v>529468</v>
       </c>
       <c r="R79" t="n">
-        <v>7000468</v>
+        <v>7000465</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11157,7 +11145,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11167,12 +11155,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
+          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11186,12 +11174,7 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Gammal granskog med fin bäckmiljö.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -11206,12 +11189,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11229,10 +11212,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124541341</v>
+        <v>124541133</v>
       </c>
       <c r="B80" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11241,61 +11224,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>529549</v>
+        <v>529497</v>
       </c>
       <c r="R80" t="n">
-        <v>7000412</v>
+        <v>7000443</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -11324,7 +11294,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11334,7 +11304,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Fertil lunglav med gott om apothecier på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11343,6 +11318,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -11351,9 +11327,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11371,10 +11362,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124541265</v>
+        <v>124541247</v>
       </c>
       <c r="B81" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11387,26 +11378,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -11464,7 +11460,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11473,7 +11469,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11494,12 +11489,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11517,7 +11512,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124540781</v>
+        <v>124540712</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11555,7 +11550,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11569,13 +11564,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>529468</v>
+        <v>529477</v>
       </c>
       <c r="R82" t="n">
-        <v>7000465</v>
+        <v>7000468</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -11604,7 +11599,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11614,12 +11609,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
+          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11633,7 +11628,12 @@
       </c>
       <c r="AH82" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Gammal granskog med fin bäckmiljö.</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -11648,12 +11648,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11821,10 +11821,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124541216</v>
+        <v>124541265</v>
       </c>
       <c r="B84" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11837,31 +11837,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11869,13 +11864,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>529524</v>
+        <v>529530</v>
       </c>
       <c r="R84" t="n">
-        <v>7000440</v>
+        <v>7000434</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -11904,7 +11899,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11914,12 +11909,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11928,6 +11923,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11948,12 +11944,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11971,7 +11967,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124541322</v>
+        <v>124540447</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -12010,14 +12006,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>529565</v>
+        <v>529509</v>
       </c>
       <c r="R85" t="n">
-        <v>7000430</v>
+        <v>7000467</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -12049,7 +12045,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12059,7 +12055,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12112,10 +12113,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124541347</v>
+        <v>124541216</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12128,26 +12129,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -12155,10 +12161,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>529549</v>
+        <v>529524</v>
       </c>
       <c r="R86" t="n">
-        <v>7000412</v>
+        <v>7000440</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -12190,7 +12196,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12200,12 +12206,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På en tallstam.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12214,7 +12220,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -12223,29 +12228,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
-        </is>
-      </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12417,10 +12417,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124541684</v>
+        <v>124541689</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12433,30 +12433,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12514,7 +12510,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -12534,22 +12530,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -12567,7 +12563,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124541689</v>
+        <v>124541545</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -12606,14 +12602,14 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>529457</v>
+        <v>529524</v>
       </c>
       <c r="R89" t="n">
-        <v>7000423</v>
+        <v>7000430</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -12645,7 +12641,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12655,7 +12651,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -12675,7 +12671,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12713,10 +12709,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124541707</v>
+        <v>124541662</v>
       </c>
       <c r="B90" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -12729,49 +12725,40 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>529452</v>
+        <v>529500</v>
       </c>
       <c r="R90" t="n">
-        <v>7000440</v>
+        <v>7000417</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12800,7 +12787,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12810,12 +12797,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12824,12 +12811,13 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -12844,12 +12832,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -12867,10 +12855,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124541568</v>
+        <v>124541684</v>
       </c>
       <c r="B91" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12883,49 +12871,44 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>529514</v>
+        <v>529457</v>
       </c>
       <c r="R91" t="n">
-        <v>7000432</v>
+        <v>7000423</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -12954,7 +12937,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12964,12 +12947,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12978,32 +12961,33 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13021,10 +13005,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124541662</v>
+        <v>124541526</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -13037,40 +13021,45 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>529500</v>
+        <v>529524</v>
       </c>
       <c r="R92" t="n">
-        <v>7000417</v>
+        <v>7000430</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -13099,7 +13088,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13109,12 +13098,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13123,7 +13112,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -13144,12 +13132,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -13167,7 +13155,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124541526</v>
+        <v>124541568</v>
       </c>
       <c r="B93" t="n">
         <v>57513</v>
@@ -13205,23 +13193,27 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>529524</v>
+        <v>529514</v>
       </c>
       <c r="R93" t="n">
-        <v>7000430</v>
+        <v>7000432</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -13250,7 +13242,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13260,12 +13252,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13317,10 +13309,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124541545</v>
+        <v>124541707</v>
       </c>
       <c r="B94" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -13333,37 +13325,46 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>529524</v>
+        <v>529452</v>
       </c>
       <c r="R94" t="n">
-        <v>7000430</v>
+        <v>7000440</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -13395,7 +13396,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13405,12 +13406,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13419,13 +13420,12 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -13440,12 +13440,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -13463,10 +13463,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124791265</v>
+        <v>124791162</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13475,20 +13475,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13498,7 +13498,11 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13506,10 +13510,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>529442</v>
+        <v>529464</v>
       </c>
       <c r="R95" t="n">
-        <v>7000277</v>
+        <v>7000280</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -13541,7 +13545,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13551,12 +13555,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13576,22 +13580,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13609,7 +13613,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124791104</v>
+        <v>124791265</v>
       </c>
       <c r="B96" t="n">
         <v>78810</v>
@@ -13642,21 +13646,9 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -13664,10 +13656,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>529457</v>
+        <v>529442</v>
       </c>
       <c r="R96" t="n">
-        <v>7000281</v>
+        <v>7000277</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -13699,7 +13691,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -13709,12 +13701,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på många granar! Och här finns fertila exemplar.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13729,7 +13721,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -13742,11 +13734,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Många granar.</t>
-        </is>
-      </c>
       <c r="AM96" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -13754,7 +13741,7 @@
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Många granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -13913,10 +13900,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124791066</v>
+        <v>124791260</v>
       </c>
       <c r="B98" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13925,32 +13912,32 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -13960,13 +13947,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>529482</v>
+        <v>529442</v>
       </c>
       <c r="R98" t="n">
-        <v>7000366</v>
+        <v>7000277</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13995,7 +13982,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -14005,7 +13992,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>På en gammal sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14358,10 +14350,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124791162</v>
+        <v>124791104</v>
       </c>
       <c r="B101" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -14370,20 +14362,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -14391,11 +14383,19 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>529464</v>
+        <v>529457</v>
       </c>
       <c r="R101" t="n">
-        <v>7000280</v>
+        <v>7000281</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Intill lunglav på en gammal sälg.</t>
+          <t>Rikligt med garnlav på många granar! Och här finns fertila exemplar.</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -14470,27 +14470,32 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Många granar.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies # Många granar.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -14508,10 +14513,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124791260</v>
+        <v>124791066</v>
       </c>
       <c r="B102" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -14520,32 +14525,32 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
@@ -14555,13 +14560,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>529442</v>
+        <v>529482</v>
       </c>
       <c r="R102" t="n">
-        <v>7000277</v>
+        <v>7000366</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -14590,7 +14595,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -14600,12 +14605,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>På en gammal sälg intill lunglav.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -14658,10 +14658,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124791358</v>
+        <v>124791630</v>
       </c>
       <c r="B103" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14670,48 +14670,61 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>529435</v>
+        <v>529505</v>
       </c>
       <c r="R103" t="n">
-        <v>7000275</v>
+        <v>7000073</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -14740,7 +14753,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14750,12 +14763,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg med lunglav.</t>
+          <t>Minst 240 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14771,26 +14784,6 @@
       <c r="AH103" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14808,10 +14801,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124791452</v>
+        <v>124791504</v>
       </c>
       <c r="B104" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14820,46 +14813,45 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>529510</v>
+        <v>529620</v>
       </c>
       <c r="R104" t="n">
-        <v>7000411</v>
+        <v>7000131</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14891,7 +14883,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14901,12 +14893,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en gran.</t>
+          <t>På en sälg tillsammans med luddlav och lunglav.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14915,6 +14907,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -14925,22 +14918,22 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14958,10 +14951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124791491</v>
+        <v>124791509</v>
       </c>
       <c r="B105" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14970,45 +14963,58 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>529561</v>
+        <v>529658</v>
       </c>
       <c r="R105" t="n">
-        <v>7000169</v>
+        <v>7000142</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -15040,7 +15046,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15050,12 +15056,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Växer på en något smalare grovbarkad sälg.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -15071,26 +15077,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -15108,10 +15094,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124791502</v>
+        <v>124791358</v>
       </c>
       <c r="B106" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -15120,32 +15106,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -15155,13 +15141,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>529620</v>
+        <v>529435</v>
       </c>
       <c r="R106" t="n">
-        <v>7000131</v>
+        <v>7000275</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -15190,7 +15176,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15200,12 +15186,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med lunglav och stuplav.</t>
+          <t>På gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -15225,22 +15211,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -15258,10 +15244,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124791428</v>
+        <v>124791502</v>
       </c>
       <c r="B107" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -15270,32 +15256,32 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
@@ -15305,13 +15291,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>529468</v>
+        <v>529620</v>
       </c>
       <c r="R107" t="n">
-        <v>7000332</v>
+        <v>7000131</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -15340,7 +15326,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15350,12 +15336,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
+          <t>På en sälg tillsammans med lunglav och stuplav.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -15408,7 +15394,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124791630</v>
+        <v>124791493</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -15443,7 +15429,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -15468,13 +15454,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>529505</v>
+        <v>529600</v>
       </c>
       <c r="R108" t="n">
-        <v>7000073</v>
+        <v>7000174</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -15503,7 +15489,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -15513,12 +15499,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Minst 240 plantor inom ca 3 m2 yta.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -15551,10 +15537,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124791633</v>
+        <v>124791492</v>
       </c>
       <c r="B109" t="n">
-        <v>56714</v>
+        <v>79927</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -15563,50 +15549,45 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>529464</v>
+        <v>529561</v>
       </c>
       <c r="R109" t="n">
-        <v>7000057</v>
+        <v>7000169</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -15638,7 +15619,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -15648,7 +15629,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Växer intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -15657,12 +15643,33 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -15680,10 +15687,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124470921</v>
+        <v>124791468</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -15692,55 +15699,53 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>529573</v>
+        <v>529561</v>
       </c>
       <c r="R110" t="n">
-        <v>7000067</v>
+        <v>7000407</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -15769,7 +15774,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -15779,12 +15784,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Minst 43 plantor inom ca 0,5 m2.</t>
+          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15798,7 +15803,27 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15816,10 +15841,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124791557</v>
+        <v>124791560</v>
       </c>
       <c r="B111" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15828,45 +15853,58 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>529533</v>
+        <v>529512</v>
       </c>
       <c r="R111" t="n">
-        <v>7000118</v>
+        <v>7000130</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15898,7 +15936,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15908,12 +15946,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Minst 163 plantor inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15929,26 +15967,6 @@
       <c r="AH111" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -15966,10 +15984,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124791408</v>
+        <v>124791638</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -15982,34 +16000,30 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -16017,10 +16031,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>529456</v>
+        <v>529635</v>
       </c>
       <c r="R112" t="n">
-        <v>7000329</v>
+        <v>6999915</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -16052,7 +16066,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -16062,12 +16076,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -16087,22 +16096,22 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -16120,7 +16129,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124791501</v>
+        <v>124791464</v>
       </c>
       <c r="B113" t="n">
         <v>79891</v>
@@ -16157,7 +16166,7 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
@@ -16167,10 +16176,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>529620</v>
+        <v>529530</v>
       </c>
       <c r="R113" t="n">
-        <v>7000131</v>
+        <v>7000400</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -16202,7 +16211,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -16212,12 +16221,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och stuplav.</t>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -16270,10 +16279,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124791638</v>
+        <v>124791408</v>
       </c>
       <c r="B114" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16286,30 +16295,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -16317,10 +16330,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>529635</v>
+        <v>529456</v>
       </c>
       <c r="R114" t="n">
-        <v>6999915</v>
+        <v>7000329</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -16352,7 +16365,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -16362,7 +16375,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16382,22 +16400,22 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -16415,10 +16433,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124791365</v>
+        <v>124791521</v>
       </c>
       <c r="B115" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16427,52 +16445,61 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>529435</v>
+        <v>529586</v>
       </c>
       <c r="R115" t="n">
-        <v>7000275</v>
+        <v>7000100</v>
       </c>
       <c r="S115" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -16501,7 +16528,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -16511,12 +16538,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Rikligt på flera granar.</t>
+          <t>Minst 405 plantor och 1 vinterståndare inom ca 5 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16532,26 +16559,6 @@
       <c r="AH115" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -16569,7 +16576,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124791493</v>
+        <v>124791641</v>
       </c>
       <c r="B116" t="n">
         <v>98101</v>
@@ -16604,7 +16611,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -16629,10 +16636,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>529600</v>
+        <v>529611</v>
       </c>
       <c r="R116" t="n">
-        <v>7000174</v>
+        <v>7000387</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -16664,7 +16671,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -16674,12 +16681,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
+          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16712,10 +16719,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124791494</v>
+        <v>124791496</v>
       </c>
       <c r="B117" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -16724,25 +16731,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -16755,10 +16762,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>529596</v>
+        <v>529624</v>
       </c>
       <c r="R117" t="n">
-        <v>7000265</v>
+        <v>7000244</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -16790,7 +16797,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -16800,7 +16807,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -16816,26 +16823,6 @@
       <c r="AH117" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM117" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -16853,7 +16840,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124791640</v>
+        <v>124791558</v>
       </c>
       <c r="B118" t="n">
         <v>79891</v>
@@ -16896,10 +16883,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>529609</v>
+        <v>529518</v>
       </c>
       <c r="R118" t="n">
-        <v>6999925</v>
+        <v>7000158</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -16931,7 +16918,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -16941,12 +16928,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>På en något smalare sälg.</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -16999,7 +16981,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124791464</v>
+        <v>124791470</v>
       </c>
       <c r="B119" t="n">
         <v>79891</v>
@@ -17046,10 +17028,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>529530</v>
+        <v>529564</v>
       </c>
       <c r="R119" t="n">
-        <v>7000400</v>
+        <v>7000301</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -17081,7 +17063,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -17091,12 +17073,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Fertila bålar.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -17124,6 +17106,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>En smalväxt sälg.</t>
+        </is>
+      </c>
       <c r="AM119" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -17131,7 +17118,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg.</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -17149,10 +17136,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124791374</v>
+        <v>124791452</v>
       </c>
       <c r="B120" t="n">
-        <v>105102</v>
+        <v>57513</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -17161,53 +17148,49 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>529435</v>
+        <v>529510</v>
       </c>
       <c r="R120" t="n">
-        <v>7000275</v>
+        <v>7000411</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -17234,24 +17217,58 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Ringhack, färska och äldre på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD120" t="b">
         <v>0</v>
       </c>
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17269,10 +17286,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124791513</v>
+        <v>124791640</v>
       </c>
       <c r="B121" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17281,58 +17298,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>529701</v>
+        <v>529609</v>
       </c>
       <c r="R121" t="n">
-        <v>7000103</v>
+        <v>6999925</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -17362,14 +17362,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>På en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17385,6 +17395,26 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -17402,10 +17432,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124791560</v>
+        <v>124791365</v>
       </c>
       <c r="B122" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -17414,61 +17444,52 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>529512</v>
+        <v>529435</v>
       </c>
       <c r="R122" t="n">
-        <v>7000130</v>
+        <v>7000275</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -17497,7 +17518,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -17507,12 +17528,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Minst 163 plantor inom ca 2 x 1 m2 yta.</t>
+          <t>Rikligt på flera granar.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -17528,6 +17549,26 @@
       <c r="AH122" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -17545,10 +17586,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124791391</v>
+        <v>124791633</v>
       </c>
       <c r="B123" t="n">
-        <v>57883</v>
+        <v>56714</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -17557,20 +17598,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>103015</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -17578,20 +17619,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -17608,10 +17641,10 @@
         <v>529464</v>
       </c>
       <c r="R123" t="n">
-        <v>7000252</v>
+        <v>7000057</v>
       </c>
       <c r="S123" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -17640,7 +17673,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -17650,7 +17683,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -17682,7 +17715,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124791639</v>
+        <v>124791628</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -17715,8 +17748,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -17734,13 +17775,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>529609</v>
+        <v>529519</v>
       </c>
       <c r="R124" t="n">
-        <v>6999925</v>
+        <v>7000108</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -17769,7 +17810,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -17779,12 +17820,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
+          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17817,10 +17858,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124791492</v>
+        <v>124791494</v>
       </c>
       <c r="B125" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -17829,34 +17870,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -17864,13 +17901,13 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>529561</v>
+        <v>529596</v>
       </c>
       <c r="R125" t="n">
-        <v>7000169</v>
+        <v>7000265</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -17899,7 +17936,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -17909,12 +17946,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Växer intill lunglav på en gammal sälg.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -17934,22 +17966,22 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -17967,7 +17999,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124791641</v>
+        <v>124791513</v>
       </c>
       <c r="B126" t="n">
         <v>98101</v>
@@ -18002,7 +18034,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18027,10 +18059,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>529611</v>
+        <v>529701</v>
       </c>
       <c r="R126" t="n">
-        <v>7000387</v>
+        <v>7000103</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -18060,24 +18092,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -18110,10 +18132,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124791468</v>
+        <v>124791391</v>
       </c>
       <c r="B127" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -18122,20 +18144,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -18143,12 +18165,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -18162,10 +18192,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>529561</v>
+        <v>529464</v>
       </c>
       <c r="R127" t="n">
-        <v>7000407</v>
+        <v>7000252</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -18197,7 +18227,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -18207,12 +18237,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -18227,26 +18252,6 @@
       <c r="AH127" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -18264,10 +18269,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124791504</v>
+        <v>124791501</v>
       </c>
       <c r="B128" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -18276,32 +18281,32 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
@@ -18361,7 +18366,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och lunglav.</t>
+          <t>På en sälg tillsammans med luddlav och stuplav.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18414,10 +18419,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124791628</v>
+        <v>124791428</v>
       </c>
       <c r="B129" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18426,61 +18431,48 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>529519</v>
+        <v>529468</v>
       </c>
       <c r="R129" t="n">
-        <v>7000108</v>
+        <v>7000332</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -18509,7 +18501,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -18519,12 +18511,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
+          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -18540,6 +18532,26 @@
       <c r="AH129" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -18557,7 +18569,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124791470</v>
+        <v>124791534</v>
       </c>
       <c r="B130" t="n">
         <v>79891</v>
@@ -18594,7 +18606,7 @@
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
@@ -18604,10 +18616,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>529564</v>
+        <v>529563</v>
       </c>
       <c r="R130" t="n">
-        <v>7000301</v>
+        <v>7000079</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -18639,7 +18651,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -18649,12 +18661,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Växer på en levande sälglåga.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -18682,11 +18694,6 @@
           <t>Salix caprea</t>
         </is>
       </c>
-      <c r="AL130" t="inlineStr">
-        <is>
-          <t>En smalväxt sälg.</t>
-        </is>
-      </c>
       <c r="AM130" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -18694,7 +18701,7 @@
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg.</t>
+          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -18712,10 +18719,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124791534</v>
+        <v>124791639</v>
       </c>
       <c r="B131" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -18724,48 +18731,53 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>529563</v>
+        <v>529609</v>
       </c>
       <c r="R131" t="n">
-        <v>7000079</v>
+        <v>6999925</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -18794,7 +18806,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -18804,12 +18816,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Växer på en levande sälglåga.</t>
+          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -18825,26 +18837,6 @@
       <c r="AH131" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -18862,10 +18854,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124791635</v>
+        <v>124791374</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>105102</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -18874,40 +18866,32 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -18922,10 +18906,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>529471</v>
+        <v>529435</v>
       </c>
       <c r="R132" t="n">
-        <v>7000063</v>
+        <v>7000275</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -18955,24 +18939,9 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Minst 360 plantor och 1 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -19005,10 +18974,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124791496</v>
+        <v>124791389</v>
       </c>
       <c r="B133" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -19017,41 +18986,45 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>529624</v>
+        <v>529464</v>
       </c>
       <c r="R133" t="n">
-        <v>7000244</v>
+        <v>7000252</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -19083,7 +19056,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19093,7 +19066,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Växer här ymnigt på en sälg.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -19109,6 +19087,26 @@
       <c r="AH133" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -19126,10 +19124,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124791467</v>
+        <v>124470921</v>
       </c>
       <c r="B134" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -19138,53 +19136,55 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>529555</v>
+        <v>529573</v>
       </c>
       <c r="R134" t="n">
-        <v>7000408</v>
+        <v>7000067</v>
       </c>
       <c r="S134" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19223,12 +19223,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Minst 43 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -19242,27 +19242,7 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM134" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -19280,10 +19260,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124791389</v>
+        <v>124791557</v>
       </c>
       <c r="B135" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -19296,44 +19276,44 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>529464</v>
+        <v>529533</v>
       </c>
       <c r="R135" t="n">
-        <v>7000252</v>
+        <v>7000118</v>
       </c>
       <c r="S135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -19362,7 +19342,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19372,12 +19352,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Växer här ymnigt på en sälg.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19397,22 +19377,22 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19430,10 +19410,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124791521</v>
+        <v>124791467</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19442,43 +19422,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -19486,17 +19458,17 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>529586</v>
+        <v>529555</v>
       </c>
       <c r="R136" t="n">
-        <v>7000100</v>
+        <v>7000408</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -19525,7 +19497,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -19535,12 +19507,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Minst 405 plantor och 1 vinterståndare inom ca 5 x 1 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19549,13 +19521,32 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AH136" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -19573,7 +19564,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124791558</v>
+        <v>124791491</v>
       </c>
       <c r="B137" t="n">
         <v>79891</v>
@@ -19608,7 +19599,11 @@
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
@@ -19616,13 +19611,13 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>529518</v>
+        <v>529561</v>
       </c>
       <c r="R137" t="n">
-        <v>7000158</v>
+        <v>7000169</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -19651,7 +19646,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -19661,7 +19656,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Växer på en något smalare grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19714,7 +19714,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124791509</v>
+        <v>124791635</v>
       </c>
       <c r="B138" t="n">
         <v>98101</v>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19774,13 +19774,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>529658</v>
+        <v>529471</v>
       </c>
       <c r="R138" t="n">
-        <v>7000142</v>
+        <v>7000063</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Minst 360 plantor och 1 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD138" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124464307</v>
+        <v>124464556</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6480,55 +6480,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529649</v>
+        <v>529670</v>
       </c>
       <c r="R46" t="n">
-        <v>6999915</v>
+        <v>6999909</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6557,7 +6543,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6567,12 +6553,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6587,6 +6568,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6604,10 +6605,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124464556</v>
+        <v>124464307</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6616,41 +6617,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529670</v>
+        <v>529649</v>
       </c>
       <c r="R47" t="n">
-        <v>6999909</v>
+        <v>6999915</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6679,7 +6694,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6689,7 +6704,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6704,26 +6724,6 @@
       <c r="AH47" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6877,10 +6877,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124470399</v>
+        <v>124471506</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6889,55 +6889,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529662</v>
+        <v>529632</v>
       </c>
       <c r="R49" t="n">
-        <v>7000031</v>
+        <v>7000254</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6966,7 +6952,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6976,12 +6962,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6996,6 +6982,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7013,10 +7019,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124471506</v>
+        <v>124470399</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7025,41 +7031,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529632</v>
+        <v>529662</v>
       </c>
       <c r="R50" t="n">
-        <v>7000254</v>
+        <v>7000031</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7088,7 +7108,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7098,12 +7118,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7118,26 +7138,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7574,10 +7574,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124467882</v>
+        <v>124453319</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7586,55 +7586,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529678</v>
+        <v>529470</v>
       </c>
       <c r="R54" t="n">
-        <v>6999878</v>
+        <v>7000406</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7663,7 +7649,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7673,12 +7659,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7692,7 +7673,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7710,7 +7711,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124453319</v>
+        <v>124463284</v>
       </c>
       <c r="B55" t="n">
         <v>78810</v>
@@ -7750,13 +7751,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529470</v>
+        <v>529624</v>
       </c>
       <c r="R55" t="n">
-        <v>7000406</v>
+        <v>6999926</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7785,7 +7786,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7795,7 +7796,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7809,7 +7810,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -7847,10 +7848,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124463284</v>
+        <v>124467882</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7859,41 +7860,55 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529624</v>
+        <v>529678</v>
       </c>
       <c r="R56" t="n">
-        <v>6999926</v>
+        <v>6999878</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7922,7 +7937,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7932,7 +7947,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7947,26 +7967,6 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124468910</v>
+        <v>124468934</v>
       </c>
       <c r="B59" t="n">
-        <v>79892</v>
+        <v>79920</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8250,31 +8250,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8283,13 +8283,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529641</v>
+        <v>529638</v>
       </c>
       <c r="R59" t="n">
-        <v>6999979</v>
+        <v>6999974</v>
       </c>
       <c r="S59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8380,10 +8380,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124468934</v>
+        <v>124468969</v>
       </c>
       <c r="B60" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8392,43 +8392,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529638</v>
+        <v>529652</v>
       </c>
       <c r="R60" t="n">
-        <v>6999974</v>
+        <v>6999989</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8460,7 +8455,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8470,7 +8465,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8522,10 +8517,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124468969</v>
+        <v>124468910</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8538,37 +8533,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529652</v>
+        <v>529641</v>
       </c>
       <c r="R61" t="n">
-        <v>6999989</v>
+        <v>6999979</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -18419,7 +18419,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124791428</v>
+        <v>124791534</v>
       </c>
       <c r="B129" t="n">
         <v>79891</v>
@@ -18466,13 +18466,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>529468</v>
+        <v>529563</v>
       </c>
       <c r="R129" t="n">
-        <v>7000332</v>
+        <v>7000079</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -18511,12 +18511,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
+          <t>Växer på en levande sälglåga.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -18551,7 +18551,7 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -18569,10 +18569,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124791534</v>
+        <v>124791639</v>
       </c>
       <c r="B130" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -18581,48 +18581,53 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>529563</v>
+        <v>529609</v>
       </c>
       <c r="R130" t="n">
-        <v>7000079</v>
+        <v>6999925</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -18651,7 +18656,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -18661,12 +18666,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Växer på en levande sälglåga.</t>
+          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -18682,26 +18687,6 @@
       <c r="AH130" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -18719,10 +18704,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124791639</v>
+        <v>124791428</v>
       </c>
       <c r="B131" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -18731,50 +18716,45 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>529609</v>
+        <v>529468</v>
       </c>
       <c r="R131" t="n">
-        <v>6999925</v>
+        <v>7000332</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -18806,7 +18786,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -18816,12 +18796,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
+          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -18837,6 +18817,26 @@
       <c r="AH131" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -18974,10 +18974,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124791389</v>
+        <v>124791467</v>
       </c>
       <c r="B133" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -18990,41 +18990,46 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>529464</v>
+        <v>529555</v>
       </c>
       <c r="R133" t="n">
-        <v>7000252</v>
+        <v>7000408</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -19056,7 +19061,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19066,12 +19071,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Växer här ymnigt på en sälg.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -19080,7 +19085,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -19091,22 +19095,22 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -19124,10 +19128,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124470921</v>
+        <v>124791389</v>
       </c>
       <c r="B134" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -19136,55 +19140,48 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>529573</v>
+        <v>529464</v>
       </c>
       <c r="R134" t="n">
-        <v>7000067</v>
+        <v>7000252</v>
       </c>
       <c r="S134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -19213,7 +19210,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19223,12 +19220,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Minst 43 plantor inom ca 0,5 m2.</t>
+          <t>Växer här ymnigt på en sälg.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -19237,12 +19234,33 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM134" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -19260,10 +19278,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124791557</v>
+        <v>124470921</v>
       </c>
       <c r="B135" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -19272,48 +19290,55 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>529533</v>
+        <v>529573</v>
       </c>
       <c r="R135" t="n">
-        <v>7000118</v>
+        <v>7000067</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -19342,7 +19367,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19352,12 +19377,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Minst 43 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19366,33 +19391,12 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19410,10 +19414,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124791467</v>
+        <v>124791557</v>
       </c>
       <c r="B136" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19426,49 +19430,44 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>529555</v>
+        <v>529533</v>
       </c>
       <c r="R136" t="n">
-        <v>7000408</v>
+        <v>7000118</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -19497,7 +19496,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -19507,12 +19506,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19521,6 +19520,7 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
@@ -19541,12 +19541,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124464556</v>
+        <v>124469884</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6480,41 +6480,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529670</v>
+        <v>529708</v>
       </c>
       <c r="R46" t="n">
-        <v>6999909</v>
+        <v>7000000</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6543,7 +6557,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6553,7 +6567,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6567,27 +6586,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6605,10 +6604,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124464307</v>
+        <v>124464827</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6617,55 +6616,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529649</v>
+        <v>529687</v>
       </c>
       <c r="R47" t="n">
-        <v>6999915</v>
+        <v>6999902</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6694,7 +6693,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6704,12 +6703,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6741,10 +6740,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124468294</v>
+        <v>124468910</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6753,40 +6752,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6795,13 +6785,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529689</v>
+        <v>529641</v>
       </c>
       <c r="R48" t="n">
-        <v>6999938</v>
+        <v>6999979</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6830,7 +6820,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6840,12 +6830,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:21</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6860,6 +6845,26 @@
       <c r="AH48" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6877,10 +6882,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124471506</v>
+        <v>124468969</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6893,21 +6898,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6917,13 +6922,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529632</v>
+        <v>529652</v>
       </c>
       <c r="R49" t="n">
-        <v>7000254</v>
+        <v>6999989</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6952,7 +6957,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6962,12 +6967,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:50</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6981,27 +6981,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124470399</v>
+        <v>124462260</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7031,40 +7031,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7073,13 +7064,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529662</v>
+        <v>529584</v>
       </c>
       <c r="R50" t="n">
-        <v>7000031</v>
+        <v>6999935</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -7108,7 +7099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7118,12 +7109,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7138,6 +7129,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7155,7 +7166,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124462835</v>
+        <v>124465010</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -7190,7 +7201,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7209,13 +7220,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529579</v>
+        <v>529689</v>
       </c>
       <c r="R51" t="n">
-        <v>6999920</v>
+        <v>6999902</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7244,7 +7255,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7254,12 +7265,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 38 plantor inom ca 0,5 m2.</t>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7273,7 +7284,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -7291,7 +7302,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124465010</v>
+        <v>124464307</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -7326,7 +7337,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7345,10 +7356,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529689</v>
+        <v>529649</v>
       </c>
       <c r="R52" t="n">
-        <v>6999902</v>
+        <v>6999915</v>
       </c>
       <c r="S52" t="n">
         <v>8</v>
@@ -7380,7 +7391,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7390,12 +7401,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7427,7 +7438,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124462260</v>
+        <v>124464353</v>
       </c>
       <c r="B53" t="n">
         <v>79891</v>
@@ -7472,13 +7483,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529584</v>
+        <v>529642</v>
       </c>
       <c r="R53" t="n">
-        <v>6999935</v>
+        <v>6999931</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7507,7 +7518,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7517,12 +7528,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7536,7 +7542,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -7574,10 +7580,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124453319</v>
+        <v>124465430</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7590,37 +7596,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529470</v>
+        <v>529636</v>
       </c>
       <c r="R54" t="n">
-        <v>7000406</v>
+        <v>6999890</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7649,7 +7660,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7659,7 +7670,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7673,7 +7684,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7688,12 +7699,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7711,10 +7722,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124463284</v>
+        <v>124471570</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7723,25 +7734,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7751,13 +7762,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529624</v>
+        <v>529604</v>
       </c>
       <c r="R55" t="n">
-        <v>6999926</v>
+        <v>7000308</v>
       </c>
       <c r="S55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7786,7 +7797,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7796,7 +7807,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7810,27 +7821,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7848,10 +7839,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124467882</v>
+        <v>124463284</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7860,55 +7851,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529678</v>
+        <v>529624</v>
       </c>
       <c r="R56" t="n">
-        <v>6999878</v>
+        <v>6999926</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7937,7 +7914,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7947,12 +7924,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7967,6 +7939,26 @@
       <c r="AH56" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7984,10 +7976,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124471570</v>
+        <v>124462545</v>
       </c>
       <c r="B57" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7996,41 +7988,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529604</v>
+        <v>529580</v>
       </c>
       <c r="R57" t="n">
-        <v>7000308</v>
+        <v>6999910</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -8059,7 +8056,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8069,7 +8066,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8084,6 +8086,26 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -8101,10 +8123,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124462373</v>
+        <v>124467882</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8113,31 +8135,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8146,13 +8177,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529580</v>
+        <v>529678</v>
       </c>
       <c r="R58" t="n">
-        <v>6999912</v>
+        <v>6999878</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8179,14 +8210,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8200,27 +8241,7 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8238,10 +8259,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124468934</v>
+        <v>124462835</v>
       </c>
       <c r="B59" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8250,31 +8271,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8283,13 +8313,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529638</v>
+        <v>529579</v>
       </c>
       <c r="R59" t="n">
-        <v>6999974</v>
+        <v>6999920</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8318,7 +8348,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8328,7 +8358,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 38 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8342,27 +8377,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -8380,10 +8395,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124468969</v>
+        <v>124468294</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8392,41 +8407,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529652</v>
+        <v>529689</v>
       </c>
       <c r="R60" t="n">
-        <v>6999989</v>
+        <v>6999938</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8455,7 +8484,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8465,7 +8494,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8480,26 +8514,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8517,10 +8531,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124468910</v>
+        <v>124471362</v>
       </c>
       <c r="B61" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8529,31 +8543,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -8562,13 +8585,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>529641</v>
+        <v>529623</v>
       </c>
       <c r="R61" t="n">
-        <v>6999979</v>
+        <v>7000094</v>
       </c>
       <c r="S61" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8597,7 +8620,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8607,7 +8630,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:41</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8621,27 +8649,7 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -8659,10 +8667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124463366</v>
+        <v>124470399</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8671,31 +8679,40 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8704,13 +8721,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529608</v>
+        <v>529662</v>
       </c>
       <c r="R62" t="n">
-        <v>6999935</v>
+        <v>7000031</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8739,7 +8756,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8749,7 +8766,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8764,26 +8786,6 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8801,10 +8803,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124464827</v>
+        <v>124462373</v>
       </c>
       <c r="B63" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8817,51 +8819,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529687</v>
+        <v>529580</v>
       </c>
       <c r="R63" t="n">
-        <v>6999902</v>
+        <v>6999912</v>
       </c>
       <c r="S63" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8888,24 +8881,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>17:05</t>
-        </is>
-      </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
+          <t>Växer på en gammal grovbarkad skadad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8919,7 +8902,27 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8937,10 +8940,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124468603</v>
+        <v>124468934</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8949,40 +8952,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8991,13 +8985,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529657</v>
+        <v>529638</v>
       </c>
       <c r="R64" t="n">
-        <v>6999949</v>
+        <v>6999974</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9026,7 +9020,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9036,12 +9030,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,2 m2.</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9056,6 +9045,26 @@
       <c r="AH64" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9073,10 +9082,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124464353</v>
+        <v>124471506</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9089,42 +9098,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529642</v>
+        <v>529632</v>
       </c>
       <c r="R65" t="n">
-        <v>6999931</v>
+        <v>7000254</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9153,7 +9157,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9163,7 +9167,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9177,27 +9186,27 @@
       </c>
       <c r="AH65" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -9215,10 +9224,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124469884</v>
+        <v>124463366</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9227,40 +9236,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9269,10 +9269,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529708</v>
+        <v>529608</v>
       </c>
       <c r="R66" t="n">
-        <v>7000000</v>
+        <v>6999935</v>
       </c>
       <c r="S66" t="n">
         <v>7</v>
@@ -9304,7 +9304,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9314,12 +9314,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:02</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9334,6 +9329,26 @@
       <c r="AH66" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9351,7 +9366,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124471362</v>
+        <v>124468603</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9386,7 +9401,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9405,13 +9420,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529623</v>
+        <v>529657</v>
       </c>
       <c r="R67" t="n">
-        <v>7000094</v>
+        <v>6999949</v>
       </c>
       <c r="S67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9440,7 +9455,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9450,12 +9465,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 18 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9469,7 +9484,7 @@
       </c>
       <c r="AH67" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9623,10 +9638,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124462545</v>
+        <v>124464556</v>
       </c>
       <c r="B69" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9639,42 +9654,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529580</v>
+        <v>529670</v>
       </c>
       <c r="R69" t="n">
-        <v>6999910</v>
+        <v>6999909</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9703,7 +9713,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9713,12 +9723,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9732,27 +9737,27 @@
       </c>
       <c r="AH69" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9770,10 +9775,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124465430</v>
+        <v>124463397</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9786,27 +9791,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9815,13 +9820,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529636</v>
+        <v>529620</v>
       </c>
       <c r="R70" t="n">
-        <v>6999890</v>
+        <v>6999932</v>
       </c>
       <c r="S70" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9850,7 +9855,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9860,7 +9865,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9874,27 +9879,27 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -9912,10 +9917,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124463106</v>
+        <v>124471744</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9928,39 +9933,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529619</v>
+        <v>529601</v>
       </c>
       <c r="R71" t="n">
-        <v>6999959</v>
+        <v>7000312</v>
       </c>
       <c r="S71" t="n">
         <v>8</v>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10002,12 +10002,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad sälg.</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10021,27 +10016,27 @@
       </c>
       <c r="AH71" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10059,10 +10054,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124463397</v>
+        <v>124470698</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -10071,31 +10066,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10104,13 +10108,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529620</v>
+        <v>529625</v>
       </c>
       <c r="R72" t="n">
-        <v>6999932</v>
+        <v>7000048</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -10139,7 +10143,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10149,7 +10153,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10164,26 +10173,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -10201,7 +10190,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124471744</v>
+        <v>124453319</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -10241,13 +10230,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529601</v>
+        <v>529470</v>
       </c>
       <c r="R73" t="n">
-        <v>7000312</v>
+        <v>7000406</v>
       </c>
       <c r="S73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10276,7 +10265,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10286,7 +10275,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10338,10 +10327,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124470698</v>
+        <v>124463106</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10350,40 +10339,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -10392,13 +10372,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>529625</v>
+        <v>529619</v>
       </c>
       <c r="R74" t="n">
-        <v>7000048</v>
+        <v>6999959</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10427,7 +10407,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10437,12 +10417,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 0,5 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10456,7 +10436,27 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10474,10 +10474,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124541347</v>
+        <v>124540904</v>
       </c>
       <c r="B75" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10490,40 +10490,44 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>529549</v>
+        <v>529475</v>
       </c>
       <c r="R75" t="n">
-        <v>7000412</v>
+        <v>7000452</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10552,7 +10556,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10562,12 +10566,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>På en tallstam.</t>
+          <t>Fertil lunglav på en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10582,22 +10586,17 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -10607,7 +10606,7 @@
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -10625,7 +10624,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124541322</v>
+        <v>124541265</v>
       </c>
       <c r="B76" t="n">
         <v>78810</v>
@@ -10668,10 +10667,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>529565</v>
+        <v>529530</v>
       </c>
       <c r="R76" t="n">
-        <v>7000430</v>
+        <v>7000434</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10703,7 +10702,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10713,7 +10712,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10766,10 +10770,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124541341</v>
+        <v>124540781</v>
       </c>
       <c r="B77" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10778,20 +10782,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10799,20 +10803,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -10826,10 +10822,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>529549</v>
+        <v>529468</v>
       </c>
       <c r="R77" t="n">
-        <v>7000412</v>
+        <v>7000465</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -10861,7 +10857,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10871,7 +10867,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10885,12 +10886,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -10908,10 +10924,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124540904</v>
+        <v>124540447</v>
       </c>
       <c r="B78" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10924,30 +10940,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -10955,10 +10967,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>529475</v>
+        <v>529509</v>
       </c>
       <c r="R78" t="n">
-        <v>7000452</v>
+        <v>7000467</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10990,7 +11002,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11000,12 +11012,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Fertil lunglav på en lutande smal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11020,27 +11032,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11058,7 +11070,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124540781</v>
+        <v>124540712</v>
       </c>
       <c r="B79" t="n">
         <v>57513</v>
@@ -11096,7 +11108,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -11110,13 +11122,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>529468</v>
+        <v>529477</v>
       </c>
       <c r="R79" t="n">
-        <v>7000465</v>
+        <v>7000468</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -11145,7 +11157,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -11155,12 +11167,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack i riklig mängd, både färska och äldre, på en granstam med kådaflöden.</t>
+          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -11174,7 +11186,12 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Gammal granskog med fin bäckmiljö.</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
@@ -11189,12 +11206,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -11362,10 +11379,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124541247</v>
+        <v>124540608</v>
       </c>
       <c r="B81" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11378,29 +11395,28 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -11410,10 +11426,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>529530</v>
+        <v>529477</v>
       </c>
       <c r="R81" t="n">
-        <v>7000434</v>
+        <v>7000468</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11445,7 +11461,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11455,12 +11471,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11469,6 +11485,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11489,12 +11506,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11512,7 +11529,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124540712</v>
+        <v>124540308</v>
       </c>
       <c r="B82" t="n">
         <v>57513</v>
@@ -11550,7 +11567,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -11564,10 +11581,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>529477</v>
+        <v>529573</v>
       </c>
       <c r="R82" t="n">
-        <v>7000468</v>
+        <v>7000446</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11599,7 +11616,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11609,12 +11626,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Gammalt bohål i en nu knäckt död liggande granstam med granticka intill en bäck. När granstammen stod upp fanns bohålet på ca 2 meters höjd över marken.</t>
+          <t>Ringhack, äldre, en bit upp på en granstam.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11631,11 +11648,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>Gammal granskog med fin bäckmiljö.</t>
-        </is>
-      </c>
       <c r="AJ82" t="inlineStr">
         <is>
           <t>gran</t>
@@ -11648,12 +11660,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11671,10 +11683,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124540608</v>
+        <v>124541216</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11687,28 +11699,29 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
@@ -11718,13 +11731,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>529477</v>
+        <v>529524</v>
       </c>
       <c r="R83" t="n">
-        <v>7000468</v>
+        <v>7000440</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11753,7 +11766,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11763,12 +11776,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Fruktkroppar som växer i en knäckt liggande död granstam med gammalt bohål i.</t>
+          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11777,7 +11790,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -11798,12 +11810,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11821,10 +11833,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124541265</v>
+        <v>124541247</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11837,26 +11849,31 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -11914,7 +11931,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11923,7 +11940,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -11944,12 +11960,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -11967,7 +11983,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124540447</v>
+        <v>124541322</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -12006,14 +12022,14 @@
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>529509</v>
+        <v>529565</v>
       </c>
       <c r="R85" t="n">
-        <v>7000467</v>
+        <v>7000430</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -12045,7 +12061,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -12055,12 +12071,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -12113,10 +12124,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124541216</v>
+        <v>124541341</v>
       </c>
       <c r="B86" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -12125,20 +12136,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -12146,25 +12157,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>529524</v>
+        <v>529549</v>
       </c>
       <c r="R86" t="n">
-        <v>7000440</v>
+        <v>7000412</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -12196,7 +12219,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12206,12 +12229,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en granhögstubbe.</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -12228,24 +12246,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12263,10 +12266,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124540308</v>
+        <v>124541347</v>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -12279,49 +12282,40 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>529573</v>
+        <v>529549</v>
       </c>
       <c r="R87" t="n">
-        <v>7000446</v>
+        <v>7000412</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -12350,7 +12344,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -12360,12 +12354,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, en bit upp på en granstam.</t>
+          <t>På en tallstam.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12374,6 +12368,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -12382,24 +12377,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
+        </is>
+      </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124541689</v>
+        <v>124541662</v>
       </c>
       <c r="B88" t="n">
         <v>78810</v>
@@ -12460,13 +12460,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>529457</v>
+        <v>529500</v>
       </c>
       <c r="R88" t="n">
-        <v>7000423</v>
+        <v>7000417</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -12563,7 +12563,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124541545</v>
+        <v>124541689</v>
       </c>
       <c r="B89" t="n">
         <v>78810</v>
@@ -12602,14 +12602,14 @@
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>529524</v>
+        <v>529457</v>
       </c>
       <c r="R89" t="n">
-        <v>7000430</v>
+        <v>7000423</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -12641,7 +12641,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -12709,7 +12709,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124541662</v>
+        <v>124541545</v>
       </c>
       <c r="B90" t="n">
         <v>78810</v>
@@ -12748,17 +12748,17 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>529500</v>
+        <v>529524</v>
       </c>
       <c r="R90" t="n">
-        <v>7000417</v>
+        <v>7000430</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -12797,7 +12797,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -12855,10 +12855,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124541684</v>
+        <v>124541526</v>
       </c>
       <c r="B91" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12871,41 +12871,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>529457</v>
+        <v>529524</v>
       </c>
       <c r="R91" t="n">
-        <v>7000423</v>
+        <v>7000430</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12937,7 +12938,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12947,12 +12948,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12961,33 +12962,32 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124541526</v>
+        <v>124541707</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -13046,17 +13046,21 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>529524</v>
+        <v>529452</v>
       </c>
       <c r="R92" t="n">
-        <v>7000430</v>
+        <v>7000440</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -13088,7 +13092,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13098,12 +13102,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13117,7 +13121,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -13155,10 +13159,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124541568</v>
+        <v>124541684</v>
       </c>
       <c r="B93" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13171,49 +13175,44 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>529514</v>
+        <v>529457</v>
       </c>
       <c r="R93" t="n">
-        <v>7000432</v>
+        <v>7000423</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -13242,7 +13241,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13252,12 +13251,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13266,32 +13265,33 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -13309,7 +13309,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124541707</v>
+        <v>124541568</v>
       </c>
       <c r="B94" t="n">
         <v>57513</v>
@@ -13347,7 +13347,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -13361,13 +13361,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>529452</v>
+        <v>529514</v>
       </c>
       <c r="R94" t="n">
-        <v>7000440</v>
+        <v>7000432</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -13406,12 +13406,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -13425,7 +13425,7 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -13463,10 +13463,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124791162</v>
+        <v>124791073</v>
       </c>
       <c r="B95" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -13475,20 +13475,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -13498,11 +13498,7 @@
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -13510,13 +13506,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>529464</v>
+        <v>529482</v>
       </c>
       <c r="R95" t="n">
-        <v>7000280</v>
+        <v>7000366</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -13545,7 +13541,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -13555,12 +13551,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Intill lunglav på en gammal sälg.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -13580,22 +13571,22 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -13759,10 +13750,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124791073</v>
+        <v>124791260</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -13771,30 +13762,34 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -13802,13 +13797,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>529482</v>
+        <v>529442</v>
       </c>
       <c r="R97" t="n">
-        <v>7000366</v>
+        <v>7000277</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -13837,7 +13832,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -13847,7 +13842,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På en gammal sälg intill lunglav.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13867,22 +13867,22 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -13900,10 +13900,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124791260</v>
+        <v>124791162</v>
       </c>
       <c r="B98" t="n">
-        <v>79927</v>
+        <v>79926</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13916,28 +13916,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -13947,10 +13947,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>529442</v>
+        <v>529464</v>
       </c>
       <c r="R98" t="n">
-        <v>7000277</v>
+        <v>7000280</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13992,12 +13992,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>På en gammal sälg intill lunglav.</t>
+          <t>Intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -14050,7 +14050,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124791153</v>
+        <v>124791246</v>
       </c>
       <c r="B99" t="n">
         <v>79891</v>
@@ -14097,10 +14097,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>529464</v>
+        <v>529442</v>
       </c>
       <c r="R99" t="n">
-        <v>7000280</v>
+        <v>7000277</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -14142,12 +14142,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Gott om bålar på en gammal sälg med grov fårad bark.</t>
+          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -14200,10 +14200,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124791246</v>
+        <v>124791104</v>
       </c>
       <c r="B100" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -14216,28 +14216,36 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
@@ -14247,10 +14255,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>529442</v>
+        <v>529457</v>
       </c>
       <c r="R100" t="n">
-        <v>7000277</v>
+        <v>7000281</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -14282,7 +14290,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -14292,12 +14300,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Rikligt med lunglav på en gammal grovbarkad sälg.</t>
+          <t>Rikligt med garnlav på många granar! Och här finns fertila exemplar.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -14312,27 +14320,32 @@
       </c>
       <c r="AH100" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Många granar.</t>
         </is>
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies # Många granar.</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -14350,10 +14363,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124791104</v>
+        <v>124791066</v>
       </c>
       <c r="B101" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -14366,36 +14379,28 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
@@ -14405,13 +14410,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>529457</v>
+        <v>529482</v>
       </c>
       <c r="R101" t="n">
-        <v>7000281</v>
+        <v>7000366</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -14440,7 +14445,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -14450,12 +14455,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>12:23</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav på många granar! Och här finns fertila exemplar.</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -14470,32 +14470,27 @@
       </c>
       <c r="AH101" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Många granar.</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Många granar.</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -14513,7 +14508,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124791066</v>
+        <v>124791153</v>
       </c>
       <c r="B102" t="n">
         <v>79891</v>
@@ -14560,13 +14555,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>529482</v>
+        <v>529464</v>
       </c>
       <c r="R102" t="n">
-        <v>7000366</v>
+        <v>7000280</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -14595,7 +14590,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -14605,7 +14600,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Gott om bålar på en gammal sälg med grov fårad bark.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -14658,10 +14658,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124791630</v>
+        <v>124791345</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -14670,61 +14670,48 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>529505</v>
+        <v>529435</v>
       </c>
       <c r="R103" t="n">
-        <v>7000073</v>
+        <v>7000275</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -14753,7 +14740,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -14763,12 +14750,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Minst 240 plantor inom ca 3 m2 yta.</t>
+          <t>Gott om lunglavsbålar på en gammal tvåstammig sälg.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -14784,6 +14771,26 @@
       <c r="AH103" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -14801,10 +14808,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124791504</v>
+        <v>124791521</v>
       </c>
       <c r="B104" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14813,45 +14820,58 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>529620</v>
+        <v>529586</v>
       </c>
       <c r="R104" t="n">
-        <v>7000131</v>
+        <v>7000100</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14883,7 +14903,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -14893,12 +14913,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och lunglav.</t>
+          <t>Minst 405 plantor och 1 vinterståndare inom ca 5 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -14914,26 +14934,6 @@
       <c r="AH104" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -14951,7 +14951,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124791509</v>
+        <v>124791628</v>
       </c>
       <c r="B105" t="n">
         <v>98101</v>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -15011,10 +15011,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>529658</v>
+        <v>529519</v>
       </c>
       <c r="R105" t="n">
-        <v>7000142</v>
+        <v>7000108</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15056,12 +15056,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Minst 110 plantor och 2 vinterståndare inom ca 2 x 2 m2 yta.</t>
+          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -15094,10 +15094,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124791358</v>
+        <v>124791502</v>
       </c>
       <c r="B106" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -15106,32 +15106,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
@@ -15141,13 +15141,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>529435</v>
+        <v>529620</v>
       </c>
       <c r="R106" t="n">
-        <v>7000275</v>
+        <v>7000131</v>
       </c>
       <c r="S106" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15186,12 +15186,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg med lunglav.</t>
+          <t>På en sälg tillsammans med lunglav och stuplav.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -15211,22 +15211,22 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -15244,10 +15244,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124791502</v>
+        <v>124791467</v>
       </c>
       <c r="B107" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -15256,48 +15256,53 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>529620</v>
+        <v>529555</v>
       </c>
       <c r="R107" t="n">
-        <v>7000131</v>
+        <v>7000408</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -15326,7 +15331,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -15336,12 +15341,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med lunglav och stuplav.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -15350,7 +15355,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -15361,22 +15365,22 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -15394,10 +15398,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124791493</v>
+        <v>124791504</v>
       </c>
       <c r="B108" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -15406,61 +15410,48 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>529600</v>
+        <v>529620</v>
       </c>
       <c r="R108" t="n">
-        <v>7000174</v>
+        <v>7000131</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -15489,7 +15480,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -15499,12 +15490,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
+          <t>På en sälg tillsammans med luddlav och lunglav.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -15520,6 +15511,26 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -15537,10 +15548,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124791492</v>
+        <v>124791501</v>
       </c>
       <c r="B109" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -15549,32 +15560,32 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -15584,10 +15595,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>529561</v>
+        <v>529620</v>
       </c>
       <c r="R109" t="n">
-        <v>7000169</v>
+        <v>7000131</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -15619,7 +15630,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -15629,12 +15640,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Växer intill lunglav på en gammal sälg.</t>
+          <t>På en sälg tillsammans med luddlav och stuplav.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -15687,10 +15698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124791468</v>
+        <v>124791641</v>
       </c>
       <c r="B110" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -15699,35 +15710,43 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -15735,14 +15754,14 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>529561</v>
+        <v>529611</v>
       </c>
       <c r="R110" t="n">
-        <v>7000407</v>
+        <v>7000387</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -15774,7 +15793,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -15784,12 +15803,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
+          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15798,32 +15817,13 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15841,10 +15841,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124791560</v>
+        <v>124791633</v>
       </c>
       <c r="B111" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15853,43 +15853,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -15897,14 +15889,14 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>529512</v>
+        <v>529464</v>
       </c>
       <c r="R111" t="n">
-        <v>7000130</v>
+        <v>7000057</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -15936,7 +15928,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15946,12 +15938,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Minst 163 plantor inom ca 2 x 1 m2 yta.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15960,7 +15947,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -15984,10 +15970,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124791638</v>
+        <v>124791640</v>
       </c>
       <c r="B112" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -16000,30 +15986,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -16031,10 +16013,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>529635</v>
+        <v>529609</v>
       </c>
       <c r="R112" t="n">
-        <v>6999915</v>
+        <v>6999925</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -16066,7 +16048,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -16076,7 +16058,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -16129,7 +16116,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124791464</v>
+        <v>124791470</v>
       </c>
       <c r="B113" t="n">
         <v>79891</v>
@@ -16176,10 +16163,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>529530</v>
+        <v>529564</v>
       </c>
       <c r="R113" t="n">
-        <v>7000400</v>
+        <v>7000301</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -16211,7 +16198,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -16221,12 +16208,12 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Fertila bålar.</t>
+          <t>Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -16254,6 +16241,11 @@
           <t>Salix caprea</t>
         </is>
       </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>En smalväxt sälg.</t>
+        </is>
+      </c>
       <c r="AM113" t="inlineStr">
         <is>
           <t>Bark på levande träd</t>
@@ -16261,7 +16253,7 @@
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg.</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -16279,10 +16271,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124791408</v>
+        <v>124791638</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -16295,34 +16287,30 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -16330,10 +16318,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>529456</v>
+        <v>529635</v>
       </c>
       <c r="R114" t="n">
-        <v>7000329</v>
+        <v>6999915</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -16365,7 +16353,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -16375,12 +16363,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:48</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -16400,22 +16383,22 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -16433,10 +16416,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124791521</v>
+        <v>124791491</v>
       </c>
       <c r="B115" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16445,58 +16428,45 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>529586</v>
+        <v>529561</v>
       </c>
       <c r="R115" t="n">
-        <v>7000100</v>
+        <v>7000169</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -16528,7 +16498,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -16538,12 +16508,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Minst 405 plantor och 1 vinterståndare inom ca 5 x 1 m2 yta.</t>
+          <t>Växer på en något smalare grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16559,6 +16529,26 @@
       <c r="AH115" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -16576,10 +16566,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124791641</v>
+        <v>124791494</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -16588,58 +16578,41 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>529611</v>
+        <v>529596</v>
       </c>
       <c r="R116" t="n">
-        <v>7000387</v>
+        <v>7000265</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -16671,7 +16644,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -16681,12 +16654,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16702,6 +16670,26 @@
       <c r="AH116" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -16719,10 +16707,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124791496</v>
+        <v>124791493</v>
       </c>
       <c r="B117" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -16731,41 +16719,58 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>529624</v>
+        <v>529600</v>
       </c>
       <c r="R117" t="n">
-        <v>7000244</v>
+        <v>7000174</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -16797,7 +16802,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -16807,7 +16812,12 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -16981,10 +16991,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124791470</v>
+        <v>124791557</v>
       </c>
       <c r="B119" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -16997,21 +17007,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -17028,10 +17038,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>529564</v>
+        <v>529533</v>
       </c>
       <c r="R119" t="n">
-        <v>7000301</v>
+        <v>7000118</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -17063,7 +17073,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -17073,12 +17083,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Fertila bålar med apothecier.</t>
+          <t>Långväxt fertil garnlav.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -17098,27 +17108,22 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL119" t="inlineStr">
-        <is>
-          <t>En smalväxt sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En smalväxt sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -17136,10 +17141,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124791452</v>
+        <v>124791492</v>
       </c>
       <c r="B120" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -17148,46 +17153,45 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>529510</v>
+        <v>529561</v>
       </c>
       <c r="R120" t="n">
-        <v>7000411</v>
+        <v>7000169</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -17219,7 +17223,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -17229,12 +17233,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre på stambasen av en gran.</t>
+          <t>Växer intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -17243,6 +17247,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -17253,22 +17258,22 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17286,10 +17291,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124791640</v>
+        <v>124791374</v>
       </c>
       <c r="B121" t="n">
-        <v>79891</v>
+        <v>105102</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17298,41 +17303,50 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221725</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>529609</v>
+        <v>529435</v>
       </c>
       <c r="R121" t="n">
-        <v>6999925</v>
+        <v>7000275</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -17362,24 +17376,9 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>På en något smalare sälg.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17395,26 +17394,6 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -17586,10 +17565,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124791633</v>
+        <v>124791639</v>
       </c>
       <c r="B123" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -17598,35 +17577,35 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -17634,17 +17613,17 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>529464</v>
+        <v>529609</v>
       </c>
       <c r="R123" t="n">
-        <v>7000057</v>
+        <v>6999925</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -17673,7 +17652,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -17683,7 +17662,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -17692,6 +17676,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -17715,7 +17700,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124791628</v>
+        <v>124470921</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -17750,7 +17735,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -17763,25 +17748,19 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>529519</v>
+        <v>529573</v>
       </c>
       <c r="R124" t="n">
-        <v>7000108</v>
+        <v>7000067</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -17810,7 +17789,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -17820,12 +17799,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
+          <t>Minst 43 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17834,13 +17813,12 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -17858,10 +17836,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124791494</v>
+        <v>124791496</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -17870,25 +17848,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -17901,10 +17879,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>529596</v>
+        <v>529624</v>
       </c>
       <c r="R125" t="n">
-        <v>7000265</v>
+        <v>7000244</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -17936,7 +17914,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -17946,7 +17924,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -17962,26 +17940,6 @@
       <c r="AH125" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -17999,10 +17957,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124791513</v>
+        <v>124791452</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -18011,61 +17969,49 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>529701</v>
+        <v>529510</v>
       </c>
       <c r="R126" t="n">
-        <v>7000103</v>
+        <v>7000411</v>
       </c>
       <c r="S126" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -18092,14 +18038,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Ringhack, färska och äldre på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -18108,13 +18064,32 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -18132,10 +18107,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124791391</v>
+        <v>124791389</v>
       </c>
       <c r="B127" t="n">
-        <v>57883</v>
+        <v>79891</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -18144,48 +18119,35 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
@@ -18240,18 +18202,44 @@
           <t>12:42</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Växer här ymnigt på en sälg.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -18269,7 +18257,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124791501</v>
+        <v>124791534</v>
       </c>
       <c r="B128" t="n">
         <v>79891</v>
@@ -18316,10 +18304,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>529620</v>
+        <v>529563</v>
       </c>
       <c r="R128" t="n">
-        <v>7000131</v>
+        <v>7000079</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -18351,7 +18339,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -18361,12 +18349,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och stuplav.</t>
+          <t>Växer på en levande sälglåga.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18401,7 +18389,7 @@
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -18419,10 +18407,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124791534</v>
+        <v>124791408</v>
       </c>
       <c r="B129" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18435,30 +18423,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -18466,13 +18458,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>529563</v>
+        <v>529456</v>
       </c>
       <c r="R129" t="n">
-        <v>7000079</v>
+        <v>7000329</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -18501,7 +18493,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -18511,12 +18503,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Växer på en levande sälglåga.</t>
+          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -18536,22 +18528,22 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -18569,7 +18561,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124791639</v>
+        <v>124791513</v>
       </c>
       <c r="B130" t="n">
         <v>98101</v>
@@ -18602,8 +18594,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K130" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -18621,10 +18621,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>529609</v>
+        <v>529701</v>
       </c>
       <c r="R130" t="n">
-        <v>6999925</v>
+        <v>7000103</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -18654,24 +18654,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>16:37</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Minst 140 plantor och 7 vinterståndare inom ca 1 m2 yta intill en smal sälg med lunglav.</t>
+          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -18704,10 +18694,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124791428</v>
+        <v>124791560</v>
       </c>
       <c r="B131" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -18716,48 +18706,61 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>529468</v>
+        <v>529512</v>
       </c>
       <c r="R131" t="n">
-        <v>7000332</v>
+        <v>7000130</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -18786,7 +18789,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -18796,12 +18799,12 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
+          <t>Minst 163 plantor inom ca 2 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -18817,26 +18820,6 @@
       <c r="AH131" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -18854,10 +18837,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124791374</v>
+        <v>124791464</v>
       </c>
       <c r="B132" t="n">
-        <v>105102</v>
+        <v>79891</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -18866,53 +18849,48 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>529435</v>
+        <v>529530</v>
       </c>
       <c r="R132" t="n">
-        <v>7000275</v>
+        <v>7000400</v>
       </c>
       <c r="S132" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -18939,9 +18917,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -18957,6 +18950,26 @@
       <c r="AH132" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -18974,7 +18987,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124791467</v>
+        <v>124791468</v>
       </c>
       <c r="B133" t="n">
         <v>57513</v>
@@ -19026,10 +19039,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>529555</v>
+        <v>529561</v>
       </c>
       <c r="R133" t="n">
-        <v>7000408</v>
+        <v>7000407</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -19061,7 +19074,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19071,12 +19084,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -19128,7 +19141,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124791389</v>
+        <v>124791428</v>
       </c>
       <c r="B134" t="n">
         <v>79891</v>
@@ -19171,14 +19184,14 @@
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>529464</v>
+        <v>529468</v>
       </c>
       <c r="R134" t="n">
-        <v>7000252</v>
+        <v>7000332</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -19210,7 +19223,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -19220,12 +19233,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Växer här ymnigt på en sälg.</t>
+          <t>Växer här hyfsat gott om bålar på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -19278,7 +19291,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124470921</v>
+        <v>124791509</v>
       </c>
       <c r="B135" t="n">
         <v>98101</v>
@@ -19313,7 +19326,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>110</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -19326,19 +19339,25 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>529573</v>
+        <v>529658</v>
       </c>
       <c r="R135" t="n">
-        <v>7000067</v>
+        <v>7000142</v>
       </c>
       <c r="S135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -19367,7 +19386,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -19377,12 +19396,12 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Minst 43 plantor inom ca 0,5 m2.</t>
+          <t>Minst 110 plantor och 2 vinterståndare inom ca 2 x 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -19391,12 +19410,13 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AH135" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -19414,10 +19434,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124791557</v>
+        <v>124791635</v>
       </c>
       <c r="B136" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -19426,48 +19446,61 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>529533</v>
+        <v>529471</v>
       </c>
       <c r="R136" t="n">
-        <v>7000118</v>
+        <v>7000063</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -19496,7 +19529,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -19506,12 +19539,12 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Långväxt fertil garnlav.</t>
+          <t>Minst 360 plantor och 1 vinterståndare inom ca 5 m2 yta.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -19527,26 +19560,6 @@
       <c r="AH136" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>
@@ -19564,10 +19577,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124791491</v>
+        <v>124791391</v>
       </c>
       <c r="B137" t="n">
-        <v>79891</v>
+        <v>57883</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -19576,48 +19589,61 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>529561</v>
+        <v>529464</v>
       </c>
       <c r="R137" t="n">
-        <v>7000169</v>
+        <v>7000252</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -19646,7 +19672,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -19656,12 +19682,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Växer på en något smalare grovbarkad sälg.</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -19670,33 +19691,12 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AH137" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -19714,7 +19714,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124791635</v>
+        <v>124791630</v>
       </c>
       <c r="B138" t="n">
         <v>98101</v>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -19774,13 +19774,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>529471</v>
+        <v>529505</v>
       </c>
       <c r="R138" t="n">
-        <v>7000063</v>
+        <v>7000073</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Minst 360 plantor och 1 vinterståndare inom ca 5 m2 yta.</t>
+          <t>Minst 240 plantor inom ca 3 m2 yta.</t>
         </is>
       </c>
       <c r="AD138" t="b">

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -8667,10 +8667,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124470399</v>
+        <v>124471506</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8679,55 +8679,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529662</v>
+        <v>529632</v>
       </c>
       <c r="R62" t="n">
-        <v>7000031</v>
+        <v>7000254</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8756,7 +8742,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8766,12 +8752,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,2 m2.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8786,6 +8772,26 @@
       <c r="AH62" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -9082,10 +9088,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124471506</v>
+        <v>124470399</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9094,41 +9100,55 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>529632</v>
+        <v>529662</v>
       </c>
       <c r="R65" t="n">
-        <v>7000254</v>
+        <v>7000031</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -9157,7 +9177,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -9167,12 +9187,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 4 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -9187,26 +9207,6 @@
       <c r="AH65" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -12855,10 +12855,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124541526</v>
+        <v>124541684</v>
       </c>
       <c r="B91" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -12871,42 +12871,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>529524</v>
+        <v>529457</v>
       </c>
       <c r="R91" t="n">
-        <v>7000430</v>
+        <v>7000423</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -12938,7 +12937,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -12948,12 +12947,12 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12962,32 +12961,33 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124541707</v>
+        <v>124541526</v>
       </c>
       <c r="B92" t="n">
         <v>57513</v>
@@ -13046,21 +13046,17 @@
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>529452</v>
+        <v>529524</v>
       </c>
       <c r="R92" t="n">
-        <v>7000440</v>
+        <v>7000430</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -13092,7 +13088,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -13102,12 +13098,12 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -13121,7 +13117,7 @@
       </c>
       <c r="AH92" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -13159,10 +13155,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124541684</v>
+        <v>124541707</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -13175,41 +13171,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>529457</v>
+        <v>529452</v>
       </c>
       <c r="R93" t="n">
-        <v>7000423</v>
+        <v>7000440</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -13241,7 +13242,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -13251,12 +13252,12 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Rikligt med lunglavsbålar på en smal lutande sälg.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en granstam.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -13265,7 +13266,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -13276,22 +13276,22 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -14951,10 +14951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124791628</v>
+        <v>124791502</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14963,58 +14963,45 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>529519</v>
+        <v>529620</v>
       </c>
       <c r="R105" t="n">
-        <v>7000108</v>
+        <v>7000131</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -15046,7 +15033,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15056,12 +15043,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
+          <t>På en sälg tillsammans med lunglav och stuplav.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -15077,6 +15064,26 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -15094,10 +15101,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124791502</v>
+        <v>124791628</v>
       </c>
       <c r="B106" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -15106,45 +15113,58 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>529620</v>
+        <v>529519</v>
       </c>
       <c r="R106" t="n">
-        <v>7000131</v>
+        <v>7000108</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -15176,7 +15196,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15186,12 +15206,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med lunglav och stuplav.</t>
+          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -15207,26 +15227,6 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -15398,10 +15398,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124791504</v>
+        <v>124791633</v>
       </c>
       <c r="B108" t="n">
-        <v>79920</v>
+        <v>56714</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -15410,45 +15410,50 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6462</v>
+        <v>102612</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>529620</v>
+        <v>529464</v>
       </c>
       <c r="R108" t="n">
-        <v>7000131</v>
+        <v>7000057</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -15480,7 +15485,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -15490,12 +15495,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>På en sälg tillsammans med luddlav och lunglav.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -15504,33 +15504,12 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -15548,10 +15527,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124791501</v>
+        <v>124791504</v>
       </c>
       <c r="B109" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -15560,32 +15539,32 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -15645,7 +15624,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och stuplav.</t>
+          <t>På en sälg tillsammans med luddlav och lunglav.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -15698,10 +15677,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124791641</v>
+        <v>124791501</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -15710,61 +15689,48 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>529611</v>
+        <v>529620</v>
       </c>
       <c r="R110" t="n">
-        <v>7000387</v>
+        <v>7000131</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -15793,7 +15759,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -15803,12 +15769,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+          <t>På en sälg tillsammans med luddlav och stuplav.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15824,6 +15790,26 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15841,10 +15827,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124791633</v>
+        <v>124791641</v>
       </c>
       <c r="B111" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15853,35 +15839,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -15889,17 +15883,17 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>529464</v>
+        <v>529611</v>
       </c>
       <c r="R111" t="n">
-        <v>7000057</v>
+        <v>7000387</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -15928,7 +15922,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15938,7 +15932,12 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15947,6 +15946,7 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -16416,10 +16416,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124791491</v>
+        <v>124791493</v>
       </c>
       <c r="B115" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -16428,48 +16428,61 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>529561</v>
+        <v>529600</v>
       </c>
       <c r="R115" t="n">
-        <v>7000169</v>
+        <v>7000174</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -16498,7 +16511,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -16508,12 +16521,12 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Växer på en något smalare grovbarkad sälg.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -16529,26 +16542,6 @@
       <c r="AH115" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -16566,10 +16559,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124791494</v>
+        <v>124791491</v>
       </c>
       <c r="B116" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -16582,26 +16575,30 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -16609,13 +16606,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>529596</v>
+        <v>529561</v>
       </c>
       <c r="R116" t="n">
-        <v>7000265</v>
+        <v>7000169</v>
       </c>
       <c r="S116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -16644,7 +16641,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -16654,7 +16651,12 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Växer på en något smalare grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -16674,22 +16676,22 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -16707,10 +16709,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124791493</v>
+        <v>124791494</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -16719,58 +16721,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>529600</v>
+        <v>529596</v>
       </c>
       <c r="R117" t="n">
-        <v>7000174</v>
+        <v>7000265</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -16802,7 +16787,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -16812,12 +16797,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>14:09</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 8 m2 yta vid en gammal stubbe.</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -16833,6 +16813,26 @@
       <c r="AH117" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -17141,10 +17141,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124791492</v>
+        <v>124791374</v>
       </c>
       <c r="B120" t="n">
-        <v>79927</v>
+        <v>105102</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -17157,44 +17157,49 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>221725</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>529561</v>
+        <v>529435</v>
       </c>
       <c r="R120" t="n">
-        <v>7000169</v>
+        <v>7000275</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -17221,24 +17226,9 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Växer intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -17254,26 +17244,6 @@
       <c r="AH120" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -17291,10 +17261,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124791374</v>
+        <v>124791492</v>
       </c>
       <c r="B121" t="n">
-        <v>105102</v>
+        <v>79927</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -17307,49 +17277,44 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221725</v>
+        <v>6464</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>529435</v>
+        <v>529561</v>
       </c>
       <c r="R121" t="n">
-        <v>7000275</v>
+        <v>7000169</v>
       </c>
       <c r="S121" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -17376,9 +17341,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Växer intill lunglav på en gammal sälg.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -17394,6 +17374,26 @@
       <c r="AH121" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -18107,10 +18107,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124791389</v>
+        <v>124791513</v>
       </c>
       <c r="B127" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -18119,45 +18119,58 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>529464</v>
+        <v>529701</v>
       </c>
       <c r="R127" t="n">
-        <v>7000252</v>
+        <v>7000103</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -18187,24 +18200,14 @@
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Växer här ymnigt på en sälg.</t>
+          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -18220,26 +18223,6 @@
       <c r="AH127" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM127" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -18257,7 +18240,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124791534</v>
+        <v>124791389</v>
       </c>
       <c r="B128" t="n">
         <v>79891</v>
@@ -18300,17 +18283,17 @@
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>529563</v>
+        <v>529464</v>
       </c>
       <c r="R128" t="n">
-        <v>7000079</v>
+        <v>7000252</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -18339,7 +18322,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -18349,12 +18332,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Växer på en levande sälglåga.</t>
+          <t>Växer här ymnigt på en sälg.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -18389,7 +18372,7 @@
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -18407,10 +18390,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124791408</v>
+        <v>124791534</v>
       </c>
       <c r="B129" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -18423,34 +18406,30 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
@@ -18458,13 +18437,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>529456</v>
+        <v>529563</v>
       </c>
       <c r="R129" t="n">
-        <v>7000329</v>
+        <v>7000079</v>
       </c>
       <c r="S129" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -18493,7 +18472,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -18503,12 +18482,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
+          <t>Växer på en levande sälglåga.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -18528,22 +18507,22 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # På sälglåga. # Salix caprea</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -18561,10 +18540,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124791513</v>
+        <v>124791408</v>
       </c>
       <c r="B130" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -18573,58 +18552,49 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>529701</v>
+        <v>529456</v>
       </c>
       <c r="R130" t="n">
-        <v>7000103</v>
+        <v>7000329</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -18654,14 +18624,24 @@
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-04-26</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Minst 21 plantor och 1 vinterståndare inom ca 1 m2 yta.</t>
+          <t>Riklig med bålar på en död stående gran och även på flera levande granar.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -18677,6 +18657,26 @@
       <c r="AH130" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -9366,10 +9366,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124468603</v>
+        <v>124464556</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9378,55 +9378,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529657</v>
+        <v>529670</v>
       </c>
       <c r="R67" t="n">
-        <v>6999949</v>
+        <v>6999909</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9455,7 +9441,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9465,12 +9451,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:32</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 0,2 m2.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9485,6 +9466,26 @@
       <c r="AH67" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9502,10 +9503,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124465862</v>
+        <v>124463397</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9514,40 +9515,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9556,13 +9548,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529657</v>
+        <v>529620</v>
       </c>
       <c r="R68" t="n">
-        <v>6999868</v>
+        <v>6999932</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9591,7 +9583,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9601,12 +9593,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9620,7 +9607,27 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -9638,10 +9645,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124464556</v>
+        <v>124468603</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9650,41 +9657,55 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529670</v>
+        <v>529657</v>
       </c>
       <c r="R69" t="n">
-        <v>6999909</v>
+        <v>6999949</v>
       </c>
       <c r="S69" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9713,7 +9734,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9723,7 +9744,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Minst 18 plantor inom ca 0,2 m2.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9738,26 +9764,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9775,10 +9781,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124463397</v>
+        <v>124465862</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9787,31 +9793,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9820,13 +9835,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529620</v>
+        <v>529657</v>
       </c>
       <c r="R70" t="n">
-        <v>6999932</v>
+        <v>6999868</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9855,7 +9870,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9865,7 +9880,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9879,27 +9899,7 @@
       </c>
       <c r="AH70" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13012,7 +13012,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -14951,10 +14951,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124791502</v>
+        <v>124791628</v>
       </c>
       <c r="B105" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -14963,45 +14963,58 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>529620</v>
+        <v>529519</v>
       </c>
       <c r="R105" t="n">
-        <v>7000131</v>
+        <v>7000108</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -15033,7 +15046,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -15043,12 +15056,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med lunglav och stuplav.</t>
+          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -15064,26 +15077,6 @@
       <c r="AH105" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -15101,10 +15094,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124791628</v>
+        <v>124791502</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -15113,58 +15106,45 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>529519</v>
+        <v>529620</v>
       </c>
       <c r="R106" t="n">
-        <v>7000108</v>
+        <v>7000131</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -15196,7 +15176,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -15206,12 +15186,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Minst 400 plantor inom ca 2 m2 yta.</t>
+          <t>På en sälg tillsammans med lunglav och stuplav.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -15227,6 +15207,26 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -15251,7 +15251,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -15398,10 +15398,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124791633</v>
+        <v>124791504</v>
       </c>
       <c r="B108" t="n">
-        <v>56714</v>
+        <v>79920</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -15410,50 +15410,45 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>529464</v>
+        <v>529620</v>
       </c>
       <c r="R108" t="n">
-        <v>7000057</v>
+        <v>7000131</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -15485,7 +15480,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -15495,7 +15490,12 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>På en sälg tillsammans med luddlav och lunglav.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -15504,12 +15504,33 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -15527,10 +15548,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124791504</v>
+        <v>124791501</v>
       </c>
       <c r="B109" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -15539,32 +15560,32 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
@@ -15624,7 +15645,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och lunglav.</t>
+          <t>På en sälg tillsammans med luddlav och stuplav.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -15677,10 +15698,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124791501</v>
+        <v>124791641</v>
       </c>
       <c r="B110" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -15689,48 +15710,61 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>529620</v>
+        <v>529611</v>
       </c>
       <c r="R110" t="n">
-        <v>7000131</v>
+        <v>7000387</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -15759,7 +15793,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -15769,12 +15803,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>På en sälg tillsammans med luddlav och stuplav.</t>
+          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -15790,26 +15824,6 @@
       <c r="AH110" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -15827,10 +15841,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124791641</v>
+        <v>124791633</v>
       </c>
       <c r="B111" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -15839,43 +15853,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -15883,17 +15889,17 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>529611</v>
+        <v>529464</v>
       </c>
       <c r="R111" t="n">
-        <v>7000387</v>
+        <v>7000057</v>
       </c>
       <c r="S111" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -15922,7 +15928,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -15932,12 +15938,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Minst 45 plantor och 3 vinterståndare inom ca 1 m2 yta.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -15946,7 +15947,6 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -18837,14 +18837,14 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124791464</v>
+        <v>124791468</v>
       </c>
       <c r="B132" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -18853,44 +18853,49 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>529530</v>
+        <v>529561</v>
       </c>
       <c r="R132" t="n">
-        <v>7000400</v>
+        <v>7000407</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -18919,7 +18924,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -18929,12 +18934,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Fertila bålar.</t>
+          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -18943,7 +18948,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -18954,22 +18958,22 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -18987,10 +18991,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124791468</v>
+        <v>124791464</v>
       </c>
       <c r="B133" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -19003,49 +19007,44 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>529561</v>
+        <v>529530</v>
       </c>
       <c r="R133" t="n">
-        <v>7000407</v>
+        <v>7000400</v>
       </c>
       <c r="S133" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -19074,7 +19073,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -19084,12 +19083,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och halvgamla, på stambasen.</t>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -19098,6 +19097,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -19108,22 +19108,22 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>

--- a/artfynd/A 2288-2025 artfynd.xlsx
+++ b/artfynd/A 2288-2025 artfynd.xlsx
@@ -6468,10 +6468,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124465862</v>
+        <v>124464827</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6480,55 +6480,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Trättflon, Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>529657</v>
+        <v>529687</v>
       </c>
       <c r="R46" t="n">
-        <v>6999868</v>
+        <v>6999902</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
+          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6604,10 +6604,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124468934</v>
+        <v>124463106</v>
       </c>
       <c r="B47" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6616,31 +6616,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6649,13 +6649,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>529638</v>
+        <v>529619</v>
       </c>
       <c r="R47" t="n">
-        <v>6999974</v>
+        <v>6999959</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6694,7 +6694,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Växer på en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6882,10 +6887,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124465010</v>
+        <v>124453319</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6894,55 +6899,41 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529689</v>
+        <v>529470</v>
       </c>
       <c r="R49" t="n">
-        <v>6999902</v>
+        <v>7000406</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6971,7 +6962,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6981,12 +6972,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:13</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7000,7 +6986,27 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7018,10 +7024,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124468910</v>
+        <v>124463284</v>
       </c>
       <c r="B50" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7034,39 +7040,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529641</v>
+        <v>529624</v>
       </c>
       <c r="R50" t="n">
-        <v>6999979</v>
+        <v>6999926</v>
       </c>
       <c r="S50" t="n">
         <v>9</v>
@@ -7098,7 +7099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7108,7 +7109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7127,22 +7128,22 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -7160,7 +7161,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124453319</v>
+        <v>124471506</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -7200,10 +7201,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>529470</v>
+        <v>529632</v>
       </c>
       <c r="R51" t="n">
-        <v>7000406</v>
+        <v>7000254</v>
       </c>
       <c r="S51" t="n">
         <v>7</v>
@@ -7235,7 +7236,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7245,7 +7246,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7297,10 +7303,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124462545</v>
+        <v>124469884</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7309,31 +7315,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7342,13 +7357,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>529580</v>
+        <v>529708</v>
       </c>
       <c r="R52" t="n">
-        <v>6999910</v>
+        <v>7000000</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7377,7 +7392,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7387,12 +7402,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
+          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7407,26 +7422,6 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7444,10 +7439,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124471506</v>
+        <v>124465862</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7456,41 +7451,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>529632</v>
+        <v>529657</v>
       </c>
       <c r="R53" t="n">
-        <v>7000254</v>
+        <v>6999868</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7519,7 +7528,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7529,12 +7538,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Minst 28 plantor inom 1 m2 intill en stor rotvälta.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7548,27 +7557,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -7586,7 +7575,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124462260</v>
+        <v>124468969</v>
       </c>
       <c r="B54" t="n">
         <v>79891</v>
@@ -7620,24 +7609,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>529584</v>
+        <v>529652</v>
       </c>
       <c r="R54" t="n">
-        <v>6999935</v>
+        <v>6999989</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7666,7 +7650,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7676,12 +7660,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7695,7 +7674,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -7733,10 +7712,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124464307</v>
+        <v>124468934</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7745,40 +7724,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7787,13 +7757,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>529649</v>
+        <v>529638</v>
       </c>
       <c r="R55" t="n">
-        <v>6999915</v>
+        <v>6999974</v>
       </c>
       <c r="S55" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7822,7 +7792,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7832,12 +7802,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:51</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7852,6 +7817,26 @@
       <c r="AH55" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7869,7 +7854,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124469884</v>
+        <v>124465010</v>
       </c>
       <c r="B56" t="n">
         <v>98101</v>
@@ -7904,7 +7889,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7923,13 +7908,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>529708</v>
+        <v>529689</v>
       </c>
       <c r="R56" t="n">
-        <v>7000000</v>
+        <v>6999902</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7958,7 +7943,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7968,12 +7953,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 50 plantor och 4 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 37 plantor och 3 vinterståndare inom ca 2 x 0,5 m2.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7987,7 +7972,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -8005,7 +7990,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124468294</v>
+        <v>124464307</v>
       </c>
       <c r="B57" t="n">
         <v>98101</v>
@@ -8040,7 +8025,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -8059,10 +8044,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>529689</v>
+        <v>529649</v>
       </c>
       <c r="R57" t="n">
-        <v>6999938</v>
+        <v>6999915</v>
       </c>
       <c r="S57" t="n">
         <v>8</v>
@@ -8094,7 +8079,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -8104,12 +8089,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
+          <t>Minst 16 plantor och 2 vinterståndare inom ca 1 m2 intill en sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8141,10 +8126,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124471570</v>
+        <v>124464556</v>
       </c>
       <c r="B58" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -8153,25 +8138,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -8181,13 +8166,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>529604</v>
+        <v>529670</v>
       </c>
       <c r="R58" t="n">
-        <v>7000308</v>
+        <v>6999909</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8216,7 +8201,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8226,7 +8211,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8240,7 +8225,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -8258,7 +8263,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124463366</v>
+        <v>124463397</v>
       </c>
       <c r="B59" t="n">
         <v>79891</v>
@@ -8303,13 +8308,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>529608</v>
+        <v>529620</v>
       </c>
       <c r="R59" t="n">
-        <v>6999935</v>
+        <v>6999932</v>
       </c>
       <c r="S59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8338,7 +8343,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8348,7 +8353,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8400,10 +8405,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124464827</v>
+        <v>124471362</v>
       </c>
       <c r="B60" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8412,55 +8417,55 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>529687</v>
+        <v>529623</v>
       </c>
       <c r="R60" t="n">
-        <v>6999902</v>
+        <v>7000094</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8489,7 +8494,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8499,12 +8504,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog med murkna björkhögstubbar för talltitans bohålsbygge.</t>
+          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8518,7 +8523,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -8673,10 +8678,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124471362</v>
+        <v>124465430</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8685,40 +8690,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -8727,13 +8723,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>529623</v>
+        <v>529636</v>
       </c>
       <c r="R62" t="n">
-        <v>7000094</v>
+        <v>6999890</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8762,7 +8758,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>19:41</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8772,12 +8768,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>19:41</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 130 plantor och 8 vinterståndare inom ca 1 m2.</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8791,7 +8782,27 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8809,10 +8820,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124463284</v>
+        <v>124471570</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8821,25 +8832,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -8849,13 +8860,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>529624</v>
+        <v>529604</v>
       </c>
       <c r="R63" t="n">
-        <v>6999926</v>
+        <v>7000308</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8884,7 +8895,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8894,7 +8905,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8908,27 +8919,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8946,10 +8937,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124465430</v>
+        <v>124470698</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8958,31 +8949,40 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8991,13 +8991,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>529636</v>
+        <v>529625</v>
       </c>
       <c r="R64" t="n">
-        <v>6999890</v>
+        <v>7000048</v>
       </c>
       <c r="S64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -9036,7 +9036,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9050,27 +9055,7 @@
       </c>
       <c r="AH64" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -9224,10 +9209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124471744</v>
+        <v>124464353</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9240,37 +9225,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>529601</v>
+        <v>529642</v>
       </c>
       <c r="R66" t="n">
-        <v>7000312</v>
+        <v>6999931</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -9299,7 +9289,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -9309,7 +9299,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9323,27 +9313,27 @@
       </c>
       <c r="AH66" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9361,7 +9351,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124470698</v>
+        <v>124462835</v>
       </c>
       <c r="B67" t="n">
         <v>98101</v>
@@ -9396,7 +9386,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -9415,13 +9405,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>529625</v>
+        <v>529579</v>
       </c>
       <c r="R67" t="n">
-        <v>7000048</v>
+        <v>6999920</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9450,7 +9440,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9460,12 +9450,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 0,5 m2.</t>
+          <t>Minst 38 plantor inom ca 0,5 m2.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9497,7 +9487,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124463106</v>
+        <v>124462545</v>
       </c>
       <c r="B68" t="n">
         <v>79891</v>
@@ -9542,13 +9532,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>529619</v>
+        <v>529580</v>
       </c>
       <c r="R68" t="n">
-        <v>6999959</v>
+        <v>6999910</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -9577,7 +9567,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9587,12 +9577,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Växer på en gammal grovbarkad sälg.</t>
+          <t>Växer på tre gamla grovbarkade skadade sälgar.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9606,7 +9596,7 @@
       </c>
       <c r="AH68" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -9644,10 +9634,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124462835</v>
+        <v>124462260</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9656,40 +9646,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9698,13 +9679,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>529579</v>
+        <v>529584</v>
       </c>
       <c r="R69" t="n">
-        <v>6999920</v>
+        <v>6999935</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -9733,7 +9714,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9743,12 +9724,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Minst 38 plantor inom ca 0,5 m2.</t>
+          <t>Växer på en gammal grovbarkad sälg i barrblandskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9763,6 +9744,26 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -9780,10 +9781,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124468969</v>
+        <v>124468910</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9796,37 +9797,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>529652</v>
+        <v>529641</v>
       </c>
       <c r="R70" t="n">
-        <v>6999989</v>
+        <v>6999979</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9855,7 +9861,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9865,7 +9871,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9917,10 +9923,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124463397</v>
+        <v>124471744</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9933,39 +9939,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>529620</v>
+        <v>529601</v>
       </c>
       <c r="R71" t="n">
-        <v>6999932</v>
+        <v>7000312</v>
       </c>
       <c r="S71" t="n">
         <v>8</v>
@@ -9997,7 +9998,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -10007,7 +10008,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -10026,22 +10027,22 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -10059,7 +10060,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124467882</v>
+        <v>124468294</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -10094,7 +10095,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -10113,10 +10114,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>529678</v>
+        <v>529689</v>
       </c>
       <c r="R72" t="n">
-        <v>6999878</v>
+        <v>6999938</v>
       </c>
       <c r="S72" t="n">
         <v>8</v>
@@ -10148,7 +10149,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -10158,12 +10159,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
+          <t>Mattbildande växtsätt med minst 330 plantor och 16 vinterståndare inom ca 1 m2.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -10195,7 +10196,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124464353</v>
+        <v>124463366</v>
       </c>
       <c r="B73" t="n">
         <v>79891</v>
@@ -10240,13 +10241,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>529642</v>
+        <v>529608</v>
       </c>
       <c r="R73" t="n">
-        <v>6999931</v>
+        <v>6999935</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -10275,7 +10276,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -10285,7 +10286,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10299,7 +10300,7 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -10337,10 +10338,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124464556</v>
+        <v>124467882</v>
       </c>
       <c r="B74" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -10349,41 +10350,55 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Trättflon, Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>529670</v>
+        <v>529678</v>
       </c>
       <c r="R74" t="n">
-        <v>6999909</v>
+        <v>6999878</v>
       </c>
       <c r="S74" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10412,7 +10427,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10422,7 +10437,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Minst 160 plantor och 5 vinterståndare inom ca 3 m2.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10437,26 +10457,6 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -10625,10 +10625,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124541322</v>
+        <v>124541341</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10637,44 +10637,61 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>529565</v>
+        <v>529549</v>
       </c>
       <c r="R76" t="n">
-        <v>7000430</v>
+        <v>7000412</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -10703,7 +10720,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10713,7 +10730,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10722,7 +10739,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -10731,24 +10747,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Gammal granskog.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -10912,10 +10913,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124541341</v>
+        <v>124541265</v>
       </c>
       <c r="B78" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10924,61 +10925,44 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>529549</v>
+        <v>529530</v>
       </c>
       <c r="R78" t="n">
-        <v>7000412</v>
+        <v>7000434</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -11007,7 +10991,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -11017,7 +11001,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -11026,6 +11015,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -11034,9 +11024,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Gammal granskog.</t>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -11204,10 +11209,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124541265</v>
+        <v>124540904</v>
       </c>
       <c r="B80" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -11220,37 +11225,41 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>529530</v>
+        <v>529475</v>
       </c>
       <c r="R80" t="n">
-        <v>7000434</v>
+        <v>7000452</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -11282,7 +11291,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -11292,12 +11301,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Fertil lunglav på en lutande smal sälg.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -11312,27 +11321,27 @@
       </c>
       <c r="AH80" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -11350,10 +11359,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124540904</v>
+        <v>124541322</v>
       </c>
       <c r="B81" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -11366,41 +11375,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>529475</v>
+        <v>529565</v>
       </c>
       <c r="R81" t="n">
-        <v>7000452</v>
+        <v>7000430</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11432,7 +11437,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -11442,12 +11447,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:02</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Fertil lunglav på en lutande smal sälg.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -11462,27 +11462,27 @@
       </c>
       <c r="AH81" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -11800,7 +11800,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124541545</v>
+        <v>124541689</v>
       </c>
       <c r="B84" t="n">
         <v>78810</v>
@@ -11839,14 +11839,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
+          <t>Trättflon, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>529524</v>
+        <v>529457</v>
       </c>
       <c r="R84" t="n">
-        <v>7000430</v>
+        <v>7000423</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11888,7 +11888,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="AH84" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -12092,7 +12092,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124541689</v>
+        <v>124541545</v>
       </c>
       <c r="B86" t="n">
         <v>78810</v>
@@ -12131,14 +12131,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Trättflon, Jmt</t>
+          <t>Trättflon, Stugubäckmyran, Stugun, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>529457</v>
+        <v>529524</v>
       </c>
       <c r="R86" t="n">
-        <v>7000423</v>
+        <v>7000430</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -12388,10 +12388,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124791246</v>
+        <v>124791073</v>
       </c>
       <c r="B88" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -12404,30 +12404,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -12435,13 +12431,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>529442</v>
+       